--- a/template_defensie_hr.xlsx
+++ b/template_defensie_hr.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1038">
   <si>
     <t>Personeelsnummer</t>
   </si>
@@ -518,1951 +518,1960 @@
     <t>5</t>
   </si>
   <si>
-    <t>Anita</t>
-  </si>
-  <si>
-    <t>Leopold</t>
-  </si>
-  <si>
-    <t>Martine</t>
-  </si>
-  <si>
-    <t>Arne</t>
-  </si>
-  <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t>Van Dyck</t>
-  </si>
-  <si>
-    <t>Vandeputte</t>
-  </si>
-  <si>
-    <t>Vereecke</t>
-  </si>
-  <si>
-    <t>Merckx</t>
-  </si>
-  <si>
-    <t>Huybrechts</t>
+    <t>Stefan</t>
+  </si>
+  <si>
+    <t>Maarten</t>
+  </si>
+  <si>
+    <t>Mohammed</t>
+  </si>
+  <si>
+    <t>Bo</t>
+  </si>
+  <si>
+    <t>Guy</t>
+  </si>
+  <si>
+    <t>De Clercq</t>
+  </si>
+  <si>
+    <t>Jacobs</t>
+  </si>
+  <si>
+    <t>Huys</t>
+  </si>
+  <si>
+    <t>Verbeke</t>
+  </si>
+  <si>
+    <t>De Baere</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>V</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>26/04/1989</t>
-  </si>
-  <si>
-    <t>29/12/2000</t>
-  </si>
-  <si>
-    <t>13/05/1998</t>
-  </si>
-  <si>
-    <t>15/10/1994</t>
-  </si>
-  <si>
-    <t>20/05/1982</t>
-  </si>
-  <si>
-    <t>Rosières</t>
-  </si>
-  <si>
-    <t>Vitrival</t>
-  </si>
-  <si>
-    <t>Aarsele</t>
-  </si>
-  <si>
-    <t>Lustin</t>
-  </si>
-  <si>
-    <t>Soulme</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Luxemburgs</t>
-  </si>
-  <si>
-    <t>Duits</t>
-  </si>
-  <si>
-    <t>Noors</t>
-  </si>
-  <si>
-    <t>Nederlands</t>
-  </si>
-  <si>
-    <t>Frans</t>
+    <t>01/06/1973</t>
+  </si>
+  <si>
+    <t>03/11/1984</t>
+  </si>
+  <si>
+    <t>05/07/1980</t>
+  </si>
+  <si>
+    <t>06/07/1976</t>
+  </si>
+  <si>
+    <t>29/06/1986</t>
+  </si>
+  <si>
+    <t>Lapscheure</t>
+  </si>
+  <si>
+    <t>Harsin</t>
+  </si>
+  <si>
+    <t>Haren-Tongeren</t>
+  </si>
+  <si>
+    <t>Okegem</t>
+  </si>
+  <si>
+    <t>Micheroux</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Oostenrijks</t>
+  </si>
+  <si>
+    <t>Italiaans</t>
+  </si>
+  <si>
+    <t>Iers</t>
+  </si>
+  <si>
+    <t>Belgisch</t>
   </si>
   <si>
     <t>Weduwe/Weduwnaar</t>
   </si>
   <si>
+    <t>Gehuwd</t>
+  </si>
+  <si>
+    <t>Ongehuwd</t>
+  </si>
+  <si>
     <t>Wettelijk samenwonend</t>
   </si>
   <si>
-    <t>Gehuwd</t>
-  </si>
-  <si>
-    <t>Gescheiden</t>
-  </si>
-  <si>
-    <t>50.06.01-679.92</t>
-  </si>
-  <si>
-    <t>03.09.11-411.93</t>
-  </si>
-  <si>
-    <t>92.09.26-182.63</t>
-  </si>
-  <si>
-    <t>88.03.24-076.06</t>
-  </si>
-  <si>
-    <t>03.05.28-754.85</t>
-  </si>
-  <si>
-    <t>AH0814830</t>
-  </si>
-  <si>
-    <t>BD0722302</t>
-  </si>
-  <si>
-    <t>MY3926516</t>
-  </si>
-  <si>
-    <t>FH6567607</t>
-  </si>
-  <si>
-    <t>MM4957516</t>
-  </si>
-  <si>
-    <t>385-4835091-72</t>
-  </si>
-  <si>
-    <t>199-1378218-99</t>
-  </si>
-  <si>
-    <t>858-7875435-37</t>
-  </si>
-  <si>
-    <t>525-6958677-82</t>
-  </si>
-  <si>
-    <t>307-3627966-49</t>
+    <t>02.06.25-588.36</t>
+  </si>
+  <si>
+    <t>86.05.25-626.77</t>
+  </si>
+  <si>
+    <t>04.01.01-874.89</t>
+  </si>
+  <si>
+    <t>00.04.24-662.33</t>
+  </si>
+  <si>
+    <t>68.09.27-054.45</t>
+  </si>
+  <si>
+    <t>IZ3202247</t>
+  </si>
+  <si>
+    <t>IZ8883708</t>
+  </si>
+  <si>
+    <t>IY7429908</t>
+  </si>
+  <si>
+    <t>XR8498537</t>
+  </si>
+  <si>
+    <t>LN9328855</t>
+  </si>
+  <si>
+    <t>849-8817796-51</t>
+  </si>
+  <si>
+    <t>405-4402372-16</t>
+  </si>
+  <si>
+    <t>873-4888748-64</t>
+  </si>
+  <si>
+    <t>941-6775376-19</t>
+  </si>
+  <si>
+    <t>544-4506948-39</t>
   </si>
   <si>
     <t>B-</t>
   </si>
   <si>
+    <t>A+</t>
+  </si>
+  <si>
     <t>O+</t>
   </si>
   <si>
-    <t>AB+</t>
-  </si>
-  <si>
-    <t>O-</t>
-  </si>
-  <si>
-    <t>A-</t>
-  </si>
-  <si>
-    <t>joppe22@example.com</t>
-  </si>
-  <si>
-    <t>pde-groote@example.org</t>
-  </si>
-  <si>
-    <t>stien39@example.org</t>
-  </si>
-  <si>
-    <t>yveswauters@example.org</t>
-  </si>
-  <si>
-    <t>wvan-hecke@example.org</t>
-  </si>
-  <si>
-    <t>+3268-7667260</t>
-  </si>
-  <si>
-    <t>+32887 173864</t>
-  </si>
-  <si>
-    <t>0686-787423</t>
-  </si>
-  <si>
-    <t>+32(0)49 0827083</t>
-  </si>
-  <si>
-    <t>0067-176779</t>
-  </si>
-  <si>
-    <t>Kevinsingel</t>
-  </si>
-  <si>
-    <t>Elsring</t>
-  </si>
-  <si>
-    <t>Lowielaan</t>
-  </si>
-  <si>
-    <t>Stéphanielei</t>
-  </si>
-  <si>
-    <t>Lisettesteeg</t>
-  </si>
-  <si>
-    <t>19B</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>9423</t>
-  </si>
-  <si>
-    <t>7135</t>
-  </si>
-  <si>
-    <t>3024</t>
-  </si>
-  <si>
-    <t>5151</t>
-  </si>
-  <si>
-    <t>9094</t>
-  </si>
-  <si>
-    <t>Neufchâteau</t>
-  </si>
-  <si>
-    <t>Aarschot</t>
-  </si>
-  <si>
-    <t>Edelare</t>
-  </si>
-  <si>
-    <t>Briegden</t>
-  </si>
-  <si>
-    <t>Nevele</t>
-  </si>
-  <si>
-    <t>Afghanistan</t>
-  </si>
-  <si>
-    <t>Macau</t>
-  </si>
-  <si>
-    <t>Man</t>
-  </si>
-  <si>
-    <t>Sri Lanka</t>
-  </si>
-  <si>
-    <t>Turkmenistan</t>
-  </si>
-  <si>
-    <t>Georges Deleu Verhoeven</t>
-  </si>
-  <si>
-    <t>Kristel Hens</t>
-  </si>
-  <si>
-    <t>Arthur Bervoets</t>
-  </si>
-  <si>
-    <t>Mike Thijs</t>
-  </si>
-  <si>
-    <t>Anita Van den Broeck</t>
-  </si>
-  <si>
-    <t>+32754 010414</t>
-  </si>
-  <si>
-    <t>+32(0)823 475520</t>
-  </si>
-  <si>
-    <t>+3245 3291031</t>
-  </si>
-  <si>
-    <t>046 0333094</t>
-  </si>
-  <si>
-    <t>+3262 1420717</t>
-  </si>
-  <si>
-    <t>Moeder</t>
+    <t>huybrechtsgeorges@example.com</t>
+  </si>
+  <si>
+    <t>bpauwels@example.org</t>
+  </si>
+  <si>
+    <t>veerle75@example.net</t>
+  </si>
+  <si>
+    <t>sjacobs@example.org</t>
+  </si>
+  <si>
+    <t>kevinlemmens@example.org</t>
+  </si>
+  <si>
+    <t>086-8440038</t>
+  </si>
+  <si>
+    <t>+32881-055765</t>
+  </si>
+  <si>
+    <t>+32(0)439-066744</t>
+  </si>
+  <si>
+    <t>(0312)-662930</t>
+  </si>
+  <si>
+    <t>(0262) 653260</t>
+  </si>
+  <si>
+    <t>Annieweg</t>
+  </si>
+  <si>
+    <t>Edgardring</t>
+  </si>
+  <si>
+    <t>Kjellbaan</t>
+  </si>
+  <si>
+    <t>Carinesteeg</t>
+  </si>
+  <si>
+    <t>Brunosteeg</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>3707</t>
+  </si>
+  <si>
+    <t>3412</t>
+  </si>
+  <si>
+    <t>4680</t>
+  </si>
+  <si>
+    <t>2164</t>
+  </si>
+  <si>
+    <t>8147</t>
+  </si>
+  <si>
+    <t>Liezele</t>
+  </si>
+  <si>
+    <t>Zutendaal</t>
+  </si>
+  <si>
+    <t>Pecq</t>
+  </si>
+  <si>
+    <t>Spermalie</t>
+  </si>
+  <si>
+    <t>Edingen</t>
+  </si>
+  <si>
+    <t>Brits Indische Oceaanterritorium</t>
+  </si>
+  <si>
+    <t>Libië</t>
+  </si>
+  <si>
+    <t>Wallis en Futuna</t>
+  </si>
+  <si>
+    <t>Tuvalu</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Elias Van Driessche</t>
+  </si>
+  <si>
+    <t>Kathleen Verhoeven</t>
+  </si>
+  <si>
+    <t>Anne Torfs</t>
+  </si>
+  <si>
+    <t>Ida Cornelis</t>
+  </si>
+  <si>
+    <t>Marieke Lambert</t>
+  </si>
+  <si>
+    <t>+32(0)11-1930334</t>
+  </si>
+  <si>
+    <t>(0839)-386616</t>
+  </si>
+  <si>
+    <t>(0113)-547098</t>
+  </si>
+  <si>
+    <t>01 239 00 20</t>
+  </si>
+  <si>
+    <t>0435 170059</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>Broer</t>
   </si>
   <si>
     <t>Vader</t>
   </si>
   <si>
-    <t>Dochter</t>
-  </si>
-  <si>
-    <t>Vriend(in)</t>
-  </si>
-  <si>
-    <t>Luitenant-Generaal</t>
-  </si>
-  <si>
-    <t>Sergeant</t>
-  </si>
-  <si>
-    <t>Kapitein</t>
-  </si>
-  <si>
-    <t>Eerste Sergeant</t>
+    <t>Soldaat</t>
   </si>
   <si>
     <t>Korporaal</t>
   </si>
   <si>
-    <t>M627153</t>
-  </si>
-  <si>
-    <t>M825803</t>
-  </si>
-  <si>
-    <t>M705504</t>
-  </si>
-  <si>
-    <t>M790591</t>
-  </si>
-  <si>
-    <t>M515348</t>
-  </si>
-  <si>
-    <t>39-589722</t>
-  </si>
-  <si>
-    <t>73-827326</t>
-  </si>
-  <si>
-    <t>88-533036</t>
-  </si>
-  <si>
-    <t>87-249342</t>
-  </si>
-  <si>
-    <t>33-997994</t>
-  </si>
-  <si>
-    <t>2de Regiment Lansiers</t>
-  </si>
-  <si>
-    <t>Mine Counter Measures</t>
-  </si>
-  <si>
-    <t>4de Regiment Genie</t>
+    <t>Eerste Korporaal</t>
+  </si>
+  <si>
+    <t>Majoor</t>
+  </si>
+  <si>
+    <t>Brigadegeneraal</t>
+  </si>
+  <si>
+    <t>M276403</t>
+  </si>
+  <si>
+    <t>M543661</t>
+  </si>
+  <si>
+    <t>M920850</t>
+  </si>
+  <si>
+    <t>M807086</t>
+  </si>
+  <si>
+    <t>M647184</t>
+  </si>
+  <si>
+    <t>47-407280</t>
+  </si>
+  <si>
+    <t>51-108156</t>
+  </si>
+  <si>
+    <t>25-533168</t>
+  </si>
+  <si>
+    <t>49-931286</t>
+  </si>
+  <si>
+    <t>45-265281</t>
+  </si>
+  <si>
+    <t>2de Bataljon Jagers te Voet</t>
+  </si>
+  <si>
+    <t>Bataljon ISTAR</t>
+  </si>
+  <si>
+    <t>3de Bataljon Parachutisten</t>
   </si>
   <si>
     <t>1ste Bataljon Artillerie</t>
   </si>
   <si>
-    <t>Medisch Interventiecentrum</t>
+    <t>1ste Regiment Gidsen</t>
+  </si>
+  <si>
+    <t>Luchtcomponent</t>
+  </si>
+  <si>
+    <t>Landcomponent</t>
+  </si>
+  <si>
+    <t>Marinecomponent</t>
   </si>
   <si>
     <t>Medische Component</t>
   </si>
   <si>
-    <t>Landcomponent</t>
-  </si>
-  <si>
-    <t>Luchtcomponent</t>
-  </si>
-  <si>
-    <t>Luchtmachtbasis Florennes</t>
+    <t>Kwartier Berlaar</t>
+  </si>
+  <si>
+    <t>Kamp Lagland - Arlon</t>
+  </si>
+  <si>
+    <t>Kwartier Lombardsijde</t>
   </si>
   <si>
     <t>Kwartier Majoor Housiau - Marche-en-Famenne</t>
   </si>
   <si>
-    <t>Kamp Lagland - Arlon</t>
-  </si>
-  <si>
-    <t>Kwartier Rucquoy - Tournai</t>
-  </si>
-  <si>
-    <t>Paracommando</t>
-  </si>
-  <si>
-    <t>Mechanieker luchtvaartuigen</t>
+    <t>Kamp Beverlo - Leopoldsburg</t>
+  </si>
+  <si>
+    <t>Infanterist</t>
+  </si>
+  <si>
+    <t>Muzikant</t>
+  </si>
+  <si>
+    <t>Navigator</t>
   </si>
   <si>
     <t>Genieofficier</t>
   </si>
   <si>
-    <t>Brandbestrijding</t>
-  </si>
-  <si>
-    <t>Luchtmachtpiloot</t>
-  </si>
-  <si>
-    <t>16/11/2017</t>
-  </si>
-  <si>
-    <t>13/05/2021</t>
-  </si>
-  <si>
-    <t>23/09/1987</t>
-  </si>
-  <si>
-    <t>17/08/1995</t>
-  </si>
-  <si>
-    <t>22/10/1989</t>
-  </si>
-  <si>
-    <t>22/04/2009</t>
-  </si>
-  <si>
-    <t>14/05/2020</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Stand-by</t>
+    <t>23/03/2009</t>
+  </si>
+  <si>
+    <t>07/08/2018</t>
+  </si>
+  <si>
+    <t>04/07/1999</t>
+  </si>
+  <si>
+    <t>24/11/2012</t>
+  </si>
+  <si>
+    <t>04/11/1994</t>
+  </si>
+  <si>
+    <t>30/11/2009</t>
+  </si>
+  <si>
+    <t>17/06/2015</t>
+  </si>
+  <si>
+    <t>04/10/2020</t>
+  </si>
+  <si>
+    <t>24/01/2004</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Medisch onbeschikbaar</t>
+  </si>
+  <si>
+    <t>Ingezet - Binnenland</t>
+  </si>
+  <si>
+    <t>Reserve</t>
+  </si>
+  <si>
+    <t>Pensioen</t>
   </si>
   <si>
     <t>Verlof</t>
   </si>
   <si>
-    <t>In opleiding</t>
-  </si>
-  <si>
-    <t>Medisch onbeschikbaar</t>
-  </si>
-  <si>
-    <t>Reserve</t>
+    <t>Zeer Geheim</t>
+  </si>
+  <si>
+    <t>Vertrouwelijk</t>
+  </si>
+  <si>
+    <t>Cosmic Top Secret (NATO)</t>
+  </si>
+  <si>
+    <t>Geheim</t>
+  </si>
+  <si>
+    <t>HO1</t>
+  </si>
+  <si>
+    <t>BOO4</t>
+  </si>
+  <si>
+    <t>HO3</t>
+  </si>
+  <si>
+    <t>BOF2</t>
+  </si>
+  <si>
+    <t>BOO3</t>
+  </si>
+  <si>
+    <t>FN Five-seveN - Standaard</t>
+  </si>
+  <si>
+    <t>FN P90 - Standaard</t>
+  </si>
+  <si>
+    <t>Niet gekwalificeerd</t>
+  </si>
+  <si>
+    <t>82/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>88/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>94/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>55/100 (Voldoende)</t>
+  </si>
+  <si>
+    <t>76/100 (Goed)</t>
+  </si>
+  <si>
+    <t>Rupsbandvoertuig - Piranha</t>
+  </si>
+  <si>
+    <t>Rupsbandvoertuig - Pandur</t>
+  </si>
+  <si>
+    <t>CE - Vrachtwagen + aanhanger</t>
+  </si>
+  <si>
+    <t>D - Bus / Troepenvervoer</t>
+  </si>
+  <si>
+    <t>Nederlands: B2; Engels: B1; Frans: B2</t>
+  </si>
+  <si>
+    <t>Duits: B1; Engels: C1</t>
+  </si>
+  <si>
+    <t>Engels: B2; Frans: B1</t>
+  </si>
+  <si>
+    <t>Engels: C2; Nederlands: Moedertaal</t>
+  </si>
+  <si>
+    <t>Nederlands: Moedertaal; Engels: C2</t>
   </si>
   <si>
     <t>Geen</t>
   </si>
   <si>
-    <t>Vertrouwelijk</t>
-  </si>
-  <si>
-    <t>Zeer Geheim</t>
-  </si>
-  <si>
-    <t>HO3</t>
-  </si>
-  <si>
-    <t>BV1</t>
-  </si>
-  <si>
-    <t>HO4</t>
-  </si>
-  <si>
-    <t>BOO3</t>
-  </si>
-  <si>
-    <t>FN MAG - Gekwalificeerd</t>
-  </si>
-  <si>
-    <t>Carl Gustaf - Gekwalificeerd</t>
-  </si>
-  <si>
-    <t>M72 LAW - Gekwalificeerd</t>
-  </si>
-  <si>
-    <t>Niet gekwalificeerd</t>
-  </si>
-  <si>
-    <t>FN P90 - Standaard</t>
-  </si>
-  <si>
-    <t>63/100 (Voldoende)</t>
-  </si>
-  <si>
-    <t>100/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>97/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>50/100 (Voldoende)</t>
-  </si>
-  <si>
-    <t>93/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>C - Vrachtwagen</t>
-  </si>
-  <si>
-    <t>Rupsbandvoertuig - Dingo</t>
-  </si>
-  <si>
-    <t>D - Bus / Troepenvervoer</t>
-  </si>
-  <si>
-    <t>Nederlands: B1; Duits: C1; Frans: C2; Engels: A2</t>
-  </si>
-  <si>
-    <t>Nederlands: C2; Engels: A2; Duits: C1</t>
-  </si>
-  <si>
-    <t>Engels: A2; Frans: C1; Duits: B1; Nederlands: C2</t>
-  </si>
-  <si>
-    <t>Duits: B1; Nederlands: C1</t>
-  </si>
-  <si>
-    <t>Engels: B1; Duits: B2; Nederlands: B1</t>
-  </si>
-  <si>
-    <t>Militair Kruis 2de Klasse; Medaille NATO Meritorious Service; Herinneringsmedaille Humanitaire Operaties</t>
-  </si>
-  <si>
-    <t>Operatiemedaille ISAF; Militair Kruis 2de Klasse; Herinneringsmedaille Buitenlandse Operaties</t>
-  </si>
-  <si>
-    <t>KERKHOFS I.G. / 42-316602 / O-</t>
-  </si>
-  <si>
-    <t>WELLENS W.E. / 58-250491 / A+</t>
-  </si>
-  <si>
-    <t>CLAES E.P. / 94-503284 / A+</t>
-  </si>
-  <si>
-    <t>DESMET A.P. / 20-430413 / B-</t>
-  </si>
-  <si>
-    <t>DE BLOCK P.A. / 56-140137 / B+</t>
-  </si>
-  <si>
-    <t>BE57838641235835</t>
-  </si>
-  <si>
-    <t>BE62260460943261</t>
-  </si>
-  <si>
-    <t>BE48630883909327</t>
-  </si>
-  <si>
-    <t>BE77586783151842</t>
-  </si>
-  <si>
-    <t>BE82411471601268</t>
-  </si>
-  <si>
-    <t>Martens BV</t>
-  </si>
-  <si>
-    <t>Everaert CV</t>
-  </si>
-  <si>
-    <t>Van Dijck-Van Impe VOF</t>
-  </si>
-  <si>
-    <t>Baert-Huysmans NV</t>
-  </si>
-  <si>
-    <t>Verhaeghe VOF</t>
-  </si>
-  <si>
-    <t>BE0646913453</t>
-  </si>
-  <si>
-    <t>BE0253768956</t>
-  </si>
-  <si>
-    <t>BE0650546620</t>
-  </si>
-  <si>
-    <t>BE0593107303</t>
-  </si>
-  <si>
-    <t>BE0275923152</t>
-  </si>
-  <si>
-    <t>8430031260609</t>
-  </si>
-  <si>
-    <t>8437104180154</t>
-  </si>
-  <si>
-    <t>8710401089659</t>
-  </si>
-  <si>
-    <t>8433750362890</t>
-  </si>
-  <si>
-    <t>5412934646417</t>
+    <t>Burgerlijk Kruis 1ste Klasse; Operatiemedaille ISAF</t>
+  </si>
+  <si>
+    <t>VAN RAEMDONCK A.Y. / 57-685829 / AB+</t>
+  </si>
+  <si>
+    <t>DEVOS C.K. / 52-986300 / A-</t>
+  </si>
+  <si>
+    <t>DE WITTE N.W. / 18-410320 / O+</t>
+  </si>
+  <si>
+    <t>PAUWELS M.I. / 67-410471 / AB-</t>
+  </si>
+  <si>
+    <t>MERCKX F.F. / 66-207391 / AB+</t>
+  </si>
+  <si>
+    <t>BE02919937663840</t>
+  </si>
+  <si>
+    <t>BE46311336849036</t>
+  </si>
+  <si>
+    <t>BE76276936901095</t>
+  </si>
+  <si>
+    <t>BE28908790062920</t>
+  </si>
+  <si>
+    <t>BE43030942136801</t>
+  </si>
+  <si>
+    <t>Desmedt BV</t>
+  </si>
+  <si>
+    <t>Deconinck NV</t>
+  </si>
+  <si>
+    <t>De Vos-Viaene NV</t>
+  </si>
+  <si>
+    <t>Merckx-De Clercq BV</t>
+  </si>
+  <si>
+    <t>Van den Broeck-Goossens NV</t>
+  </si>
+  <si>
+    <t>BE0758424689</t>
+  </si>
+  <si>
+    <t>BE0699904062</t>
+  </si>
+  <si>
+    <t>BE0373972322</t>
+  </si>
+  <si>
+    <t>BE0435694001</t>
+  </si>
+  <si>
+    <t>BE0105509989</t>
+  </si>
+  <si>
+    <t>5412475984672</t>
+  </si>
+  <si>
+    <t>8714530262884</t>
+  </si>
+  <si>
+    <t>8436276375504</t>
+  </si>
+  <si>
+    <t>8703370356846</t>
+  </si>
+  <si>
+    <t>3005243583966</t>
   </si>
   <si>
     <t>900</t>
   </si>
   <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>0647689605</t>
+  </si>
+  <si>
+    <t>0896583550</t>
+  </si>
+  <si>
+    <t>0629536596</t>
+  </si>
+  <si>
+    <t>0361905644</t>
+  </si>
+  <si>
+    <t>0757096815</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>08.07.2023</t>
+  </si>
+  <si>
+    <t>09.09.2023</t>
+  </si>
+  <si>
+    <t>24.02.2026</t>
+  </si>
+  <si>
+    <t>31.01.2023</t>
+  </si>
+  <si>
+    <t>14.07.2023</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>FRT-388911</t>
+  </si>
+  <si>
+    <t>MAT-695675</t>
+  </si>
+  <si>
+    <t>HLB-792328</t>
+  </si>
+  <si>
+    <t>HLB-475239</t>
+  </si>
+  <si>
+    <t>HLB-191307</t>
+  </si>
+  <si>
+    <t>Premium Klep DN50</t>
+  </si>
+  <si>
+    <t>Industrieel Plaat 2mm staal</t>
+  </si>
+  <si>
+    <t>Speciaal Bout M8x40</t>
+  </si>
+  <si>
+    <t>Technisch Buis 100mm</t>
+  </si>
+  <si>
+    <t>Industrieel Reinigingsmiddel</t>
+  </si>
+  <si>
+    <t>002 - Hulpstoffen</t>
+  </si>
+  <si>
+    <t>003 - Verpakkingsmateriaal</t>
+  </si>
+  <si>
+    <t>008 - Reserveonderdelen</t>
+  </si>
+  <si>
+    <t>012 - Chemicaliën</t>
+  </si>
+  <si>
+    <t>ERSA - Reserveonderdeel</t>
+  </si>
+  <si>
+    <t>ROH - Grondstof</t>
+  </si>
+  <si>
+    <t>DIEN - Dienst</t>
+  </si>
+  <si>
+    <t>FERT - Eindproduct</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>0000456370</t>
+  </si>
+  <si>
+    <t>0000114491</t>
+  </si>
+  <si>
+    <t>0000793262</t>
+  </si>
+  <si>
+    <t>0000804348</t>
+  </si>
+  <si>
+    <t>0000349889</t>
+  </si>
+  <si>
+    <t>Troch, Beernaert en Blondeel CommV</t>
+  </si>
+  <si>
+    <t>Rombouts-Borremans CV</t>
+  </si>
+  <si>
+    <t>Bogaert-Dewaele CV</t>
+  </si>
+  <si>
+    <t>Van Dyck BV</t>
+  </si>
+  <si>
+    <t>De Jonghe VOF</t>
+  </si>
+  <si>
+    <t>4585503332</t>
+  </si>
+  <si>
+    <t>4571632517</t>
+  </si>
+  <si>
+    <t>4543894700</t>
+  </si>
+  <si>
+    <t>4537373418</t>
+  </si>
+  <si>
+    <t>4599437834</t>
+  </si>
+  <si>
+    <t>00090</t>
+  </si>
+  <si>
+    <t>00130</t>
+  </si>
+  <si>
+    <t>00040</t>
+  </si>
+  <si>
+    <t>00030</t>
+  </si>
+  <si>
+    <t>00010</t>
+  </si>
+  <si>
+    <t>005 - Inkoop Logistiek</t>
+  </si>
+  <si>
+    <t>003 - Inkoop IT</t>
+  </si>
+  <si>
+    <t>002 - Inkoop Technisch</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2133.10</t>
+  </si>
+  <si>
+    <t>3280.98</t>
+  </si>
+  <si>
+    <t>1606.20</t>
+  </si>
+  <si>
+    <t>2457.16</t>
+  </si>
+  <si>
+    <t>488.77</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>PAL</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>16905.32</t>
+  </si>
+  <si>
+    <t>38336.00</t>
+  </si>
+  <si>
+    <t>2494.12</t>
+  </si>
+  <si>
+    <t>41768.71</t>
+  </si>
+  <si>
+    <t>9727.09</t>
+  </si>
+  <si>
+    <t>5099420758</t>
+  </si>
+  <si>
+    <t>5088688213</t>
+  </si>
+  <si>
+    <t>5047935871</t>
+  </si>
+  <si>
+    <t>5048508373</t>
+  </si>
+  <si>
+    <t>5080951734</t>
+  </si>
+  <si>
+    <t>5121405842</t>
+  </si>
+  <si>
+    <t>5135741672</t>
+  </si>
+  <si>
+    <t>5131912357</t>
+  </si>
+  <si>
+    <t>5131376387</t>
+  </si>
+  <si>
+    <t>5163298053</t>
+  </si>
+  <si>
+    <t>102 - Retour GR PO</t>
+  </si>
+  <si>
+    <t>501 - Goederenontvangst zonder PO</t>
+  </si>
+  <si>
+    <t>651 - Afschrijving</t>
+  </si>
+  <si>
+    <t>301 - Overplaatsing werk-werk</t>
+  </si>
+  <si>
+    <t>B20260023</t>
+  </si>
+  <si>
+    <t>B20252652</t>
+  </si>
+  <si>
+    <t>B20236472</t>
+  </si>
+  <si>
+    <t>B20231452</t>
+  </si>
+  <si>
+    <t>B20243278</t>
+  </si>
+  <si>
+    <t>7920</t>
+  </si>
+  <si>
+    <t>3020</t>
+  </si>
+  <si>
+    <t>7900</t>
+  </si>
+  <si>
+    <t>PD - MRP</t>
+  </si>
+  <si>
+    <t>ND - Geen planning</t>
+  </si>
+  <si>
+    <t>V1 - Automatisch herbestelpunt</t>
+  </si>
+  <si>
+    <t>0000344487</t>
+  </si>
+  <si>
+    <t>0000119744</t>
+  </si>
+  <si>
+    <t>0000336336</t>
+  </si>
+  <si>
+    <t>0000465682</t>
+  </si>
+  <si>
+    <t>0000256339</t>
+  </si>
+  <si>
+    <t>Wouters-Van Gorp CV</t>
+  </si>
+  <si>
+    <t>De Bruyne, De Block en Desmet CV</t>
+  </si>
+  <si>
+    <t>Van Loo, Van den Bergh en Janssens CommV</t>
+  </si>
+  <si>
+    <t>Callebaut, Merckx en Heymans CV</t>
+  </si>
+  <si>
+    <t>Daniels, De Smedt en Geuens VOF</t>
+  </si>
+  <si>
+    <t>0577961108</t>
+  </si>
+  <si>
+    <t>0475338875</t>
+  </si>
+  <si>
+    <t>0526174222</t>
+  </si>
+  <si>
+    <t>0703556658</t>
+  </si>
+  <si>
+    <t>0665428351</t>
+  </si>
+  <si>
+    <t>000300</t>
+  </si>
+  <si>
+    <t>000100</t>
+  </si>
+  <si>
+    <t>000170</t>
+  </si>
+  <si>
+    <t>000290</t>
+  </si>
+  <si>
+    <t>000270</t>
+  </si>
+  <si>
+    <t>50 - Overheid</t>
+  </si>
+  <si>
+    <t>30 - Detailhandel</t>
+  </si>
+  <si>
+    <t>20 - Groothandel</t>
+  </si>
+  <si>
+    <t>03 - Reserveonderdelen</t>
+  </si>
+  <si>
+    <t>02 - Diensten</t>
+  </si>
+  <si>
+    <t>01 - Producten</t>
+  </si>
+  <si>
+    <t>10 - Militair materieel</t>
+  </si>
+  <si>
+    <t>04 - Consulting</t>
+  </si>
+  <si>
+    <t>0004 - Verzendpunt Gent</t>
+  </si>
+  <si>
+    <t>0001 - Verzendpunt Antwerpen</t>
+  </si>
+  <si>
+    <t>8025172501</t>
+  </si>
+  <si>
+    <t>8043903344</t>
+  </si>
+  <si>
+    <t>8017861268</t>
+  </si>
+  <si>
+    <t>8031508085</t>
+  </si>
+  <si>
+    <t>8023986969</t>
+  </si>
+  <si>
+    <t>9053794750</t>
+  </si>
+  <si>
+    <t>9095228447</t>
+  </si>
+  <si>
+    <t>9064263757</t>
+  </si>
+  <si>
+    <t>9017334949</t>
+  </si>
+  <si>
+    <t>9045216053</t>
+  </si>
+  <si>
+    <t>PR00</t>
+  </si>
+  <si>
+    <t>K004</t>
+  </si>
+  <si>
+    <t>K007</t>
+  </si>
+  <si>
+    <t>K005</t>
+  </si>
+  <si>
+    <t>MWST</t>
+  </si>
+  <si>
+    <t>CIF</t>
+  </si>
+  <si>
+    <t>CIP</t>
+  </si>
+  <si>
+    <t>DDP</t>
+  </si>
+  <si>
+    <t>FAS</t>
+  </si>
+  <si>
+    <t>ZB01 - Netto 14 dagen</t>
+  </si>
+  <si>
+    <t>ZB02 - Netto 30 dagen</t>
+  </si>
+  <si>
+    <t>ZB04 - 2% 10d, netto 30d</t>
+  </si>
+  <si>
+    <t>04 - Particulier</t>
+  </si>
+  <si>
+    <t>03 - Overheid</t>
+  </si>
+  <si>
+    <t>06 - Defensie</t>
+  </si>
+  <si>
+    <t>BE01 - Vlaanderen</t>
+  </si>
+  <si>
+    <t>BE02 - Wallonië</t>
+  </si>
+  <si>
+    <t>NL01 - Randstad</t>
+  </si>
+  <si>
+    <t>140000</t>
+  </si>
+  <si>
+    <t>160000</t>
+  </si>
+  <si>
+    <t>510000</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>Uitzonderlijke kosten</t>
+  </si>
+  <si>
+    <t>Opbrengsten verkoop</t>
+  </si>
+  <si>
+    <t>Overige kosten</t>
+  </si>
+  <si>
+    <t>Vorderingen op klanten</t>
+  </si>
+  <si>
+    <t>Kas</t>
+  </si>
+  <si>
+    <t>3100 - Marketing</t>
+  </si>
+  <si>
+    <t>1300 - IT</t>
+  </si>
+  <si>
+    <t>4000 - R&amp;D</t>
+  </si>
+  <si>
+    <t>3000 - Verkoop</t>
+  </si>
+  <si>
+    <t>PC4787</t>
+  </si>
+  <si>
+    <t>PC2618</t>
+  </si>
+  <si>
+    <t>PC3205</t>
+  </si>
+  <si>
+    <t>PC4393</t>
+  </si>
+  <si>
+    <t>PC9014</t>
+  </si>
+  <si>
+    <t>SA - Grootboekdocument</t>
+  </si>
+  <si>
+    <t>KG - Leverancierscreditnota</t>
+  </si>
+  <si>
+    <t>DG - Klantcreditnota</t>
+  </si>
+  <si>
+    <t>S - Debet</t>
+  </si>
+  <si>
+    <t>H - Credit</t>
+  </si>
+  <si>
+    <t>143442.46</t>
+  </si>
+  <si>
+    <t>26462.19</t>
+  </si>
+  <si>
+    <t>17736.90</t>
+  </si>
+  <si>
+    <t>90242.10</t>
+  </si>
+  <si>
+    <t>282104.89</t>
+  </si>
+  <si>
+    <t>V5 - 21% BTW verlegging</t>
+  </si>
+  <si>
+    <t>V3 - 21% BTW</t>
+  </si>
+  <si>
+    <t>VX - BTW intracommunautair</t>
+  </si>
+  <si>
+    <t>0804648420</t>
+  </si>
+  <si>
+    <t>0904976700</t>
+  </si>
+  <si>
+    <t>0539354509</t>
+  </si>
+  <si>
+    <t>1000 - Operations</t>
+  </si>
+  <si>
+    <t>3000 - Defensie</t>
+  </si>
+  <si>
+    <t>2000 - Support</t>
+  </si>
+  <si>
+    <t>849648</t>
+  </si>
+  <si>
+    <t>887529</t>
+  </si>
+  <si>
+    <t>801793</t>
+  </si>
+  <si>
+    <t>864780</t>
+  </si>
+  <si>
+    <t>839440</t>
+  </si>
+  <si>
+    <t>420000 - Loonkosten</t>
+  </si>
+  <si>
+    <t>440000 - Overige kosten</t>
+  </si>
+  <si>
+    <t>410000 - Externe diensten</t>
+  </si>
+  <si>
+    <t>1420 - Manuren</t>
+  </si>
+  <si>
+    <t>1440 - Setup-uren</t>
+  </si>
+  <si>
+    <t>1430 - Reparatie-uren</t>
+  </si>
+  <si>
+    <t>1410 - Machineuren</t>
+  </si>
+  <si>
+    <t>P-9637.4.09</t>
+  </si>
+  <si>
+    <t>P-8862.1.05</t>
+  </si>
+  <si>
+    <t>P-1983.4.04</t>
+  </si>
+  <si>
+    <t>P-3329.3.08</t>
+  </si>
+  <si>
+    <t>P-4804.4.09</t>
+  </si>
+  <si>
+    <t>00082005</t>
+  </si>
+  <si>
+    <t>00081261</t>
+  </si>
+  <si>
+    <t>00032047</t>
+  </si>
+  <si>
+    <t>00041845</t>
+  </si>
+  <si>
+    <t>00010604</t>
+  </si>
+  <si>
+    <t>BE10 - België Brussel</t>
+  </si>
+  <si>
+    <t>NL10 - Nederland</t>
+  </si>
+  <si>
+    <t>BE30 - België Luik</t>
+  </si>
+  <si>
+    <t>0003 - Magazijn</t>
+  </si>
+  <si>
+    <t>0004 - Productie</t>
+  </si>
+  <si>
+    <t>0001 - Hoofdkantoor</t>
+  </si>
+  <si>
+    <t>4 - Extern</t>
+  </si>
+  <si>
+    <t>1 - Actief</t>
+  </si>
+  <si>
+    <t>2 - Gepensioneerd</t>
+  </si>
+  <si>
+    <t>5 - Stagiair</t>
+  </si>
+  <si>
+    <t>02 - Deeltijds onbepaalde duur</t>
+  </si>
+  <si>
+    <t>05 - Interimkracht</t>
+  </si>
+  <si>
+    <t>01 - Voltijds onbepaalde duur</t>
+  </si>
+  <si>
+    <t>03 - Voltijds bepaalde duur</t>
+  </si>
+  <si>
+    <t>58180089</t>
+  </si>
+  <si>
+    <t>50891639</t>
+  </si>
+  <si>
+    <t>58159674</t>
+  </si>
+  <si>
+    <t>58313102</t>
+  </si>
+  <si>
+    <t>54047783</t>
+  </si>
+  <si>
+    <t>50000008 - Analist</t>
+  </si>
+  <si>
+    <t>50000003 - Senior Specialist</t>
+  </si>
+  <si>
+    <t>50000002 - Teamleider</t>
+  </si>
+  <si>
+    <t>50000005 - Junior Medewerker</t>
+  </si>
+  <si>
+    <t>50000002 - Ingenieur</t>
+  </si>
+  <si>
+    <t>50000004 - Administratief</t>
+  </si>
+  <si>
+    <t>50000007 - Operator</t>
+  </si>
+  <si>
+    <t>50000006 - Analist</t>
+  </si>
+  <si>
+    <t>B1 - Maandelijks bedienden</t>
+  </si>
+  <si>
+    <t>W1 - Tweewekelijks</t>
+  </si>
+  <si>
+    <t>01 - Standaard</t>
+  </si>
+  <si>
+    <t>B2 - Maandelijks arbeiders</t>
+  </si>
+  <si>
+    <t>3100 - Verplaatsingsvergoeding</t>
+  </si>
+  <si>
+    <t>2000 - Eindejaarspremie</t>
+  </si>
+  <si>
+    <t>1300 - Weekendpremie</t>
+  </si>
+  <si>
+    <t>1400 - Gevarentoelage</t>
+  </si>
+  <si>
+    <t>0007 - Geplande werktijd</t>
+  </si>
+  <si>
+    <t>2001 - Afwezigheden</t>
+  </si>
+  <si>
+    <t>0015 - Aanvullende betalingen</t>
+  </si>
+  <si>
+    <t>0014 - Periodieke betalingen/inhoudingen</t>
+  </si>
+  <si>
+    <t>0009 - Bankgegevens</t>
+  </si>
+  <si>
+    <t>6054538280</t>
+  </si>
+  <si>
+    <t>6048910321</t>
+  </si>
+  <si>
+    <t>6016189595</t>
+  </si>
+  <si>
+    <t>6089495570</t>
+  </si>
+  <si>
+    <t>6068879739</t>
+  </si>
+  <si>
+    <t>31938879</t>
+  </si>
+  <si>
+    <t>57448551</t>
+  </si>
+  <si>
+    <t>27271838</t>
+  </si>
+  <si>
+    <t>42178609</t>
+  </si>
+  <si>
+    <t>27048757</t>
+  </si>
+  <si>
+    <t>02734365</t>
+  </si>
+  <si>
+    <t>06619798</t>
+  </si>
+  <si>
+    <t>03469962</t>
+  </si>
+  <si>
+    <t>01282378</t>
+  </si>
+  <si>
+    <t>05250120</t>
+  </si>
+  <si>
+    <t>QC-01 - Kwaliteitscontrole 1</t>
+  </si>
+  <si>
+    <t>MC-01 - CNC Freesmachine 1</t>
+  </si>
+  <si>
+    <t>AS-01 - Assemblagelijn 1</t>
+  </si>
+  <si>
+    <t>PK-01 - Verpakkingslijn 1</t>
+  </si>
+  <si>
+    <t>MC-02 - CNC Draaibank 2</t>
+  </si>
+  <si>
+    <t>0065091067</t>
+  </si>
+  <si>
+    <t>0062956010</t>
+  </si>
+  <si>
+    <t>0044837444</t>
+  </si>
+  <si>
+    <t>0050608758</t>
+  </si>
+  <si>
+    <t>0035897872</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>0052054376</t>
+  </si>
+  <si>
+    <t>0042654991</t>
+  </si>
+  <si>
+    <t>0034065742</t>
+  </si>
+  <si>
+    <t>0083924734</t>
+  </si>
+  <si>
+    <t>0080172445</t>
+  </si>
+  <si>
+    <t>ANT-05-04-024</t>
+  </si>
+  <si>
+    <t>BRU-02-04-049</t>
+  </si>
+  <si>
+    <t>LIE-06-00-049</t>
+  </si>
+  <si>
+    <t>LIE-09-04-007</t>
+  </si>
+  <si>
+    <t>GNT-04-04-007</t>
+  </si>
+  <si>
+    <t>4097919143</t>
+  </si>
+  <si>
+    <t>4057756913</t>
+  </si>
+  <si>
+    <t>4065875852</t>
+  </si>
+  <si>
+    <t>4018563774</t>
+  </si>
+  <si>
+    <t>4024627010</t>
+  </si>
+  <si>
+    <t>1094797191</t>
+  </si>
+  <si>
+    <t>1032081886</t>
+  </si>
+  <si>
+    <t>1024553854</t>
+  </si>
+  <si>
+    <t>1057938679</t>
+  </si>
+  <si>
+    <t>1084734742</t>
+  </si>
+  <si>
+    <t>MP330774</t>
+  </si>
+  <si>
+    <t>MP522716</t>
+  </si>
+  <si>
+    <t>MP186809</t>
+  </si>
+  <si>
+    <t>MP158174</t>
+  </si>
+  <si>
+    <t>MP388735</t>
+  </si>
+  <si>
+    <t>IFLO - Functionele locatie</t>
+  </si>
+  <si>
+    <t>IFLOT - Technische plaats</t>
+  </si>
+  <si>
+    <t>EQUI - Equipment technisch</t>
+  </si>
+  <si>
+    <t>000892851689</t>
+  </si>
+  <si>
+    <t>000298550942</t>
+  </si>
+  <si>
+    <t>000189082374</t>
+  </si>
+  <si>
+    <t>000773484716</t>
+  </si>
+  <si>
+    <t>000552770892</t>
+  </si>
+  <si>
+    <t>IP-94413</t>
+  </si>
+  <si>
+    <t>IP-48201</t>
+  </si>
+  <si>
+    <t>IP-84858</t>
+  </si>
+  <si>
+    <t>IP-67187</t>
+  </si>
+  <si>
+    <t>IP-81316</t>
+  </si>
+  <si>
+    <t>9 - Kenmerken</t>
+  </si>
+  <si>
+    <t>5 - Activiteiten</t>
+  </si>
+  <si>
+    <t>3 - Maatregelen</t>
+  </si>
+  <si>
+    <t>R - Afgekeurd</t>
+  </si>
+  <si>
+    <t>A2 - Aanvaard na herbewerking</t>
+  </si>
+  <si>
+    <t>A - Aanvaard</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>0714989541</t>
-  </si>
-  <si>
-    <t>0678758192</t>
-  </si>
-  <si>
-    <t>0177050753</t>
-  </si>
-  <si>
-    <t>0845306284</t>
-  </si>
-  <si>
-    <t>0102036950</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>13.04.2024</t>
-  </si>
-  <si>
-    <t>12.10.2024</t>
-  </si>
-  <si>
-    <t>22.06.2023</t>
-  </si>
-  <si>
-    <t>02.03.2024</t>
-  </si>
-  <si>
-    <t>24.10.2024</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>SEK</t>
-  </si>
-  <si>
-    <t>DKK</t>
-  </si>
-  <si>
-    <t>CZK</t>
-  </si>
-  <si>
-    <t>FR</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>NL</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>ERS-561408</t>
-  </si>
-  <si>
-    <t>ERS-824946</t>
-  </si>
-  <si>
-    <t>ERS-441384</t>
-  </si>
-  <si>
-    <t>ERS-220351</t>
-  </si>
-  <si>
-    <t>ERS-481526</t>
-  </si>
-  <si>
-    <t>Standaard Smeermiddel</t>
-  </si>
-  <si>
-    <t>Speciaal Bout M8x40</t>
-  </si>
-  <si>
-    <t>Premium Kabel 3x2.5mm</t>
-  </si>
-  <si>
-    <t>Premium Buis 100mm</t>
-  </si>
-  <si>
-    <t>Premium Pomp onderdeel</t>
-  </si>
-  <si>
-    <t>008 - Reserveonderdelen</t>
-  </si>
-  <si>
-    <t>011 - Voeding</t>
-  </si>
-  <si>
-    <t>003 - Verpakkingsmateriaal</t>
-  </si>
-  <si>
-    <t>ERSA - Reserveonderdeel</t>
-  </si>
-  <si>
-    <t>DIEN - Dienst</t>
-  </si>
-  <si>
-    <t>NLAG - Niet-voorraad</t>
-  </si>
-  <si>
-    <t>VERP - Verpakking</t>
-  </si>
-  <si>
-    <t>HALB - Halffabricaat</t>
-  </si>
-  <si>
-    <t>0001</t>
-  </si>
-  <si>
-    <t>0002</t>
-  </si>
-  <si>
-    <t>0003</t>
-  </si>
-  <si>
-    <t>0000545407</t>
-  </si>
-  <si>
-    <t>0000173011</t>
-  </si>
-  <si>
-    <t>0000492742</t>
-  </si>
-  <si>
-    <t>0000753313</t>
-  </si>
-  <si>
-    <t>0000322947</t>
-  </si>
-  <si>
-    <t>Engels CommV</t>
-  </si>
-  <si>
-    <t>Vos CV</t>
-  </si>
-  <si>
-    <t>De Backer-Meert CommV</t>
-  </si>
-  <si>
-    <t>Celis-Van den Broeck VOF</t>
-  </si>
-  <si>
-    <t>Wouters, Geens en Lemmens VOF</t>
-  </si>
-  <si>
-    <t>4589996201</t>
-  </si>
-  <si>
-    <t>4528360276</t>
-  </si>
-  <si>
-    <t>4599591037</t>
-  </si>
-  <si>
-    <t>4547788505</t>
-  </si>
-  <si>
-    <t>4546332966</t>
-  </si>
-  <si>
-    <t>00080</t>
-  </si>
-  <si>
-    <t>00110</t>
-  </si>
-  <si>
-    <t>00050</t>
-  </si>
-  <si>
-    <t>00030</t>
-  </si>
-  <si>
-    <t>003 - Inkoop IT</t>
-  </si>
-  <si>
-    <t>001 - Inkoop Algemeen</t>
-  </si>
-  <si>
-    <t>005 - Inkoop Logistiek</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>3802.58</t>
-  </si>
-  <si>
-    <t>4026.27</t>
-  </si>
-  <si>
-    <t>3935.82</t>
-  </si>
-  <si>
-    <t>2187.46</t>
-  </si>
-  <si>
-    <t>3228.14</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>KM</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>SET</t>
-  </si>
-  <si>
-    <t>32798.49</t>
-  </si>
-  <si>
-    <t>49834.17</t>
-  </si>
-  <si>
-    <t>48234.91</t>
-  </si>
-  <si>
-    <t>4837.11</t>
-  </si>
-  <si>
-    <t>37989.42</t>
-  </si>
-  <si>
-    <t>5095159875</t>
-  </si>
-  <si>
-    <t>5099632284</t>
-  </si>
-  <si>
-    <t>5049026632</t>
-  </si>
-  <si>
-    <t>5065111193</t>
-  </si>
-  <si>
-    <t>5061261973</t>
-  </si>
-  <si>
-    <t>5167274904</t>
-  </si>
-  <si>
-    <t>5150650913</t>
-  </si>
-  <si>
-    <t>5112103555</t>
-  </si>
-  <si>
-    <t>5110946381</t>
-  </si>
-  <si>
-    <t>5112036445</t>
-  </si>
-  <si>
-    <t>601 - Goederenuitgifte levering</t>
-  </si>
-  <si>
-    <t>262 - Retour verbruik PO</t>
-  </si>
-  <si>
-    <t>202 - Retour verbruik</t>
-  </si>
-  <si>
-    <t>501 - Goederenontvangst zonder PO</t>
-  </si>
-  <si>
-    <t>B20252086</t>
-  </si>
-  <si>
-    <t>B20233708</t>
-  </si>
-  <si>
-    <t>B20264717</t>
-  </si>
-  <si>
-    <t>B20235431</t>
-  </si>
-  <si>
-    <t>B20232066</t>
-  </si>
-  <si>
-    <t>7900</t>
-  </si>
-  <si>
-    <t>3010</t>
-  </si>
-  <si>
-    <t>3020</t>
-  </si>
-  <si>
-    <t>PD - MRP</t>
-  </si>
-  <si>
-    <t>ND - Geen planning</t>
-  </si>
-  <si>
-    <t>V1 - Automatisch herbestelpunt</t>
-  </si>
-  <si>
-    <t>VV - Handmatig</t>
-  </si>
-  <si>
-    <t>0000409448</t>
-  </si>
-  <si>
-    <t>0000473528</t>
-  </si>
-  <si>
-    <t>0000874439</t>
-  </si>
-  <si>
-    <t>0000606961</t>
-  </si>
-  <si>
-    <t>0000330613</t>
-  </si>
-  <si>
-    <t>De Leeuw-Pattyn VOF</t>
-  </si>
-  <si>
-    <t>Van den Eynde, De Vos en Goossens CV</t>
-  </si>
-  <si>
-    <t>Boonen-Declercq NV</t>
-  </si>
-  <si>
-    <t>Vandenberghe, Lemmens en Coenen NV</t>
-  </si>
-  <si>
-    <t>Verelst, Christiaens en Geens NV</t>
-  </si>
-  <si>
-    <t>0344844578</t>
-  </si>
-  <si>
-    <t>0679081376</t>
-  </si>
-  <si>
-    <t>0927347083</t>
-  </si>
-  <si>
-    <t>0409268135</t>
-  </si>
-  <si>
-    <t>0683700708</t>
-  </si>
-  <si>
-    <t>000300</t>
-  </si>
-  <si>
-    <t>000080</t>
-  </si>
-  <si>
-    <t>000040</t>
-  </si>
-  <si>
-    <t>000130</t>
-  </si>
-  <si>
-    <t>000250</t>
-  </si>
-  <si>
-    <t>50 - Overheid</t>
-  </si>
-  <si>
-    <t>30 - Detailhandel</t>
-  </si>
-  <si>
-    <t>10 - Directe verkoop</t>
-  </si>
-  <si>
-    <t>20 - Groothandel</t>
-  </si>
-  <si>
-    <t>10 - Militair materieel</t>
-  </si>
-  <si>
-    <t>02 - Diensten</t>
-  </si>
-  <si>
-    <t>01 - Producten</t>
-  </si>
-  <si>
-    <t>0003 - Verzendpunt Luik</t>
-  </si>
-  <si>
-    <t>0004 - Verzendpunt Gent</t>
-  </si>
-  <si>
-    <t>8047434344</t>
-  </si>
-  <si>
-    <t>8060302317</t>
-  </si>
-  <si>
-    <t>8084124679</t>
-  </si>
-  <si>
-    <t>8055452713</t>
-  </si>
-  <si>
-    <t>8068391512</t>
-  </si>
-  <si>
-    <t>9047859961</t>
-  </si>
-  <si>
-    <t>9030671018</t>
-  </si>
-  <si>
-    <t>9059676154</t>
-  </si>
-  <si>
-    <t>9014145963</t>
-  </si>
-  <si>
-    <t>9072092269</t>
-  </si>
-  <si>
-    <t>RB00</t>
-  </si>
-  <si>
-    <t>MWST</t>
-  </si>
-  <si>
-    <t>KA00</t>
-  </si>
-  <si>
-    <t>PR00</t>
-  </si>
-  <si>
-    <t>K007</t>
-  </si>
-  <si>
-    <t>CFR</t>
-  </si>
-  <si>
-    <t>FCA</t>
-  </si>
-  <si>
-    <t>ZB02 - Netto 30 dagen</t>
-  </si>
-  <si>
-    <t>ZB06 - Netto 45 dagen</t>
-  </si>
-  <si>
-    <t>ZB01 - Netto 14 dagen</t>
-  </si>
-  <si>
-    <t>01 - Industrie</t>
-  </si>
-  <si>
-    <t>05 - Non-profit</t>
-  </si>
-  <si>
-    <t>06 - Defensie</t>
-  </si>
-  <si>
-    <t>04 - Particulier</t>
-  </si>
-  <si>
-    <t>DE01 - West</t>
-  </si>
-  <si>
-    <t>BE03 - Brussel</t>
-  </si>
-  <si>
-    <t>NL01 - Randstad</t>
-  </si>
-  <si>
-    <t>BE02 - Wallonië</t>
-  </si>
-  <si>
-    <t>160000</t>
-  </si>
-  <si>
-    <t>610000</t>
-  </si>
-  <si>
-    <t>113100</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>700000</t>
-  </si>
-  <si>
-    <t>Overige kosten</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>Financiële opbrengsten</t>
-  </si>
-  <si>
-    <t>Verzekeringskosten</t>
-  </si>
-  <si>
-    <t>Crediteuren</t>
-  </si>
-  <si>
-    <t>2100 - Kwaliteit</t>
-  </si>
-  <si>
-    <t>1300 - IT</t>
-  </si>
-  <si>
-    <t>2000 - Productie</t>
-  </si>
-  <si>
-    <t>5000 - Onderhoud</t>
-  </si>
-  <si>
-    <t>PC4181</t>
-  </si>
-  <si>
-    <t>PC3017</t>
-  </si>
-  <si>
-    <t>PC2217</t>
-  </si>
-  <si>
-    <t>PC8560</t>
-  </si>
-  <si>
-    <t>PC2883</t>
-  </si>
-  <si>
-    <t>SA - Grootboekdocument</t>
-  </si>
-  <si>
-    <t>KG - Leverancierscreditnota</t>
-  </si>
-  <si>
-    <t>AB - Boekhoudkundig document</t>
-  </si>
-  <si>
-    <t>DA - Klantdocument</t>
-  </si>
-  <si>
-    <t>S - Debet</t>
-  </si>
-  <si>
-    <t>H - Credit</t>
-  </si>
-  <si>
-    <t>82424.40</t>
-  </si>
-  <si>
-    <t>447466.15</t>
-  </si>
-  <si>
-    <t>6312.89</t>
-  </si>
-  <si>
-    <t>428043.88</t>
-  </si>
-  <si>
-    <t>196774.48</t>
-  </si>
-  <si>
-    <t>V2 - 12% BTW</t>
-  </si>
-  <si>
-    <t>V4 - 0% Export</t>
-  </si>
-  <si>
-    <t>VX - BTW intracommunautair</t>
-  </si>
-  <si>
-    <t>V0 - 0% BTW binnenland</t>
-  </si>
-  <si>
-    <t>V1 - 6% BTW</t>
-  </si>
-  <si>
-    <t>0956526198</t>
-  </si>
-  <si>
-    <t>0814421981</t>
-  </si>
-  <si>
-    <t>0976703903</t>
-  </si>
-  <si>
-    <t>0738999206</t>
-  </si>
-  <si>
-    <t>0684521612</t>
-  </si>
-  <si>
-    <t>1000 - Operations</t>
-  </si>
-  <si>
-    <t>2000 - Support</t>
-  </si>
-  <si>
-    <t>3000 - Defensie</t>
-  </si>
-  <si>
-    <t>887109</t>
-  </si>
-  <si>
-    <t>845417</t>
-  </si>
-  <si>
-    <t>874062</t>
-  </si>
-  <si>
-    <t>889589</t>
-  </si>
-  <si>
-    <t>874637</t>
-  </si>
-  <si>
-    <t>430000 - Afschrijvingen</t>
-  </si>
-  <si>
-    <t>420000 - Loonkosten</t>
-  </si>
-  <si>
-    <t>410000 - Externe diensten</t>
-  </si>
-  <si>
-    <t>440000 - Overige kosten</t>
-  </si>
-  <si>
-    <t>1440 - Setup-uren</t>
-  </si>
-  <si>
-    <t>1410 - Machineuren</t>
-  </si>
-  <si>
-    <t>P-9084.3.03</t>
-  </si>
-  <si>
-    <t>P-7455.2.02</t>
-  </si>
-  <si>
-    <t>P-5656.2.01</t>
-  </si>
-  <si>
-    <t>P-2692.4.10</t>
-  </si>
-  <si>
-    <t>P-6561.4.01</t>
-  </si>
-  <si>
-    <t>00015189</t>
-  </si>
-  <si>
-    <t>00029332</t>
-  </si>
-  <si>
-    <t>00011796</t>
-  </si>
-  <si>
-    <t>00082883</t>
-  </si>
-  <si>
-    <t>00071255</t>
-  </si>
-  <si>
-    <t>BE30 - België Luik</t>
-  </si>
-  <si>
-    <t>NL10 - Nederland</t>
-  </si>
-  <si>
-    <t>BE10 - België Brussel</t>
-  </si>
-  <si>
-    <t>0004 - Productie</t>
-  </si>
-  <si>
-    <t>0003 - Magazijn</t>
-  </si>
-  <si>
-    <t>0001 - Hoofdkantoor</t>
-  </si>
-  <si>
-    <t>0002 - Filiaal</t>
-  </si>
-  <si>
-    <t>3 - Tijdelijk</t>
-  </si>
-  <si>
-    <t>4 - Extern</t>
-  </si>
-  <si>
-    <t>1 - Actief</t>
-  </si>
-  <si>
-    <t>2 - Gepensioneerd</t>
-  </si>
-  <si>
-    <t>5 - Stagiair</t>
-  </si>
-  <si>
-    <t>01 - Voltijds onbepaalde duur</t>
-  </si>
-  <si>
-    <t>06 - Freelancer</t>
-  </si>
-  <si>
-    <t>04 - Deeltijds bepaalde duur</t>
-  </si>
-  <si>
-    <t>52784348</t>
-  </si>
-  <si>
-    <t>58179814</t>
-  </si>
-  <si>
-    <t>58356497</t>
-  </si>
-  <si>
-    <t>52810450</t>
-  </si>
-  <si>
-    <t>59922617</t>
-  </si>
-  <si>
-    <t>50000001 - Manager Afdeling</t>
-  </si>
-  <si>
-    <t>50000007 - Projectleider</t>
-  </si>
-  <si>
-    <t>50000003 - Senior Specialist</t>
-  </si>
-  <si>
-    <t>50000008 - Analist</t>
-  </si>
-  <si>
-    <t>50000001 - Manager</t>
-  </si>
-  <si>
-    <t>50000007 - Operator</t>
-  </si>
-  <si>
-    <t>50000006 - Analist</t>
-  </si>
-  <si>
-    <t>W1 - Tweewekelijks</t>
-  </si>
-  <si>
-    <t>B2 - Maandelijks arbeiders</t>
-  </si>
-  <si>
-    <t>B1 - Maandelijks bedienden</t>
-  </si>
-  <si>
-    <t>01 - Standaard</t>
-  </si>
-  <si>
-    <t>3000 - Kilometervergoeding</t>
-  </si>
-  <si>
-    <t>1000 - Basisloon</t>
-  </si>
-  <si>
-    <t>2000 - Eindejaarspremie</t>
-  </si>
-  <si>
-    <t>1300 - Weekendpremie</t>
-  </si>
-  <si>
-    <t>0002 - Persoonlijke gegevens</t>
-  </si>
-  <si>
-    <t>0009 - Bankgegevens</t>
-  </si>
-  <si>
-    <t>2006 - Afwezigheidsquota</t>
-  </si>
-  <si>
-    <t>0000 - Maatregelen</t>
-  </si>
-  <si>
-    <t>0021 - Familie/personen</t>
-  </si>
-  <si>
-    <t>6092944349</t>
-  </si>
-  <si>
-    <t>6088632486</t>
-  </si>
-  <si>
-    <t>6063810481</t>
-  </si>
-  <si>
-    <t>6085392086</t>
-  </si>
-  <si>
-    <t>6079399672</t>
-  </si>
-  <si>
-    <t>19766550</t>
-  </si>
-  <si>
-    <t>24493079</t>
-  </si>
-  <si>
-    <t>73257755</t>
-  </si>
-  <si>
-    <t>52175078</t>
-  </si>
-  <si>
-    <t>86814497</t>
-  </si>
-  <si>
-    <t>05936464</t>
-  </si>
-  <si>
-    <t>09159331</t>
-  </si>
-  <si>
-    <t>01342946</t>
-  </si>
-  <si>
-    <t>03129210</t>
-  </si>
-  <si>
-    <t>08857665</t>
-  </si>
-  <si>
-    <t>MC-01 - CNC Freesmachine 1</t>
-  </si>
-  <si>
-    <t>PK-01 - Verpakkingslijn 1</t>
-  </si>
-  <si>
-    <t>WD-01 - Laslijn 1</t>
-  </si>
-  <si>
-    <t>QC-01 - Kwaliteitscontrole 1</t>
-  </si>
-  <si>
-    <t>0083946541</t>
-  </si>
-  <si>
-    <t>0084873555</t>
-  </si>
-  <si>
-    <t>0085093629</t>
-  </si>
-  <si>
-    <t>0092743390</t>
-  </si>
-  <si>
-    <t>0096804484</t>
-  </si>
-  <si>
-    <t>0005</t>
-  </si>
-  <si>
-    <t>0004</t>
-  </si>
-  <si>
-    <t>0051083652</t>
-  </si>
-  <si>
-    <t>0086144739</t>
-  </si>
-  <si>
-    <t>0014300859</t>
-  </si>
-  <si>
-    <t>0094853278</t>
-  </si>
-  <si>
-    <t>0039545714</t>
-  </si>
-  <si>
-    <t>BRU-02-03-049</t>
-  </si>
-  <si>
-    <t>BRU-07-01-046</t>
-  </si>
-  <si>
-    <t>LIE-01-01-028</t>
-  </si>
-  <si>
-    <t>GNT-05-05-025</t>
-  </si>
-  <si>
-    <t>BRU-10-03-033</t>
-  </si>
-  <si>
-    <t>4092115959</t>
-  </si>
-  <si>
-    <t>4095234010</t>
-  </si>
-  <si>
-    <t>4083725622</t>
-  </si>
-  <si>
-    <t>4098037877</t>
-  </si>
-  <si>
-    <t>4046402521</t>
-  </si>
-  <si>
-    <t>1013628382</t>
-  </si>
-  <si>
-    <t>1027061810</t>
-  </si>
-  <si>
-    <t>1069587581</t>
-  </si>
-  <si>
-    <t>1012121910</t>
-  </si>
-  <si>
-    <t>1037250428</t>
-  </si>
-  <si>
-    <t>MP686831</t>
-  </si>
-  <si>
-    <t>MP352739</t>
-  </si>
-  <si>
-    <t>MP427680</t>
-  </si>
-  <si>
-    <t>MP437991</t>
-  </si>
-  <si>
-    <t>MP597868</t>
-  </si>
-  <si>
-    <t>IFLOT - Technische plaats</t>
-  </si>
-  <si>
-    <t>IFLO - Functionele locatie</t>
-  </si>
-  <si>
-    <t>EQKT - Equipment</t>
-  </si>
-  <si>
-    <t>000741785600</t>
-  </si>
-  <si>
-    <t>000237384685</t>
-  </si>
-  <si>
-    <t>000609644505</t>
-  </si>
-  <si>
-    <t>000409446421</t>
-  </si>
-  <si>
-    <t>000523920659</t>
-  </si>
-  <si>
-    <t>IP-37770</t>
-  </si>
-  <si>
-    <t>IP-51246</t>
-  </si>
-  <si>
-    <t>IP-68254</t>
-  </si>
-  <si>
-    <t>IP-20346</t>
-  </si>
-  <si>
-    <t>IP-94295</t>
-  </si>
-  <si>
-    <t>3 - Maatregelen</t>
-  </si>
-  <si>
-    <t>9 - Kenmerken</t>
-  </si>
-  <si>
-    <t>1 - Foutsoorten</t>
-  </si>
-  <si>
-    <t>2 - Foutoorzaken</t>
-  </si>
-  <si>
-    <t>R - Afgekeurd</t>
-  </si>
-  <si>
-    <t>A1 - Aanvaard met beperkingen</t>
-  </si>
-  <si>
-    <t>A2 - Aanvaard na herbewerking</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>500</t>
+    <t>002 - Vloeropslagplaats</t>
   </si>
   <si>
     <t>001 - Hoogbouwmagazijn</t>
   </si>
   <si>
-    <t>004 - Koelmagazijn</t>
-  </si>
-  <si>
-    <t>002 - Vloeropslagplaats</t>
-  </si>
-  <si>
-    <t>H-07-06</t>
-  </si>
-  <si>
-    <t>C-16-06</t>
-  </si>
-  <si>
-    <t>G-09-01</t>
-  </si>
-  <si>
-    <t>D-40-01</t>
-  </si>
-  <si>
-    <t>A-27-06</t>
-  </si>
-  <si>
-    <t>0000396340</t>
-  </si>
-  <si>
-    <t>0000253816</t>
-  </si>
-  <si>
-    <t>0000862148</t>
-  </si>
-  <si>
-    <t>0000854765</t>
-  </si>
-  <si>
-    <t>0000192363</t>
-  </si>
-  <si>
-    <t>HU79747974</t>
-  </si>
-  <si>
-    <t>HU20191173</t>
-  </si>
-  <si>
-    <t>HU88106293</t>
-  </si>
-  <si>
-    <t>HU49393255</t>
-  </si>
-  <si>
-    <t>HU90099324</t>
+    <t>003 - Stellingopslag</t>
+  </si>
+  <si>
+    <t>010 - Goederenontvangst</t>
+  </si>
+  <si>
+    <t>F-42-06</t>
+  </si>
+  <si>
+    <t>C-14-05</t>
+  </si>
+  <si>
+    <t>H-24-02</t>
+  </si>
+  <si>
+    <t>B-14-01</t>
+  </si>
+  <si>
+    <t>A-32-02</t>
+  </si>
+  <si>
+    <t>0000721034</t>
+  </si>
+  <si>
+    <t>0000840798</t>
+  </si>
+  <si>
+    <t>0000464181</t>
+  </si>
+  <si>
+    <t>0000681635</t>
+  </si>
+  <si>
+    <t>0000627319</t>
+  </si>
+  <si>
+    <t>HU97348974</t>
+  </si>
+  <si>
+    <t>HU77389251</t>
+  </si>
+  <si>
+    <t>HU91602429</t>
+  </si>
+  <si>
+    <t>HU60237979</t>
+  </si>
+  <si>
+    <t>HU18109580</t>
+  </si>
+  <si>
+    <t>DC_ANT_01</t>
   </si>
   <si>
     <t>DC_BRU_01</t>
   </si>
   <si>
+    <t>LOC_GNT_01</t>
+  </si>
+  <si>
     <t>LOC_ANT_01</t>
   </si>
   <si>
-    <t>LOC_AMS_01</t>
-  </si>
-  <si>
-    <t>DC_ANT_01</t>
-  </si>
-  <si>
-    <t>SCM-520713</t>
-  </si>
-  <si>
-    <t>SCM-803293</t>
-  </si>
-  <si>
-    <t>SCM-926399</t>
-  </si>
-  <si>
-    <t>SCM-549030</t>
-  </si>
-  <si>
-    <t>SCM-504080</t>
-  </si>
-  <si>
-    <t>DP-2024-10</t>
-  </si>
-  <si>
-    <t>DP-2025-05</t>
-  </si>
-  <si>
-    <t>DP-2025-07</t>
-  </si>
-  <si>
-    <t>DP-2024-02</t>
-  </si>
-  <si>
-    <t>DP-2024-05</t>
-  </si>
-  <si>
-    <t>FRA -&gt; PAR</t>
-  </si>
-  <si>
-    <t>FRA -&gt; ROT</t>
+    <t>SCM-906071</t>
+  </si>
+  <si>
+    <t>SCM-577824</t>
+  </si>
+  <si>
+    <t>SCM-596711</t>
+  </si>
+  <si>
+    <t>SCM-479296</t>
+  </si>
+  <si>
+    <t>SCM-884536</t>
+  </si>
+  <si>
+    <t>DP-2025-11</t>
+  </si>
+  <si>
+    <t>DP-2026-11</t>
+  </si>
+  <si>
+    <t>DP-2024-01</t>
+  </si>
+  <si>
+    <t>DP-2026-01</t>
+  </si>
+  <si>
+    <t>DP-2025-03</t>
+  </si>
+  <si>
+    <t>FRA -&gt; ANT</t>
+  </si>
+  <si>
+    <t>LIE -&gt; ROT</t>
   </si>
   <si>
     <t>ROT -&gt; AMS</t>
   </si>
   <si>
-    <t>ANT -&gt; BRU</t>
-  </si>
-  <si>
-    <t>LIE -&gt; LON</t>
-  </si>
-  <si>
-    <t>Vendor 0000891609</t>
-  </si>
-  <si>
-    <t>Vendor 0000142571</t>
-  </si>
-  <si>
-    <t>Vendor 0000832559</t>
-  </si>
-  <si>
-    <t>Vendor 0000838703</t>
-  </si>
-  <si>
-    <t>Vendor 0000955309</t>
-  </si>
-  <si>
-    <t>QA-7878</t>
-  </si>
-  <si>
-    <t>QA-5472</t>
-  </si>
-  <si>
-    <t>QA-2977</t>
-  </si>
-  <si>
-    <t>QA-8141</t>
-  </si>
-  <si>
-    <t>QA-5595</t>
-  </si>
-  <si>
-    <t>5570735129</t>
-  </si>
-  <si>
-    <t>5521016930</t>
-  </si>
-  <si>
-    <t>5519557695</t>
-  </si>
-  <si>
-    <t>5581315387</t>
-  </si>
-  <si>
-    <t>5558485576</t>
-  </si>
-  <si>
-    <t>FMAN</t>
-  </si>
-  <si>
-    <t>FAUTO</t>
+    <t>ROT -&gt; FRA</t>
+  </si>
+  <si>
+    <t>PAR -&gt; LON</t>
+  </si>
+  <si>
+    <t>Vendor 0000651823</t>
+  </si>
+  <si>
+    <t>Vendor 0000962905</t>
+  </si>
+  <si>
+    <t>Vendor 0000822839</t>
+  </si>
+  <si>
+    <t>Vendor 0000398565</t>
+  </si>
+  <si>
+    <t>Vendor 0000918878</t>
+  </si>
+  <si>
+    <t>QA-6347</t>
+  </si>
+  <si>
+    <t>QA-7484</t>
+  </si>
+  <si>
+    <t>QA-8327</t>
+  </si>
+  <si>
+    <t>QA-5271</t>
+  </si>
+  <si>
+    <t>QA-2508</t>
+  </si>
+  <si>
+    <t>5557183868</t>
+  </si>
+  <si>
+    <t>5547821556</t>
+  </si>
+  <si>
+    <t>5540901445</t>
+  </si>
+  <si>
+    <t>5577194912</t>
+  </si>
+  <si>
+    <t>5556052107</t>
+  </si>
+  <si>
+    <t>FP02</t>
+  </si>
+  <si>
+    <t>FP01</t>
   </si>
   <si>
     <t>FP03</t>
   </si>
   <si>
-    <t>683708094549</t>
-  </si>
-  <si>
-    <t>974388350659</t>
-  </si>
-  <si>
-    <t>940898251839</t>
-  </si>
-  <si>
-    <t>906918711913</t>
-  </si>
-  <si>
-    <t>866164388528</t>
-  </si>
-  <si>
-    <t>8435220026</t>
-  </si>
-  <si>
-    <t>4404845895</t>
-  </si>
-  <si>
-    <t>7717851411</t>
-  </si>
-  <si>
-    <t>6699735269</t>
-  </si>
-  <si>
-    <t>7861953153</t>
-  </si>
-  <si>
-    <t>CO-337813</t>
-  </si>
-  <si>
-    <t>CO-312044</t>
-  </si>
-  <si>
-    <t>CO-968233</t>
-  </si>
-  <si>
-    <t>CO-244956</t>
-  </si>
-  <si>
-    <t>CO-344873</t>
-  </si>
-  <si>
-    <t>PR-474642</t>
-  </si>
-  <si>
-    <t>PR-838064</t>
-  </si>
-  <si>
-    <t>PR-417451</t>
-  </si>
-  <si>
-    <t>PR-496688</t>
-  </si>
-  <si>
-    <t>PR-758422</t>
-  </si>
-  <si>
-    <t>IN-4506575</t>
-  </si>
-  <si>
-    <t>IN-8751266</t>
-  </si>
-  <si>
-    <t>IN-9630431</t>
-  </si>
-  <si>
-    <t>IN-6564012</t>
-  </si>
-  <si>
-    <t>IN-6757722</t>
-  </si>
-  <si>
-    <t>ISK-18356014</t>
-  </si>
-  <si>
-    <t>ISK-37043694</t>
-  </si>
-  <si>
-    <t>ISK-33909106</t>
-  </si>
-  <si>
-    <t>ITR-65976922</t>
-  </si>
-  <si>
-    <t>ISK-27141891</t>
-  </si>
-  <si>
-    <t>REG-003</t>
+    <t>FSTD</t>
+  </si>
+  <si>
+    <t>575211033547</t>
+  </si>
+  <si>
+    <t>957241656463</t>
+  </si>
+  <si>
+    <t>596739460941</t>
+  </si>
+  <si>
+    <t>284271096863</t>
+  </si>
+  <si>
+    <t>896187544052</t>
+  </si>
+  <si>
+    <t>5281311463</t>
+  </si>
+  <si>
+    <t>5968997420</t>
+  </si>
+  <si>
+    <t>9004983913</t>
+  </si>
+  <si>
+    <t>4839584397</t>
+  </si>
+  <si>
+    <t>9297892742</t>
+  </si>
+  <si>
+    <t>CO-572995</t>
+  </si>
+  <si>
+    <t>CO-169478</t>
+  </si>
+  <si>
+    <t>CO-438271</t>
+  </si>
+  <si>
+    <t>CO-174561</t>
+  </si>
+  <si>
+    <t>CO-373092</t>
+  </si>
+  <si>
+    <t>PR-153800</t>
+  </si>
+  <si>
+    <t>PR-417890</t>
+  </si>
+  <si>
+    <t>PR-968164</t>
+  </si>
+  <si>
+    <t>PR-109233</t>
+  </si>
+  <si>
+    <t>PR-608030</t>
+  </si>
+  <si>
+    <t>IN-5725234</t>
+  </si>
+  <si>
+    <t>IN-2184962</t>
+  </si>
+  <si>
+    <t>IN-5499988</t>
+  </si>
+  <si>
+    <t>IN-3269793</t>
+  </si>
+  <si>
+    <t>IN-4118587</t>
+  </si>
+  <si>
+    <t>ITR-91495707</t>
+  </si>
+  <si>
+    <t>SAG-42799018</t>
+  </si>
+  <si>
+    <t>SAG-75743473</t>
+  </si>
+  <si>
+    <t>SAG-32902729</t>
+  </si>
+  <si>
+    <t>ITR-20712049</t>
   </si>
   <si>
     <t>REG-001</t>
   </si>
   <si>
+    <t>REG-002</t>
+  </si>
+  <si>
     <t>REG-004</t>
   </si>
   <si>
-    <t>16655.0</t>
-  </si>
-  <si>
-    <t>80996.0</t>
-  </si>
-  <si>
-    <t>66854.0</t>
-  </si>
-  <si>
-    <t>12379.0</t>
-  </si>
-  <si>
-    <t>93344.0</t>
-  </si>
-  <si>
-    <t>W2 - Water industrieel</t>
+    <t>93881.0</t>
+  </si>
+  <si>
+    <t>80713.0</t>
+  </si>
+  <si>
+    <t>95934.0</t>
+  </si>
+  <si>
+    <t>41170.0</t>
+  </si>
+  <si>
+    <t>85132.0</t>
+  </si>
+  <si>
+    <t>G2 - Aardgas sociaal</t>
+  </si>
+  <si>
+    <t>E2 - Elektriciteit nacht</t>
   </si>
   <si>
     <t>G1 - Aardgas normaal</t>
   </si>
   <si>
-    <t>G2 - Aardgas sociaal</t>
-  </si>
-  <si>
-    <t>W1 - Water huishoudelijk</t>
+    <t>E1 - Elektriciteit dag</t>
   </si>
   <si>
     <t>03 - Water</t>
@@ -2471,112 +2480,118 @@
     <t>04 - Warmte</t>
   </si>
   <si>
-    <t>29.10.2018</t>
-  </si>
-  <si>
-    <t>17.09.2021</t>
-  </si>
-  <si>
-    <t>25.01.2018</t>
-  </si>
-  <si>
-    <t>12.12.2015</t>
-  </si>
-  <si>
-    <t>03.11.2018</t>
-  </si>
-  <si>
-    <t>07.08.2023</t>
-  </si>
-  <si>
-    <t>20.09.2018</t>
-  </si>
-  <si>
-    <t>549204979114887291</t>
-  </si>
-  <si>
-    <t>545992785569763927</t>
-  </si>
-  <si>
-    <t>548882063856276798</t>
-  </si>
-  <si>
-    <t>549817046756373020</t>
-  </si>
-  <si>
-    <t>546307040961229275</t>
-  </si>
-  <si>
-    <t>16898 kWh</t>
-  </si>
-  <si>
-    <t>15512 kWh</t>
-  </si>
-  <si>
-    <t>22704 kWh</t>
-  </si>
-  <si>
-    <t>36225 kWh</t>
-  </si>
-  <si>
-    <t>16025 kWh</t>
-  </si>
-  <si>
-    <t>PRJ-6392</t>
-  </si>
-  <si>
-    <t>IT-8590</t>
-  </si>
-  <si>
-    <t>MIL-5903</t>
-  </si>
-  <si>
-    <t>IT-1285</t>
-  </si>
-  <si>
-    <t>IT-9164</t>
-  </si>
-  <si>
-    <t>NW-812716</t>
-  </si>
-  <si>
-    <t>NW-367691</t>
-  </si>
-  <si>
-    <t>NW-910857</t>
-  </si>
-  <si>
-    <t>NW-405863</t>
-  </si>
-  <si>
-    <t>NW-539440</t>
-  </si>
-  <si>
-    <t>0090</t>
-  </si>
-  <si>
-    <t>0150</t>
-  </si>
-  <si>
-    <t>0450</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>0280</t>
+    <t>05 - Telecommunicatie</t>
+  </si>
+  <si>
+    <t>05.01.2019</t>
+  </si>
+  <si>
+    <t>16.04.2017</t>
+  </si>
+  <si>
+    <t>26.07.2024</t>
+  </si>
+  <si>
+    <t>19.12.2020</t>
+  </si>
+  <si>
+    <t>07.11.2021</t>
+  </si>
+  <si>
+    <t>27.09.2024</t>
+  </si>
+  <si>
+    <t>05.09.2022</t>
+  </si>
+  <si>
+    <t>549587151894192901</t>
+  </si>
+  <si>
+    <t>542390666605856738</t>
+  </si>
+  <si>
+    <t>545200324403471002</t>
+  </si>
+  <si>
+    <t>547078702367283268</t>
+  </si>
+  <si>
+    <t>546809303858179621</t>
+  </si>
+  <si>
+    <t>9783 kWh</t>
+  </si>
+  <si>
+    <t>40949 kWh</t>
+  </si>
+  <si>
+    <t>30235 kWh</t>
+  </si>
+  <si>
+    <t>31453 kWh</t>
+  </si>
+  <si>
+    <t>20292 kWh</t>
+  </si>
+  <si>
+    <t>DEF-3736</t>
+  </si>
+  <si>
+    <t>PRJ-2558</t>
+  </si>
+  <si>
+    <t>IT-7287</t>
+  </si>
+  <si>
+    <t>DEF-8179</t>
+  </si>
+  <si>
+    <t>PRJ-9806</t>
+  </si>
+  <si>
+    <t>NW-594554</t>
+  </si>
+  <si>
+    <t>NW-809644</t>
+  </si>
+  <si>
+    <t>NW-531749</t>
+  </si>
+  <si>
+    <t>NW-606365</t>
+  </si>
+  <si>
+    <t>NW-781730</t>
+  </si>
+  <si>
+    <t>0460</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>Fase 2 compleet</t>
+  </si>
+  <si>
+    <t>Prototype gereed</t>
+  </si>
+  <si>
+    <t>Fase 1 compleet</t>
+  </si>
+  <si>
+    <t>Ontwerp goedgekeurd</t>
   </si>
   <si>
     <t>Testfase compleet</t>
-  </si>
-  <si>
-    <t>Projectafsluiting</t>
-  </si>
-  <si>
-    <t>UAT gereed</t>
-  </si>
-  <si>
-    <t>Overdracht</t>
   </si>
   <si>
     <t>Kolomnaam</t>
@@ -3500,35 +3515,37 @@
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="24.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="25.7109375" customWidth="1"/>
+    <col min="14" max="14" width="31.7109375" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" customWidth="1"/>
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="13.7109375" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" customWidth="1"/>
-    <col min="21" max="21" width="25.7109375" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" customWidth="1"/>
+    <col min="20" max="20" width="34.7109375" customWidth="1"/>
+    <col min="21" max="21" width="21.7109375" customWidth="1"/>
     <col min="22" max="22" width="22.7109375" customWidth="1"/>
     <col min="23" max="23" width="21.7109375" customWidth="1"/>
-    <col min="24" max="24" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="18.7109375" customWidth="1"/>
     <col min="25" max="25" width="12.7109375" customWidth="1"/>
     <col min="26" max="26" width="14.7109375" customWidth="1"/>
-    <col min="27" max="27" width="28.7109375" customWidth="1"/>
+    <col min="27" max="27" width="29.7109375" customWidth="1"/>
     <col min="28" max="28" width="20.7109375" customWidth="1"/>
     <col min="29" max="29" width="40.7109375" customWidth="1"/>
-    <col min="30" max="30" width="29.7109375" customWidth="1"/>
+    <col min="30" max="30" width="28.7109375" customWidth="1"/>
     <col min="31" max="31" width="23.7109375" customWidth="1"/>
     <col min="32" max="32" width="24.7109375" customWidth="1"/>
     <col min="33" max="33" width="13.7109375" customWidth="1"/>
-    <col min="34" max="35" width="23.7109375" customWidth="1"/>
+    <col min="34" max="34" width="23.7109375" customWidth="1"/>
+    <col min="35" max="35" width="26.7109375" customWidth="1"/>
     <col min="36" max="36" width="12.7109375" customWidth="1"/>
-    <col min="37" max="37" width="30.7109375" customWidth="1"/>
-    <col min="38" max="38" width="22.7109375" customWidth="1"/>
-    <col min="39" max="39" width="26.7109375" customWidth="1"/>
-    <col min="40" max="41" width="40.7109375" customWidth="1"/>
-    <col min="42" max="42" width="32.7109375" customWidth="1"/>
+    <col min="37" max="37" width="27.7109375" customWidth="1"/>
+    <col min="38" max="38" width="21.7109375" customWidth="1"/>
+    <col min="39" max="39" width="30.7109375" customWidth="1"/>
+    <col min="40" max="40" width="39.7109375" customWidth="1"/>
+    <col min="41" max="41" width="40.7109375" customWidth="1"/>
+    <col min="42" max="42" width="38.7109375" customWidth="1"/>
     <col min="43" max="43" width="18.7109375" customWidth="1"/>
-    <col min="44" max="44" width="24.7109375" customWidth="1"/>
+    <col min="44" max="44" width="28.7109375" customWidth="1"/>
     <col min="45" max="45" width="14.7109375" customWidth="1"/>
     <col min="46" max="46" width="15.7109375" customWidth="1"/>
     <col min="47" max="47" width="21.7109375" customWidth="1"/>
@@ -3544,7 +3561,7 @@
     <col min="57" max="57" width="28.7109375" customWidth="1"/>
     <col min="58" max="59" width="27.7109375" customWidth="1"/>
     <col min="60" max="60" width="32.7109375" customWidth="1"/>
-    <col min="61" max="61" width="31.7109375" customWidth="1"/>
+    <col min="61" max="61" width="36.7109375" customWidth="1"/>
     <col min="62" max="62" width="23.7109375" customWidth="1"/>
     <col min="63" max="63" width="31.7109375" customWidth="1"/>
     <col min="64" max="64" width="25.7109375" customWidth="1"/>
@@ -3559,13 +3576,13 @@
     <col min="73" max="73" width="31.7109375" customWidth="1"/>
     <col min="74" max="74" width="32.7109375" customWidth="1"/>
     <col min="75" max="75" width="25.7109375" customWidth="1"/>
-    <col min="76" max="76" width="38.7109375" customWidth="1"/>
+    <col min="76" max="76" width="40.7109375" customWidth="1"/>
     <col min="77" max="77" width="26.7109375" customWidth="1"/>
     <col min="78" max="78" width="34.7109375" customWidth="1"/>
     <col min="79" max="79" width="32.7109375" customWidth="1"/>
     <col min="80" max="80" width="31.7109375" customWidth="1"/>
     <col min="81" max="81" width="28.7109375" customWidth="1"/>
-    <col min="82" max="82" width="25.7109375" customWidth="1"/>
+    <col min="82" max="82" width="30.7109375" customWidth="1"/>
     <col min="83" max="84" width="21.7109375" customWidth="1"/>
     <col min="85" max="85" width="27.7109375" customWidth="1"/>
     <col min="86" max="86" width="15.7109375" customWidth="1"/>
@@ -3591,9 +3608,10 @@
     <col min="108" max="108" width="29.7109375" customWidth="1"/>
     <col min="109" max="110" width="33.7109375" customWidth="1"/>
     <col min="111" max="111" width="30.7109375" customWidth="1"/>
-    <col min="112" max="112" width="21.7109375" customWidth="1"/>
-    <col min="113" max="114" width="28.7109375" customWidth="1"/>
-    <col min="115" max="115" width="30.7109375" customWidth="1"/>
+    <col min="112" max="112" width="27.7109375" customWidth="1"/>
+    <col min="113" max="113" width="28.7109375" customWidth="1"/>
+    <col min="114" max="114" width="32.7109375" customWidth="1"/>
+    <col min="115" max="115" width="40.7109375" customWidth="1"/>
     <col min="116" max="116" width="20.7109375" customWidth="1"/>
     <col min="117" max="117" width="23.7109375" customWidth="1"/>
     <col min="118" max="118" width="28.7109375" customWidth="1"/>
@@ -3626,7 +3644,7 @@
     <col min="151" max="151" width="26.7109375" customWidth="1"/>
     <col min="152" max="152" width="21.7109375" customWidth="1"/>
     <col min="153" max="153" width="26.7109375" customWidth="1"/>
-    <col min="154" max="154" width="18.7109375" customWidth="1"/>
+    <col min="154" max="154" width="23.7109375" customWidth="1"/>
     <col min="155" max="155" width="22.7109375" customWidth="1"/>
     <col min="156" max="156" width="23.7109375" customWidth="1"/>
     <col min="157" max="157" width="37.7109375" customWidth="1"/>
@@ -3634,7 +3652,7 @@
     <col min="159" max="159" width="30.7109375" customWidth="1"/>
     <col min="160" max="160" width="21.7109375" customWidth="1"/>
     <col min="161" max="161" width="31.7109375" customWidth="1"/>
-    <col min="162" max="162" width="19.7109375" customWidth="1"/>
+    <col min="162" max="162" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:162" ht="30" customHeight="1">
@@ -4148,7 +4166,7 @@
         <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I2" t="s">
         <v>198</v>
@@ -4166,85 +4184,85 @@
         <v>217</v>
       </c>
       <c r="N2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="O2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="T2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="U2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="V2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="X2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Y2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Z2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AA2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AB2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AC2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AD2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AE2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG2" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
       <c r="AH2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AI2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AJ2" t="s">
         <v>320</v>
       </c>
       <c r="AK2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AN2" t="s">
         <v>337</v>
       </c>
       <c r="AO2" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="AP2" t="s">
         <v>344</v>
@@ -4268,7 +4286,7 @@
         <v>372</v>
       </c>
       <c r="AW2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AX2" t="s">
         <v>378</v>
@@ -4277,28 +4295,28 @@
         <v>383</v>
       </c>
       <c r="AZ2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BA2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="BB2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="BC2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="BD2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="BE2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="BF2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="BG2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="BH2" t="s">
         <v>421</v>
@@ -4313,10 +4331,10 @@
         <v>436</v>
       </c>
       <c r="BL2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BM2" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="BN2" t="s">
         <v>445</v>
@@ -4325,25 +4343,25 @@
         <v>450</v>
       </c>
       <c r="BP2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BQ2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BR2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="BS2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BT2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BU2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BV2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="BW2" t="s">
         <v>485</v>
@@ -4358,52 +4376,52 @@
         <v>500</v>
       </c>
       <c r="CA2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="CB2" t="s">
         <v>505</v>
       </c>
       <c r="CC2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="CD2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="CE2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="CF2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="CG2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="CH2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="CI2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="CJ2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="CK2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="CL2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="CM2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="CN2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="CO2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="CP2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="CQ2" t="s">
         <v>565</v>
@@ -4414,77 +4432,74 @@
       <c r="CS2" t="s">
         <v>572</v>
       </c>
-      <c r="CT2" t="s">
-        <v>577</v>
-      </c>
       <c r="CU2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="CV2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="CW2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="CX2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="CY2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="CZ2" t="s">
         <v>444</v>
       </c>
       <c r="DA2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="DB2" t="s">
+        <v>603</v>
+      </c>
+      <c r="DC2" t="s">
         <v>606</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>609</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>613</v>
       </c>
-      <c r="DE2" t="s">
-        <v>618</v>
-      </c>
       <c r="DF2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="DG2" t="s">
+        <v>622</v>
+      </c>
+      <c r="DH2" t="s">
         <v>626</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>630</v>
       </c>
-      <c r="DI2" t="s">
-        <v>633</v>
-      </c>
       <c r="DJ2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="DK2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="DL2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="DM2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="DN2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="DO2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="DP2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="DQ2" t="s">
-        <v>420</v>
+        <v>668</v>
       </c>
       <c r="DR2" t="s">
         <v>672</v>
@@ -4514,97 +4529,97 @@
         <v>710</v>
       </c>
       <c r="EA2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="EB2" t="s">
-        <v>370</v>
+        <v>716</v>
       </c>
       <c r="EC2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="ED2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="EE2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="EF2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="EG2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="EH2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="EI2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="EJ2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="EK2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="EL2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="EM2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="EN2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="EO2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="EP2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="EQ2" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="ER2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="ES2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="ET2" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="EU2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="EV2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="EW2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="EX2" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="EY2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="FA2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="FB2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="FC2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="FD2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="FE2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="FF2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="3" spans="1:162">
@@ -4630,7 +4645,7 @@
         <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I3" t="s">
         <v>199</v>
@@ -4648,76 +4663,79 @@
         <v>218</v>
       </c>
       <c r="N3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="T3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="U3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="V3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="X3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Z3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AA3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AB3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AC3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AD3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AE3" t="s">
-        <v>304</v>
+        <v>302</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>306</v>
       </c>
       <c r="AG3" t="s">
-        <v>311</v>
+        <v>162</v>
       </c>
       <c r="AH3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AI3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AJ3" t="s">
         <v>321</v>
       </c>
       <c r="AK3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AM3" t="s">
         <v>334</v>
@@ -4747,40 +4765,40 @@
         <v>370</v>
       </c>
       <c r="AV3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AW3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AX3" t="s">
         <v>379</v>
       </c>
       <c r="AY3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AZ3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BA3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="BB3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="BC3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="BD3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="BE3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BF3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BG3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="BH3" t="s">
         <v>422</v>
@@ -4807,22 +4825,22 @@
         <v>451</v>
       </c>
       <c r="BP3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BQ3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="BR3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BS3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BT3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BU3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="BV3" t="s">
         <v>482</v>
@@ -4840,49 +4858,49 @@
         <v>501</v>
       </c>
       <c r="CA3" t="s">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="CB3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CC3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="CD3" t="s">
         <v>513</v>
       </c>
       <c r="CE3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="CF3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="CG3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="CH3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="CI3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="CJ3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="CK3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="CL3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="CM3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="CN3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="CO3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="CP3" t="s">
         <v>562</v>
@@ -4896,77 +4914,74 @@
       <c r="CS3" t="s">
         <v>573</v>
       </c>
-      <c r="CT3" t="s">
-        <v>578</v>
-      </c>
       <c r="CU3" t="s">
+        <v>579</v>
+      </c>
+      <c r="CV3" t="s">
         <v>582</v>
       </c>
-      <c r="CV3" t="s">
-        <v>586</v>
-      </c>
       <c r="CW3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="CX3" t="s">
+        <v>590</v>
+      </c>
+      <c r="CY3" t="s">
         <v>594</v>
       </c>
-      <c r="CY3" t="s">
-        <v>597</v>
-      </c>
       <c r="CZ3" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="DA3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="DB3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="DC3" t="s">
+        <v>606</v>
+      </c>
+      <c r="DD3" t="s">
         <v>610</v>
       </c>
-      <c r="DD3" t="s">
+      <c r="DE3" t="s">
         <v>614</v>
       </c>
-      <c r="DE3" t="s">
-        <v>619</v>
-      </c>
       <c r="DF3" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="DG3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="DH3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="DI3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="DJ3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="DK3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="DL3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="DM3" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="DN3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="DO3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="DP3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="DQ3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="DR3" t="s">
         <v>673</v>
@@ -4993,7 +5008,7 @@
         <v>706</v>
       </c>
       <c r="DZ3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="EA3" t="s">
         <v>714</v>
@@ -5002,94 +5017,91 @@
         <v>717</v>
       </c>
       <c r="EC3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="ED3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="EE3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="EF3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="EG3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="EH3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="EI3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="EJ3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="EK3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="EL3" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="EM3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="EN3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="EO3" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="EP3" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="EQ3" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="ER3" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="ES3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="ET3" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="EU3" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="EV3" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="EW3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="EX3" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="EY3" t="s">
-        <v>819</v>
-      </c>
-      <c r="EZ3" t="s">
         <v>823</v>
       </c>
       <c r="FA3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="FB3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="FC3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="FD3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="FE3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="FF3" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4" spans="1:162">
@@ -5103,7 +5115,7 @@
         <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
         <v>181</v>
@@ -5115,10 +5127,10 @@
         <v>191</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J4" t="s">
         <v>204</v>
@@ -5130,79 +5142,82 @@
         <v>214</v>
       </c>
       <c r="M4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="R4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="T4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="V4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="W4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="X4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Z4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AA4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AC4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AD4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AE4" t="s">
-        <v>305</v>
+        <v>303</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>307</v>
       </c>
       <c r="AG4" t="s">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="AH4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AI4" t="s">
         <v>317</v>
       </c>
       <c r="AJ4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AM4" t="s">
         <v>335</v>
@@ -5211,7 +5226,7 @@
         <v>339</v>
       </c>
       <c r="AO4" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="AP4" t="s">
         <v>346</v>
@@ -5229,10 +5244,10 @@
         <v>366</v>
       </c>
       <c r="AU4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AV4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AW4" t="s">
         <v>376</v>
@@ -5241,31 +5256,31 @@
         <v>380</v>
       </c>
       <c r="AY4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AZ4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BA4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BB4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="BC4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="BD4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="BE4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="BF4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="BG4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BH4" t="s">
         <v>423</v>
@@ -5289,25 +5304,25 @@
         <v>447</v>
       </c>
       <c r="BO4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BP4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BQ4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="BR4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="BS4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BT4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BU4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BV4" t="s">
         <v>483</v>
@@ -5325,49 +5340,49 @@
         <v>502</v>
       </c>
       <c r="CA4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="CB4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="CC4" t="s">
         <v>510</v>
       </c>
       <c r="CD4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="CE4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="CF4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="CG4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="CH4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="CI4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="CJ4" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="CK4" t="s">
         <v>540</v>
       </c>
       <c r="CL4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="CM4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="CN4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="CO4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="CP4" t="s">
         <v>562</v>
@@ -5382,76 +5397,76 @@
         <v>574</v>
       </c>
       <c r="CT4" t="s">
+        <v>575</v>
+      </c>
+      <c r="CU4" t="s">
         <v>579</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CV4" t="s">
         <v>583</v>
       </c>
-      <c r="CV4" t="s">
+      <c r="CW4" t="s">
         <v>587</v>
       </c>
-      <c r="CW4" t="s">
-        <v>592</v>
-      </c>
       <c r="CX4" t="s">
+        <v>591</v>
+      </c>
+      <c r="CY4" t="s">
         <v>595</v>
       </c>
-      <c r="CY4" t="s">
-        <v>598</v>
-      </c>
       <c r="CZ4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="DA4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="DB4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="DC4" t="s">
+        <v>606</v>
+      </c>
+      <c r="DD4" t="s">
         <v>611</v>
       </c>
-      <c r="DD4" t="s">
+      <c r="DE4" t="s">
         <v>615</v>
       </c>
-      <c r="DE4" t="s">
-        <v>620</v>
-      </c>
       <c r="DF4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="DG4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="DH4" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="DI4" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="DJ4" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="DK4" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="DL4" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="DM4" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="DN4" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="DO4" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="DP4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="DQ4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="DR4" t="s">
         <v>674</v>
@@ -5478,103 +5493,103 @@
         <v>707</v>
       </c>
       <c r="DZ4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="EA4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="EB4" t="s">
-        <v>370</v>
+        <v>718</v>
       </c>
       <c r="EC4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="ED4" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="EE4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="EF4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="EG4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="EH4" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="EI4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="EJ4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="EK4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="EL4" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="EM4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="EN4" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="EO4" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="EP4" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="EQ4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="ER4" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="ES4" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="ET4" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="EU4" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="EV4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="EW4" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="EX4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="EY4" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="EZ4" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="FA4" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="FB4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="FC4" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="FD4" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="FE4" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="FF4" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:162">
@@ -5597,13 +5612,13 @@
         <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J5" t="s">
         <v>205</v>
@@ -5615,91 +5630,91 @@
         <v>215</v>
       </c>
       <c r="M5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="O5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="T5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="U5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="V5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="W5" t="s">
         <v>267</v>
       </c>
       <c r="X5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Y5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Z5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AA5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AB5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AD5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AE5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AF5" t="s">
         <v>308</v>
       </c>
       <c r="AG5" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="AH5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AI5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AJ5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK5" t="s">
         <v>327</v>
       </c>
       <c r="AL5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AM5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN5" t="s">
         <v>340</v>
       </c>
       <c r="AO5" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="AP5" t="s">
         <v>347</v>
@@ -5723,37 +5738,37 @@
         <v>373</v>
       </c>
       <c r="AW5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AX5" t="s">
         <v>381</v>
       </c>
       <c r="AY5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AZ5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BA5" t="s">
         <v>393</v>
       </c>
       <c r="BB5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="BC5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="BD5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BE5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="BF5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="BG5" t="s">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="BH5" t="s">
         <v>424</v>
@@ -5768,34 +5783,34 @@
         <v>439</v>
       </c>
       <c r="BL5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BM5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BN5" t="s">
         <v>448</v>
       </c>
       <c r="BO5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BP5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BQ5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BR5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="BS5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="BT5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BU5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BV5" t="s">
         <v>484</v>
@@ -5816,46 +5831,46 @@
         <v>374</v>
       </c>
       <c r="CB5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="CC5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="CD5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="CE5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="CF5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="CG5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="CH5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="CI5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="CJ5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="CK5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="CL5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="CM5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="CN5" t="s">
         <v>555</v>
       </c>
       <c r="CO5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="CP5" t="s">
         <v>563</v>
@@ -5867,79 +5882,79 @@
         <v>570</v>
       </c>
       <c r="CS5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="CT5" t="s">
+        <v>576</v>
+      </c>
+      <c r="CU5" t="s">
         <v>580</v>
       </c>
-      <c r="CU5" t="s">
+      <c r="CV5" t="s">
         <v>584</v>
       </c>
-      <c r="CV5" t="s">
-        <v>588</v>
-      </c>
       <c r="CW5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="CX5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="CY5" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="CZ5" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="DA5" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="DB5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="DC5" t="s">
+        <v>607</v>
+      </c>
+      <c r="DD5" t="s">
         <v>612</v>
       </c>
-      <c r="DD5" t="s">
-        <v>616</v>
-      </c>
       <c r="DE5" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="DF5" t="s">
+        <v>620</v>
+      </c>
+      <c r="DG5" t="s">
         <v>624</v>
       </c>
-      <c r="DG5" t="s">
+      <c r="DH5" t="s">
         <v>628</v>
       </c>
-      <c r="DH5" t="s">
-        <v>630</v>
-      </c>
       <c r="DI5" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="DJ5" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="DK5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="DL5" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="DM5" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="DN5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="DO5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="DP5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="DQ5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="DR5" t="s">
         <v>675</v>
@@ -5957,7 +5972,7 @@
         <v>695</v>
       </c>
       <c r="DW5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="DX5" t="s">
         <v>703</v>
@@ -5966,100 +5981,100 @@
         <v>708</v>
       </c>
       <c r="DZ5" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="EA5" t="s">
         <v>715</v>
       </c>
       <c r="EB5" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="EC5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="ED5" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="EE5" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="EF5" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="EG5" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="EH5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="EI5" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="EJ5" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="EK5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="EL5" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="EM5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="EN5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="EO5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="EP5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="EQ5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="ER5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="ES5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="ET5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="EU5" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="EV5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="EW5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="EX5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="EY5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="FA5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="FB5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="FC5" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="FD5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="FE5" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="FF5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:162">
@@ -6082,10 +6097,10 @@
         <v>188</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I6" t="s">
         <v>201</v>
@@ -6100,91 +6115,91 @@
         <v>216</v>
       </c>
       <c r="M6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="T6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="U6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="V6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="W6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Y6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Z6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AA6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AB6" t="s">
         <v>291</v>
       </c>
       <c r="AC6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AD6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AE6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AF6" t="s">
         <v>309</v>
       </c>
       <c r="AG6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AH6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AI6" t="s">
         <v>319</v>
       </c>
       <c r="AJ6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AK6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AM6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN6" t="s">
         <v>341</v>
       </c>
       <c r="AO6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AP6" t="s">
         <v>348</v>
@@ -6202,43 +6217,43 @@
         <v>368</v>
       </c>
       <c r="AU6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AV6" t="s">
+        <v>374</v>
+      </c>
+      <c r="AW6" t="s">
         <v>373</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>377</v>
       </c>
       <c r="AX6" t="s">
         <v>382</v>
       </c>
       <c r="AY6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AZ6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="BA6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="BB6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BC6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="BD6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="BE6" t="s">
         <v>411</v>
       </c>
       <c r="BF6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="BG6" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="BH6" t="s">
         <v>425</v>
@@ -6250,37 +6265,37 @@
         <v>435</v>
       </c>
       <c r="BK6" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="BL6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="BM6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="BN6" t="s">
         <v>449</v>
       </c>
       <c r="BO6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BP6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BQ6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="BR6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="BS6" t="s">
         <v>472</v>
       </c>
       <c r="BT6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BU6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="BV6" t="s">
         <v>484</v>
@@ -6298,49 +6313,49 @@
         <v>504</v>
       </c>
       <c r="CA6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="CB6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="CC6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="CD6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="CE6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="CF6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="CG6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="CH6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="CI6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="CJ6" t="s">
         <v>537</v>
       </c>
       <c r="CK6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="CL6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="CM6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="CN6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="CO6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="CP6" t="s">
         <v>564</v>
@@ -6352,79 +6367,79 @@
         <v>571</v>
       </c>
       <c r="CS6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="CT6" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="CU6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="CV6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="CW6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="CX6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="CY6" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="CZ6" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="DA6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="DB6" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="DC6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="DD6" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="DE6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="DF6" t="s">
+        <v>621</v>
+      </c>
+      <c r="DG6" t="s">
         <v>625</v>
       </c>
-      <c r="DG6" t="s">
+      <c r="DH6" t="s">
         <v>629</v>
       </c>
-      <c r="DH6" t="s">
-        <v>632</v>
-      </c>
       <c r="DI6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="DJ6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="DK6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="DL6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="DM6" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="DN6" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="DO6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="DP6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="DQ6" t="s">
-        <v>420</v>
+        <v>668</v>
       </c>
       <c r="DR6" t="s">
         <v>676</v>
@@ -6442,7 +6457,7 @@
         <v>696</v>
       </c>
       <c r="DW6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="DX6" t="s">
         <v>704</v>
@@ -6451,100 +6466,103 @@
         <v>709</v>
       </c>
       <c r="DZ6" t="s">
+        <v>710</v>
+      </c>
+      <c r="EA6" t="s">
         <v>713</v>
       </c>
-      <c r="EA6" t="s">
-        <v>716</v>
-      </c>
       <c r="EB6" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="EC6" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="ED6" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="EE6" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="EF6" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="EG6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="EH6" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="EI6" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="EJ6" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="EK6" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="EL6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="EM6" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="EN6" t="s">
         <v>773</v>
       </c>
       <c r="EO6" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="EP6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="EQ6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="ER6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="ES6" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="ET6" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="EU6" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="EV6" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="EW6" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="EX6" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="EY6" t="s">
-        <v>822</v>
+        <v>826</v>
+      </c>
+      <c r="EZ6" t="s">
+        <v>828</v>
       </c>
       <c r="FA6" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="FB6" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="FC6" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="FD6" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="FE6" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="FF6" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -6563,13 +6581,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6577,10 +6595,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6591,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6602,7 +6620,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6613,7 +6631,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6624,7 +6642,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6635,7 +6653,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6646,7 +6664,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6657,7 +6675,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6668,7 +6686,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6676,10 +6694,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="C11" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6690,7 +6708,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6701,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6712,7 +6730,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6720,10 +6738,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C15" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6731,10 +6749,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C16" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6742,10 +6760,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C17" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6756,7 +6774,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6767,7 +6785,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6775,10 +6793,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="C20" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6789,7 +6807,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6800,7 +6818,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6811,7 +6829,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6822,7 +6840,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6833,7 +6851,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6841,10 +6859,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C26" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6855,7 +6873,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6866,7 +6884,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6874,10 +6892,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="C29" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6885,10 +6903,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C30" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6899,7 +6917,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6910,7 +6928,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6921,7 +6939,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6932,7 +6950,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6943,7 +6961,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6954,7 +6972,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6965,7 +6983,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6976,7 +6994,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6987,7 +7005,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6998,7 +7016,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7009,7 +7027,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7017,10 +7035,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C42" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7028,10 +7046,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C43" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7039,10 +7057,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C44" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7050,10 +7068,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C45" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7064,7 +7082,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7072,10 +7090,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C47" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7086,7 +7104,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7097,7 +7115,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7108,7 +7126,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7119,7 +7137,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7130,7 +7148,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7141,7 +7159,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7152,7 +7170,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7163,7 +7181,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7174,7 +7192,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7185,7 +7203,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7196,7 +7214,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7207,7 +7225,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7218,7 +7236,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7229,7 +7247,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7240,7 +7258,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7251,7 +7269,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7262,7 +7280,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7273,7 +7291,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7284,7 +7302,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7295,7 +7313,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7306,7 +7324,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7317,7 +7335,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7328,7 +7346,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7339,7 +7357,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7350,7 +7368,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7361,7 +7379,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7372,7 +7390,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7383,7 +7401,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7394,7 +7412,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7405,7 +7423,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7416,7 +7434,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7427,7 +7445,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7438,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7449,7 +7467,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7460,7 +7478,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7471,7 +7489,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7482,7 +7500,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7493,7 +7511,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7504,7 +7522,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7515,7 +7533,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7526,7 +7544,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7537,7 +7555,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7548,7 +7566,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7559,7 +7577,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7570,7 +7588,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7581,7 +7599,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7592,7 +7610,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7603,7 +7621,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7614,7 +7632,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7625,7 +7643,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7636,7 +7654,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7647,7 +7665,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7658,7 +7676,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7669,7 +7687,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7680,7 +7698,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7691,7 +7709,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7702,7 +7720,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7713,7 +7731,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7724,7 +7742,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7735,7 +7753,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7746,7 +7764,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7757,7 +7775,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7768,7 +7786,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7779,7 +7797,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7790,7 +7808,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7801,7 +7819,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7812,7 +7830,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7823,7 +7841,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7834,7 +7852,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7845,7 +7863,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7856,7 +7874,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7867,7 +7885,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7878,7 +7896,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7889,7 +7907,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7900,7 +7918,7 @@
         <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7911,7 +7929,7 @@
         <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7922,7 +7940,7 @@
         <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7933,7 +7951,7 @@
         <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7944,7 +7962,7 @@
         <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7955,7 +7973,7 @@
         <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7966,7 +7984,7 @@
         <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7977,7 +7995,7 @@
         <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -7988,7 +8006,7 @@
         <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -7999,7 +8017,7 @@
         <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8010,7 +8028,7 @@
         <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8021,7 +8039,7 @@
         <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8032,7 +8050,7 @@
         <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8043,7 +8061,7 @@
         <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8054,7 +8072,7 @@
         <v>134</v>
       </c>
       <c r="C136" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8065,7 +8083,7 @@
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8076,7 +8094,7 @@
         <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8087,7 +8105,7 @@
         <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8098,7 +8116,7 @@
         <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8109,7 +8127,7 @@
         <v>139</v>
       </c>
       <c r="C141" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8120,7 +8138,7 @@
         <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8131,7 +8149,7 @@
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8142,7 +8160,7 @@
         <v>142</v>
       </c>
       <c r="C144" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8153,7 +8171,7 @@
         <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8164,7 +8182,7 @@
         <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8175,7 +8193,7 @@
         <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8186,7 +8204,7 @@
         <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8197,7 +8215,7 @@
         <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8208,7 +8226,7 @@
         <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8219,7 +8237,7 @@
         <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8230,7 +8248,7 @@
         <v>150</v>
       </c>
       <c r="C152" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8241,7 +8259,7 @@
         <v>151</v>
       </c>
       <c r="C153" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8252,7 +8270,7 @@
         <v>152</v>
       </c>
       <c r="C154" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8263,7 +8281,7 @@
         <v>153</v>
       </c>
       <c r="C155" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8274,7 +8292,7 @@
         <v>154</v>
       </c>
       <c r="C156" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8285,7 +8303,7 @@
         <v>155</v>
       </c>
       <c r="C157" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8296,7 +8314,7 @@
         <v>156</v>
       </c>
       <c r="C158" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8307,7 +8325,7 @@
         <v>157</v>
       </c>
       <c r="C159" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8318,7 +8336,7 @@
         <v>158</v>
       </c>
       <c r="C160" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8329,7 +8347,7 @@
         <v>159</v>
       </c>
       <c r="C161" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8340,7 +8358,7 @@
         <v>160</v>
       </c>
       <c r="C162" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8351,7 +8369,7 @@
         <v>161</v>
       </c>
       <c r="C163" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>

--- a/template_defensie_hr.xlsx
+++ b/template_defensie_hr.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1040">
   <si>
     <t>Personeelsnummer</t>
   </si>
@@ -518,34 +518,34 @@
     <t>5</t>
   </si>
   <si>
-    <t>Stefan</t>
-  </si>
-  <si>
-    <t>Maarten</t>
-  </si>
-  <si>
-    <t>Mohammed</t>
-  </si>
-  <si>
-    <t>Bo</t>
-  </si>
-  <si>
-    <t>Guy</t>
-  </si>
-  <si>
-    <t>De Clercq</t>
-  </si>
-  <si>
-    <t>Jacobs</t>
-  </si>
-  <si>
-    <t>Huys</t>
-  </si>
-  <si>
-    <t>Verbeke</t>
-  </si>
-  <si>
-    <t>De Baere</t>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Tijl</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>Meert</t>
+  </si>
+  <si>
+    <t>Desmet</t>
+  </si>
+  <si>
+    <t>Lenaerts</t>
+  </si>
+  <si>
+    <t>Verbruggen</t>
+  </si>
+  <si>
+    <t>Martens</t>
   </si>
   <si>
     <t>M</t>
@@ -554,2044 +554,2050 @@
     <t>V</t>
   </si>
   <si>
-    <t>01/06/1973</t>
-  </si>
-  <si>
-    <t>03/11/1984</t>
-  </si>
-  <si>
-    <t>05/07/1980</t>
-  </si>
-  <si>
-    <t>06/07/1976</t>
-  </si>
-  <si>
-    <t>29/06/1986</t>
-  </si>
-  <si>
-    <t>Lapscheure</t>
-  </si>
-  <si>
-    <t>Harsin</t>
-  </si>
-  <si>
-    <t>Haren-Tongeren</t>
-  </si>
-  <si>
-    <t>Okegem</t>
-  </si>
-  <si>
-    <t>Micheroux</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>18/10/1959</t>
+  </si>
+  <si>
+    <t>09/08/1995</t>
+  </si>
+  <si>
+    <t>09/03/1975</t>
+  </si>
+  <si>
+    <t>07/02/1966</t>
+  </si>
+  <si>
+    <t>26/03/1993</t>
+  </si>
+  <si>
+    <t>Mielen-boven-Aalst</t>
+  </si>
+  <si>
+    <t>Vertrijk</t>
+  </si>
+  <si>
+    <t>Olsene</t>
+  </si>
+  <si>
+    <t>Achêne</t>
+  </si>
+  <si>
+    <t>Remagne</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Roemeens</t>
+  </si>
+  <si>
+    <t>Brits</t>
+  </si>
+  <si>
+    <t>Grieks</t>
+  </si>
+  <si>
+    <t>Frans</t>
+  </si>
+  <si>
+    <t>Wettelijk samenwonend</t>
+  </si>
+  <si>
+    <t>Ongehuwd</t>
+  </si>
+  <si>
+    <t>Gehuwd</t>
+  </si>
+  <si>
+    <t>Weduwe/Weduwnaar</t>
+  </si>
+  <si>
+    <t>05.09.24-919.13</t>
+  </si>
+  <si>
+    <t>83.12.26-907.43</t>
+  </si>
+  <si>
+    <t>01.06.24-964.57</t>
+  </si>
+  <si>
+    <t>04.01.09-858.59</t>
+  </si>
+  <si>
+    <t>83.05.02-127.39</t>
+  </si>
+  <si>
+    <t>PX6762373</t>
+  </si>
+  <si>
+    <t>SZ7025005</t>
+  </si>
+  <si>
+    <t>BZ1043473</t>
+  </si>
+  <si>
+    <t>XY3698370</t>
+  </si>
+  <si>
+    <t>ZJ7685326</t>
+  </si>
+  <si>
+    <t>603-7883534-38</t>
+  </si>
+  <si>
+    <t>602-9742797-28</t>
+  </si>
+  <si>
+    <t>656-5924401-26</t>
+  </si>
+  <si>
+    <t>419-7952684-47</t>
+  </si>
+  <si>
+    <t>103-4400904-87</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>janssenswendy@example.org</t>
+  </si>
+  <si>
+    <t>desmetgeert@example.org</t>
+  </si>
+  <si>
+    <t>janssensrosa@example.net</t>
+  </si>
+  <si>
+    <t>noahvandevelde@example.org</t>
+  </si>
+  <si>
+    <t>verdonckarno@example.org</t>
+  </si>
+  <si>
+    <t>001 1941725</t>
+  </si>
+  <si>
+    <t>01 412 77 80</t>
+  </si>
+  <si>
+    <t>09/ 180 56 62</t>
+  </si>
+  <si>
+    <t>+32(0)033 016597</t>
+  </si>
+  <si>
+    <t>012-5135775</t>
+  </si>
+  <si>
+    <t>Anniestraat</t>
+  </si>
+  <si>
+    <t>Jacquelineweg</t>
+  </si>
+  <si>
+    <t>Celinedreef</t>
+  </si>
+  <si>
+    <t>Rafaëllei</t>
+  </si>
+  <si>
+    <t>Erikhof</t>
+  </si>
+  <si>
+    <t>111A</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>6917</t>
+  </si>
+  <si>
+    <t>8390</t>
+  </si>
+  <si>
+    <t>6470</t>
+  </si>
+  <si>
+    <t>9256</t>
+  </si>
+  <si>
+    <t>9868</t>
+  </si>
+  <si>
+    <t>Jemeppe-sur-Sambre</t>
+  </si>
+  <si>
+    <t>Slijpe</t>
+  </si>
+  <si>
+    <t>Ville-en-Hesbaye</t>
+  </si>
+  <si>
+    <t>Marche-lez-Ecaussinnes</t>
+  </si>
+  <si>
+    <t>Bovenistier</t>
+  </si>
+  <si>
+    <t>Verenigd Koninkrijk</t>
+  </si>
+  <si>
+    <t>Bulgarije</t>
+  </si>
+  <si>
+    <t>Sint-Maarten</t>
+  </si>
+  <si>
+    <t>Brits Indische Oceaanterritorium</t>
+  </si>
+  <si>
+    <t>België</t>
+  </si>
+  <si>
+    <t>Jana Maes</t>
+  </si>
+  <si>
+    <t>Maria Maes</t>
+  </si>
+  <si>
+    <t>Fabienne Janssens</t>
+  </si>
+  <si>
+    <t>Maria Claes</t>
+  </si>
+  <si>
+    <t>Els Goossens</t>
+  </si>
+  <si>
+    <t>+32937 336521</t>
+  </si>
+  <si>
+    <t>019-5399472</t>
+  </si>
+  <si>
+    <t>(0446)-964992</t>
+  </si>
+  <si>
+    <t>+32(0)68-5312829</t>
+  </si>
+  <si>
+    <t>+32566 829187</t>
+  </si>
+  <si>
+    <t>Echtgeno(o)t(e)</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>Zus</t>
+  </si>
+  <si>
+    <t>Zoon</t>
+  </si>
+  <si>
+    <t>Onderluitenant</t>
+  </si>
+  <si>
+    <t>Sergeant</t>
+  </si>
+  <si>
+    <t>Luitenant</t>
+  </si>
+  <si>
+    <t>Adjudant</t>
+  </si>
+  <si>
+    <t>Eerste Sergeant-Majoor</t>
+  </si>
+  <si>
+    <t>M696651</t>
+  </si>
+  <si>
+    <t>M533857</t>
+  </si>
+  <si>
+    <t>M230245</t>
+  </si>
+  <si>
+    <t>M487948</t>
+  </si>
+  <si>
+    <t>M401531</t>
+  </si>
+  <si>
+    <t>98-267885</t>
+  </si>
+  <si>
+    <t>46-261390</t>
+  </si>
+  <si>
+    <t>49-500425</t>
+  </si>
+  <si>
+    <t>24-271522</t>
+  </si>
+  <si>
+    <t>19-197227</t>
+  </si>
+  <si>
+    <t>Eenheid Speciale Operaties</t>
+  </si>
+  <si>
+    <t>2de Regiment Lansiers</t>
+  </si>
+  <si>
+    <t>Bataljon ISTAR</t>
+  </si>
+  <si>
+    <t>12de Linie - Prins Leopold</t>
+  </si>
+  <si>
+    <t>Signal Battalion</t>
+  </si>
+  <si>
+    <t>ISTAR-groep</t>
+  </si>
+  <si>
+    <t>Landcomponent</t>
+  </si>
+  <si>
+    <t>Luchtcomponent</t>
+  </si>
+  <si>
+    <t>Licht Brigade</t>
+  </si>
+  <si>
+    <t>Middelzware Brigade</t>
+  </si>
+  <si>
+    <t>Kwartier Platteau - Peutie</t>
+  </si>
+  <si>
+    <t>Kwartier Rucquoy - Tournai</t>
+  </si>
+  <si>
+    <t>Kwartier Ieper</t>
+  </si>
+  <si>
+    <t>Kamp Beverlo - Leopoldsburg</t>
+  </si>
+  <si>
+    <t>Luchtmachtbasis Florennes</t>
+  </si>
+  <si>
+    <t>Chauffeur zware voertuigen</t>
+  </si>
+  <si>
+    <t>IT-specialist Cyber</t>
+  </si>
+  <si>
+    <t>Kok</t>
+  </si>
+  <si>
+    <t>Communicatiespecialist</t>
+  </si>
+  <si>
+    <t>Verpleegkundige</t>
+  </si>
+  <si>
+    <t>01/12/2004</t>
+  </si>
+  <si>
+    <t>27/06/1993</t>
+  </si>
+  <si>
+    <t>08/06/2017</t>
+  </si>
+  <si>
+    <t>08/04/2024</t>
+  </si>
+  <si>
+    <t>14/12/1987</t>
+  </si>
+  <si>
+    <t>13/03/2000</t>
+  </si>
+  <si>
+    <t>02/04/2000</t>
+  </si>
+  <si>
+    <t>07/03/2014</t>
+  </si>
+  <si>
+    <t>04/06/2006</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Oostenrijks</t>
-  </si>
-  <si>
-    <t>Italiaans</t>
-  </si>
-  <si>
-    <t>Iers</t>
-  </si>
-  <si>
-    <t>Belgisch</t>
-  </si>
-  <si>
-    <t>Weduwe/Weduwnaar</t>
-  </si>
-  <si>
-    <t>Gehuwd</t>
-  </si>
-  <si>
-    <t>Ongehuwd</t>
-  </si>
-  <si>
-    <t>Wettelijk samenwonend</t>
-  </si>
-  <si>
-    <t>02.06.25-588.36</t>
-  </si>
-  <si>
-    <t>86.05.25-626.77</t>
-  </si>
-  <si>
-    <t>04.01.01-874.89</t>
-  </si>
-  <si>
-    <t>00.04.24-662.33</t>
-  </si>
-  <si>
-    <t>68.09.27-054.45</t>
-  </si>
-  <si>
-    <t>IZ3202247</t>
-  </si>
-  <si>
-    <t>IZ8883708</t>
-  </si>
-  <si>
-    <t>IY7429908</t>
-  </si>
-  <si>
-    <t>XR8498537</t>
-  </si>
-  <si>
-    <t>LN9328855</t>
-  </si>
-  <si>
-    <t>849-8817796-51</t>
-  </si>
-  <si>
-    <t>405-4402372-16</t>
-  </si>
-  <si>
-    <t>873-4888748-64</t>
-  </si>
-  <si>
-    <t>941-6775376-19</t>
-  </si>
-  <si>
-    <t>544-4506948-39</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>O+</t>
-  </si>
-  <si>
-    <t>huybrechtsgeorges@example.com</t>
-  </si>
-  <si>
-    <t>bpauwels@example.org</t>
-  </si>
-  <si>
-    <t>veerle75@example.net</t>
-  </si>
-  <si>
-    <t>sjacobs@example.org</t>
-  </si>
-  <si>
-    <t>kevinlemmens@example.org</t>
-  </si>
-  <si>
-    <t>086-8440038</t>
-  </si>
-  <si>
-    <t>+32881-055765</t>
-  </si>
-  <si>
-    <t>+32(0)439-066744</t>
-  </si>
-  <si>
-    <t>(0312)-662930</t>
-  </si>
-  <si>
-    <t>(0262) 653260</t>
-  </si>
-  <si>
-    <t>Annieweg</t>
-  </si>
-  <si>
-    <t>Edgardring</t>
-  </si>
-  <si>
-    <t>Kjellbaan</t>
-  </si>
-  <si>
-    <t>Carinesteeg</t>
-  </si>
-  <si>
-    <t>Brunosteeg</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>3707</t>
-  </si>
-  <si>
-    <t>3412</t>
-  </si>
-  <si>
-    <t>4680</t>
-  </si>
-  <si>
-    <t>2164</t>
-  </si>
-  <si>
-    <t>8147</t>
-  </si>
-  <si>
-    <t>Liezele</t>
-  </si>
-  <si>
-    <t>Zutendaal</t>
-  </si>
-  <si>
-    <t>Pecq</t>
-  </si>
-  <si>
-    <t>Spermalie</t>
-  </si>
-  <si>
-    <t>Edingen</t>
-  </si>
-  <si>
-    <t>Brits Indische Oceaanterritorium</t>
-  </si>
-  <si>
-    <t>Libië</t>
-  </si>
-  <si>
-    <t>Wallis en Futuna</t>
-  </si>
-  <si>
-    <t>Tuvalu</t>
-  </si>
-  <si>
-    <t>Barbados</t>
-  </si>
-  <si>
-    <t>Elias Van Driessche</t>
-  </si>
-  <si>
-    <t>Kathleen Verhoeven</t>
-  </si>
-  <si>
-    <t>Anne Torfs</t>
-  </si>
-  <si>
-    <t>Ida Cornelis</t>
-  </si>
-  <si>
-    <t>Marieke Lambert</t>
-  </si>
-  <si>
-    <t>+32(0)11-1930334</t>
-  </si>
-  <si>
-    <t>(0839)-386616</t>
-  </si>
-  <si>
-    <t>(0113)-547098</t>
-  </si>
-  <si>
-    <t>01 239 00 20</t>
-  </si>
-  <si>
-    <t>0435 170059</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>Broer</t>
-  </si>
-  <si>
-    <t>Vader</t>
-  </si>
-  <si>
-    <t>Soldaat</t>
-  </si>
-  <si>
-    <t>Korporaal</t>
-  </si>
-  <si>
-    <t>Eerste Korporaal</t>
-  </si>
-  <si>
-    <t>Majoor</t>
-  </si>
-  <si>
-    <t>Brigadegeneraal</t>
-  </si>
-  <si>
-    <t>M276403</t>
-  </si>
-  <si>
-    <t>M543661</t>
-  </si>
-  <si>
-    <t>M920850</t>
-  </si>
-  <si>
-    <t>M807086</t>
-  </si>
-  <si>
-    <t>M647184</t>
-  </si>
-  <si>
-    <t>47-407280</t>
-  </si>
-  <si>
-    <t>51-108156</t>
-  </si>
-  <si>
-    <t>25-533168</t>
-  </si>
-  <si>
-    <t>49-931286</t>
-  </si>
-  <si>
-    <t>45-265281</t>
-  </si>
-  <si>
-    <t>2de Bataljon Jagers te Voet</t>
-  </si>
-  <si>
-    <t>Bataljon ISTAR</t>
-  </si>
-  <si>
-    <t>3de Bataljon Parachutisten</t>
-  </si>
-  <si>
-    <t>1ste Bataljon Artillerie</t>
-  </si>
-  <si>
-    <t>1ste Regiment Gidsen</t>
-  </si>
-  <si>
-    <t>Luchtcomponent</t>
-  </si>
-  <si>
-    <t>Landcomponent</t>
-  </si>
-  <si>
-    <t>Marinecomponent</t>
-  </si>
-  <si>
-    <t>Medische Component</t>
-  </si>
-  <si>
-    <t>Kwartier Berlaar</t>
-  </si>
-  <si>
-    <t>Kamp Lagland - Arlon</t>
-  </si>
-  <si>
-    <t>Kwartier Lombardsijde</t>
-  </si>
-  <si>
-    <t>Kwartier Majoor Housiau - Marche-en-Famenne</t>
-  </si>
-  <si>
-    <t>Kamp Beverlo - Leopoldsburg</t>
-  </si>
-  <si>
-    <t>Infanterist</t>
-  </si>
-  <si>
-    <t>Muzikant</t>
-  </si>
-  <si>
-    <t>Navigator</t>
-  </si>
-  <si>
-    <t>Genieofficier</t>
-  </si>
-  <si>
-    <t>23/03/2009</t>
-  </si>
-  <si>
-    <t>07/08/2018</t>
-  </si>
-  <si>
-    <t>04/07/1999</t>
-  </si>
-  <si>
-    <t>24/11/2012</t>
-  </si>
-  <si>
-    <t>04/11/1994</t>
-  </si>
-  <si>
-    <t>30/11/2009</t>
-  </si>
-  <si>
-    <t>17/06/2015</t>
-  </si>
-  <si>
-    <t>04/10/2020</t>
-  </si>
-  <si>
-    <t>24/01/2004</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Medisch onbeschikbaar</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Verlof</t>
+  </si>
+  <si>
+    <t>Beschikbaar</t>
+  </si>
+  <si>
+    <t>Pensioen</t>
+  </si>
+  <si>
+    <t>Stand-by</t>
   </si>
   <si>
     <t>Ingezet - Binnenland</t>
   </si>
   <si>
-    <t>Reserve</t>
-  </si>
-  <si>
-    <t>Pensioen</t>
-  </si>
-  <si>
-    <t>Verlof</t>
-  </si>
-  <si>
     <t>Zeer Geheim</t>
   </si>
   <si>
+    <t>Geheim</t>
+  </si>
+  <si>
     <t>Vertrouwelijk</t>
   </si>
   <si>
-    <t>Cosmic Top Secret (NATO)</t>
-  </si>
-  <si>
-    <t>Geheim</t>
-  </si>
-  <si>
-    <t>HO1</t>
-  </si>
-  <si>
-    <t>BOO4</t>
-  </si>
-  <si>
-    <t>HO3</t>
-  </si>
-  <si>
-    <t>BOF2</t>
-  </si>
-  <si>
-    <t>BOO3</t>
-  </si>
-  <si>
-    <t>FN Five-seveN - Standaard</t>
-  </si>
-  <si>
-    <t>FN P90 - Standaard</t>
+    <t>BV4</t>
+  </si>
+  <si>
+    <t>BOF6</t>
+  </si>
+  <si>
+    <t>HO2</t>
+  </si>
+  <si>
+    <t>FN MAG - Gekwalificeerd</t>
+  </si>
+  <si>
+    <t>M72 LAW - Gekwalificeerd</t>
   </si>
   <si>
     <t>Niet gekwalificeerd</t>
   </si>
   <si>
-    <t>82/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>88/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>94/100 (Uitstekend)</t>
-  </si>
-  <si>
-    <t>55/100 (Voldoende)</t>
-  </si>
-  <si>
-    <t>76/100 (Goed)</t>
-  </si>
-  <si>
-    <t>Rupsbandvoertuig - Piranha</t>
+    <t>FN SCAR-L - Standaard</t>
+  </si>
+  <si>
+    <t>44/100 (Onvoldoende)</t>
+  </si>
+  <si>
+    <t>67/100 (Goed)</t>
+  </si>
+  <si>
+    <t>95/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>91/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>80/100 (Uitstekend)</t>
+  </si>
+  <si>
+    <t>C - Vrachtwagen</t>
   </si>
   <si>
     <t>Rupsbandvoertuig - Pandur</t>
   </si>
   <si>
-    <t>CE - Vrachtwagen + aanhanger</t>
-  </si>
-  <si>
-    <t>D - Bus / Troepenvervoer</t>
-  </si>
-  <si>
-    <t>Nederlands: B2; Engels: B1; Frans: B2</t>
-  </si>
-  <si>
-    <t>Duits: B1; Engels: C1</t>
-  </si>
-  <si>
-    <t>Engels: B2; Frans: B1</t>
-  </si>
-  <si>
-    <t>Engels: C2; Nederlands: Moedertaal</t>
-  </si>
-  <si>
-    <t>Nederlands: Moedertaal; Engels: C2</t>
+    <t>Rupsbandvoertuig - Dingo</t>
+  </si>
+  <si>
+    <t>Duits: B2; Frans: Moedertaal; Nederlands: C2; Engels: A1</t>
+  </si>
+  <si>
+    <t>Nederlands: C1; Engels: C1; Frans: B1; Duits: A2</t>
+  </si>
+  <si>
+    <t>Nederlands: A1; Frans: C2; Engels: A1; Duits: A1</t>
+  </si>
+  <si>
+    <t>Engels: B2; Frans: C2</t>
+  </si>
+  <si>
+    <t>Engels: C1; Duits: B1; Frans: B1</t>
   </si>
   <si>
     <t>Geen</t>
   </si>
   <si>
-    <t>Burgerlijk Kruis 1ste Klasse; Operatiemedaille ISAF</t>
-  </si>
-  <si>
-    <t>VAN RAEMDONCK A.Y. / 57-685829 / AB+</t>
-  </si>
-  <si>
-    <t>DEVOS C.K. / 52-986300 / A-</t>
-  </si>
-  <si>
-    <t>DE WITTE N.W. / 18-410320 / O+</t>
-  </si>
-  <si>
-    <t>PAUWELS M.I. / 67-410471 / AB-</t>
-  </si>
-  <si>
-    <t>MERCKX F.F. / 66-207391 / AB+</t>
-  </si>
-  <si>
-    <t>BE02919937663840</t>
-  </si>
-  <si>
-    <t>BE46311336849036</t>
-  </si>
-  <si>
-    <t>BE76276936901095</t>
-  </si>
-  <si>
-    <t>BE28908790062920</t>
-  </si>
-  <si>
-    <t>BE43030942136801</t>
-  </si>
-  <si>
-    <t>Desmedt BV</t>
-  </si>
-  <si>
-    <t>Deconinck NV</t>
-  </si>
-  <si>
-    <t>De Vos-Viaene NV</t>
-  </si>
-  <si>
-    <t>Merckx-De Clercq BV</t>
-  </si>
-  <si>
-    <t>Van den Broeck-Goossens NV</t>
-  </si>
-  <si>
-    <t>BE0758424689</t>
-  </si>
-  <si>
-    <t>BE0699904062</t>
-  </si>
-  <si>
-    <t>BE0373972322</t>
-  </si>
-  <si>
-    <t>BE0435694001</t>
-  </si>
-  <si>
-    <t>BE0105509989</t>
-  </si>
-  <si>
-    <t>5412475984672</t>
-  </si>
-  <si>
-    <t>8714530262884</t>
-  </si>
-  <si>
-    <t>8436276375504</t>
-  </si>
-  <si>
-    <t>8703370356846</t>
-  </si>
-  <si>
-    <t>3005243583966</t>
-  </si>
-  <si>
-    <t>900</t>
+    <t>Kruis van Ridder in de Leopoldsorde; Herinneringsmedaille Buitenlandse Operaties; Militair Kruis 2de Klasse</t>
+  </si>
+  <si>
+    <t>NATO Medal - Non Article 5; Burgerlijk Kruis 1ste Klasse; Militair Ereteken</t>
+  </si>
+  <si>
+    <t>Operatiemedaille ISAF; Herinneringsmedaille Humanitaire Operaties</t>
+  </si>
+  <si>
+    <t>LUYTEN L.P. / 22-385999 / AB+</t>
+  </si>
+  <si>
+    <t>VAN DE VOORDE N.Q. / 98-470894 / B-</t>
+  </si>
+  <si>
+    <t>DEGRYSE J.X. / 67-379700 / AB-</t>
+  </si>
+  <si>
+    <t>AERTS W.T. / 83-520927 / A-</t>
+  </si>
+  <si>
+    <t>DE BONDT H.W. / 52-390879 / A-</t>
+  </si>
+  <si>
+    <t>BE11245564060248</t>
+  </si>
+  <si>
+    <t>BE82394540862368</t>
+  </si>
+  <si>
+    <t>BE54897440333497</t>
+  </si>
+  <si>
+    <t>BE47692052376580</t>
+  </si>
+  <si>
+    <t>BE46300379195536</t>
+  </si>
+  <si>
+    <t>Saelens-Hendrickx NV</t>
+  </si>
+  <si>
+    <t>Jacobs-Goossens BV</t>
+  </si>
+  <si>
+    <t>Reynders CommV</t>
+  </si>
+  <si>
+    <t>Stas, Vaes en Wauters VOF</t>
+  </si>
+  <si>
+    <t>Janssens, Bracke en Janssens CommV</t>
+  </si>
+  <si>
+    <t>BE0436107732</t>
+  </si>
+  <si>
+    <t>BE0782248463</t>
+  </si>
+  <si>
+    <t>BE0784174501</t>
+  </si>
+  <si>
+    <t>BE0922958120</t>
+  </si>
+  <si>
+    <t>BE0241257814</t>
+  </si>
+  <si>
+    <t>5412089472879</t>
+  </si>
+  <si>
+    <t>8705468286912</t>
+  </si>
+  <si>
+    <t>5412937077256</t>
+  </si>
+  <si>
+    <t>8433702277623</t>
+  </si>
+  <si>
+    <t>8701091828963</t>
+  </si>
+  <si>
+    <t>400</t>
   </si>
   <si>
     <t>800</t>
   </si>
   <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>0544064597</t>
+  </si>
+  <si>
+    <t>0858258090</t>
+  </si>
+  <si>
+    <t>0120350743</t>
+  </si>
+  <si>
+    <t>0361295966</t>
+  </si>
+  <si>
+    <t>0359906775</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>08.08.2023</t>
+  </si>
+  <si>
+    <t>10.07.2025</t>
+  </si>
+  <si>
+    <t>19.07.2025</t>
+  </si>
+  <si>
+    <t>31.03.2025</t>
+  </si>
+  <si>
+    <t>06.05.2025</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>ERS-425908</t>
+  </si>
+  <si>
+    <t>ERS-314939</t>
+  </si>
+  <si>
+    <t>MAT-447990</t>
+  </si>
+  <si>
+    <t>MAT-531113</t>
+  </si>
+  <si>
+    <t>FRT-129043</t>
+  </si>
+  <si>
+    <t>Industrieel Sensor</t>
+  </si>
+  <si>
+    <t>Standaard Filter element</t>
+  </si>
+  <si>
+    <t>Standaard Sensor</t>
+  </si>
+  <si>
+    <t>Premium Pomp onderdeel</t>
+  </si>
+  <si>
+    <t>Premium Beschermkap</t>
+  </si>
+  <si>
+    <t>001 - Grondstoffen</t>
+  </si>
+  <si>
+    <t>007 - Elektronica</t>
+  </si>
+  <si>
+    <t>002 - Hulpstoffen</t>
+  </si>
+  <si>
+    <t>012 - Chemicaliën</t>
+  </si>
+  <si>
+    <t>006 - Technisch materiaal</t>
+  </si>
+  <si>
+    <t>NLAG - Niet-voorraad</t>
+  </si>
+  <si>
+    <t>HIBE - Bedrijfsmiddel</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>0000499303</t>
+  </si>
+  <si>
+    <t>0000897712</t>
+  </si>
+  <si>
+    <t>0000609402</t>
+  </si>
+  <si>
+    <t>0000419596</t>
+  </si>
+  <si>
+    <t>0000904901</t>
+  </si>
+  <si>
+    <t>De Vuyst CommV</t>
+  </si>
+  <si>
+    <t>Derycke, Schepens en Leys BV</t>
+  </si>
+  <si>
+    <t>Rosseel, De Clercq en Janssens VOF</t>
+  </si>
+  <si>
+    <t>Jacobs NV</t>
+  </si>
+  <si>
+    <t>Van Hove BV</t>
+  </si>
+  <si>
+    <t>4525422224</t>
+  </si>
+  <si>
+    <t>4566754847</t>
+  </si>
+  <si>
+    <t>4543178121</t>
+  </si>
+  <si>
+    <t>4525594336</t>
+  </si>
+  <si>
+    <t>4599676212</t>
+  </si>
+  <si>
+    <t>00080</t>
+  </si>
+  <si>
+    <t>00040</t>
+  </si>
+  <si>
+    <t>00100</t>
+  </si>
+  <si>
+    <t>00130</t>
+  </si>
+  <si>
+    <t>002 - Inkoop Technisch</t>
+  </si>
+  <si>
+    <t>001 - Inkoop Algemeen</t>
+  </si>
+  <si>
+    <t>003 - Inkoop IT</t>
+  </si>
+  <si>
+    <t>3142.29</t>
+  </si>
+  <si>
+    <t>3985.82</t>
+  </si>
+  <si>
+    <t>3876.18</t>
+  </si>
+  <si>
+    <t>1903.10</t>
+  </si>
+  <si>
+    <t>1313.88</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>ROL</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>PAL</t>
+  </si>
+  <si>
+    <t>29773.96</t>
+  </si>
+  <si>
+    <t>35535.44</t>
+  </si>
+  <si>
+    <t>40170.78</t>
+  </si>
+  <si>
+    <t>29136.71</t>
+  </si>
+  <si>
+    <t>48288.77</t>
+  </si>
+  <si>
+    <t>5010998202</t>
+  </si>
+  <si>
+    <t>5046021608</t>
+  </si>
+  <si>
+    <t>5022880341</t>
+  </si>
+  <si>
+    <t>5063441235</t>
+  </si>
+  <si>
+    <t>5010471049</t>
+  </si>
+  <si>
+    <t>5142853137</t>
+  </si>
+  <si>
+    <t>5181032774</t>
+  </si>
+  <si>
+    <t>5111686777</t>
+  </si>
+  <si>
+    <t>5196154473</t>
+  </si>
+  <si>
+    <t>5122599690</t>
+  </si>
+  <si>
+    <t>101 - Goederenontvangst PO</t>
+  </si>
+  <si>
+    <t>262 - Retour verbruik PO</t>
+  </si>
+  <si>
+    <t>601 - Goederenuitgifte levering</t>
+  </si>
+  <si>
+    <t>202 - Retour verbruik</t>
+  </si>
+  <si>
+    <t>602 - Retour goederenuitgifte</t>
+  </si>
+  <si>
+    <t>B20261630</t>
+  </si>
+  <si>
+    <t>B20240173</t>
+  </si>
+  <si>
+    <t>B20232385</t>
+  </si>
+  <si>
+    <t>B20265391</t>
+  </si>
+  <si>
+    <t>B20254985</t>
+  </si>
+  <si>
+    <t>7900</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>3010</t>
+  </si>
+  <si>
+    <t>VV - Handmatig</t>
+  </si>
+  <si>
+    <t>V1 - Automatisch herbestelpunt</t>
+  </si>
+  <si>
+    <t>PD - MRP</t>
+  </si>
+  <si>
+    <t>ND - Geen planning</t>
+  </si>
+  <si>
+    <t>0000928345</t>
+  </si>
+  <si>
+    <t>0000558511</t>
+  </si>
+  <si>
+    <t>0000421403</t>
+  </si>
+  <si>
+    <t>0000886367</t>
+  </si>
+  <si>
+    <t>0000149524</t>
+  </si>
+  <si>
+    <t>Goris NV</t>
+  </si>
+  <si>
+    <t>Van Damme, Colman en Meeus VOF</t>
+  </si>
+  <si>
+    <t>Van den Bossche, De Laet en De Meyer NV</t>
+  </si>
+  <si>
+    <t>Vervaet, De Keyser en Lievens NV</t>
+  </si>
+  <si>
+    <t>Roels, Bauwens en Willems CV</t>
+  </si>
+  <si>
+    <t>0825595745</t>
+  </si>
+  <si>
+    <t>0929360113</t>
+  </si>
+  <si>
+    <t>0848044560</t>
+  </si>
+  <si>
+    <t>0980343290</t>
+  </si>
+  <si>
+    <t>0966190434</t>
+  </si>
+  <si>
+    <t>000110</t>
+  </si>
+  <si>
+    <t>000150</t>
+  </si>
+  <si>
+    <t>000250</t>
+  </si>
+  <si>
+    <t>000290</t>
+  </si>
+  <si>
+    <t>000120</t>
+  </si>
+  <si>
+    <t>10 - Directe verkoop</t>
+  </si>
+  <si>
+    <t>20 - Groothandel</t>
+  </si>
+  <si>
+    <t>50 - Overheid</t>
+  </si>
+  <si>
+    <t>30 - Detailhandel</t>
+  </si>
+  <si>
+    <t>04 - Consulting</t>
+  </si>
+  <si>
+    <t>02 - Diensten</t>
+  </si>
+  <si>
+    <t>0004 - Verzendpunt Gent</t>
+  </si>
+  <si>
+    <t>0003 - Verzendpunt Luik</t>
+  </si>
+  <si>
+    <t>0002 - Verzendpunt Brussel</t>
+  </si>
+  <si>
+    <t>8027272437</t>
+  </si>
+  <si>
+    <t>8043445458</t>
+  </si>
+  <si>
+    <t>8053531759</t>
+  </si>
+  <si>
+    <t>8046326740</t>
+  </si>
+  <si>
+    <t>8053853641</t>
+  </si>
+  <si>
+    <t>9080888441</t>
+  </si>
+  <si>
+    <t>9093293868</t>
+  </si>
+  <si>
+    <t>9013895326</t>
+  </si>
+  <si>
+    <t>9071185859</t>
+  </si>
+  <si>
+    <t>9037122139</t>
+  </si>
+  <si>
+    <t>RB00</t>
+  </si>
+  <si>
+    <t>K007</t>
+  </si>
+  <si>
+    <t>MWST</t>
+  </si>
+  <si>
+    <t>K005</t>
+  </si>
+  <si>
+    <t>CIF</t>
+  </si>
+  <si>
+    <t>DDP</t>
+  </si>
+  <si>
+    <t>FCA</t>
+  </si>
+  <si>
+    <t>ZB02 - Netto 30 dagen</t>
+  </si>
+  <si>
+    <t>ZB05 - Vooruitbetaling</t>
+  </si>
+  <si>
+    <t>ZB06 - Netto 45 dagen</t>
+  </si>
+  <si>
+    <t>ZB04 - 2% 10d, netto 30d</t>
+  </si>
+  <si>
+    <t>06 - Defensie</t>
+  </si>
+  <si>
+    <t>01 - Industrie</t>
+  </si>
+  <si>
+    <t>05 - Non-profit</t>
+  </si>
+  <si>
+    <t>02 - Handel</t>
+  </si>
+  <si>
+    <t>BE01 - Vlaanderen</t>
+  </si>
+  <si>
+    <t>DE01 - West</t>
+  </si>
+  <si>
+    <t>BE02 - Wallonië</t>
+  </si>
+  <si>
+    <t>NL01 - Randstad</t>
+  </si>
+  <si>
+    <t>530000</t>
+  </si>
+  <si>
+    <t>410000</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>Crediteuren</t>
+  </si>
+  <si>
+    <t>Grondstofkosten</t>
+  </si>
+  <si>
+    <t>Afschrijvingskosten</t>
+  </si>
+  <si>
+    <t>Overige kosten</t>
+  </si>
+  <si>
+    <t>Kapitaal</t>
+  </si>
+  <si>
+    <t>2100 - Kwaliteit</t>
+  </si>
+  <si>
+    <t>1000 - Directie</t>
+  </si>
+  <si>
+    <t>3000 - Verkoop</t>
+  </si>
+  <si>
+    <t>3100 - Marketing</t>
+  </si>
+  <si>
+    <t>2000 - Productie</t>
+  </si>
+  <si>
+    <t>PC6117</t>
+  </si>
+  <si>
+    <t>PC3484</t>
+  </si>
+  <si>
+    <t>PC5517</t>
+  </si>
+  <si>
+    <t>PC3784</t>
+  </si>
+  <si>
+    <t>PC1833</t>
+  </si>
+  <si>
+    <t>KG - Leverancierscreditnota</t>
+  </si>
+  <si>
+    <t>DG - Klantcreditnota</t>
+  </si>
+  <si>
+    <t>SA - Grootboekdocument</t>
+  </si>
+  <si>
+    <t>S - Debet</t>
+  </si>
+  <si>
+    <t>H - Credit</t>
+  </si>
+  <si>
+    <t>80791.72</t>
+  </si>
+  <si>
+    <t>38568.40</t>
+  </si>
+  <si>
+    <t>23422.80</t>
+  </si>
+  <si>
+    <t>453210.42</t>
+  </si>
+  <si>
+    <t>187408.01</t>
+  </si>
+  <si>
+    <t>V1 - 6% BTW</t>
+  </si>
+  <si>
+    <t>V0 - 0% BTW binnenland</t>
+  </si>
+  <si>
+    <t>VX - BTW intracommunautair</t>
+  </si>
+  <si>
+    <t>V5 - 21% BTW verlegging</t>
+  </si>
+  <si>
+    <t>0347088766</t>
+  </si>
+  <si>
+    <t>0883718650</t>
+  </si>
+  <si>
+    <t>0648025652</t>
+  </si>
+  <si>
+    <t>0571236327</t>
+  </si>
+  <si>
+    <t>2000 - Support</t>
+  </si>
+  <si>
+    <t>3000 - Defensie</t>
+  </si>
+  <si>
+    <t>880186</t>
+  </si>
+  <si>
+    <t>822900</t>
+  </si>
+  <si>
+    <t>861911</t>
+  </si>
+  <si>
+    <t>884573</t>
+  </si>
+  <si>
+    <t>885271</t>
+  </si>
+  <si>
+    <t>410000 - Externe diensten</t>
+  </si>
+  <si>
+    <t>440000 - Overige kosten</t>
+  </si>
+  <si>
+    <t>420000 - Loonkosten</t>
+  </si>
+  <si>
+    <t>430000 - Afschrijvingen</t>
+  </si>
+  <si>
+    <t>1420 - Manuren</t>
+  </si>
+  <si>
+    <t>1430 - Reparatie-uren</t>
+  </si>
+  <si>
+    <t>1440 - Setup-uren</t>
+  </si>
+  <si>
+    <t>P-6017.3.06</t>
+  </si>
+  <si>
+    <t>P-4961.4.06</t>
+  </si>
+  <si>
+    <t>P-9763.3.08</t>
+  </si>
+  <si>
+    <t>P-9598.5.04</t>
+  </si>
+  <si>
+    <t>P-5968.4.05</t>
+  </si>
+  <si>
+    <t>00038688</t>
+  </si>
+  <si>
+    <t>00082433</t>
+  </si>
+  <si>
+    <t>00057563</t>
+  </si>
+  <si>
+    <t>00042441</t>
+  </si>
+  <si>
+    <t>00084810</t>
+  </si>
+  <si>
+    <t>BE20 - België Antwerpen</t>
+  </si>
+  <si>
+    <t>BE30 - België Luik</t>
+  </si>
+  <si>
+    <t>NL10 - Nederland</t>
+  </si>
+  <si>
+    <t>BE10 - België Brussel</t>
+  </si>
+  <si>
+    <t>0001 - Hoofdkantoor</t>
+  </si>
+  <si>
+    <t>0002 - Filiaal</t>
+  </si>
+  <si>
+    <t>0004 - Productie</t>
+  </si>
+  <si>
+    <t>5 - Stagiair</t>
+  </si>
+  <si>
+    <t>2 - Gepensioneerd</t>
+  </si>
+  <si>
+    <t>4 - Extern</t>
+  </si>
+  <si>
+    <t>3 - Tijdelijk</t>
+  </si>
+  <si>
+    <t>04 - Deeltijds bepaalde duur</t>
+  </si>
+  <si>
+    <t>01 - Voltijds onbepaalde duur</t>
+  </si>
+  <si>
+    <t>05 - Interimkracht</t>
+  </si>
+  <si>
+    <t>51018408</t>
+  </si>
+  <si>
+    <t>56624618</t>
+  </si>
+  <si>
+    <t>53117827</t>
+  </si>
+  <si>
+    <t>52787044</t>
+  </si>
+  <si>
+    <t>52167815</t>
+  </si>
+  <si>
+    <t>50000008 - Analist</t>
+  </si>
+  <si>
+    <t>50000001 - Manager Afdeling</t>
+  </si>
+  <si>
+    <t>50000005 - Junior Medewerker</t>
+  </si>
+  <si>
+    <t>50000002 - Teamleider</t>
+  </si>
+  <si>
+    <t>50000001 - Manager</t>
+  </si>
+  <si>
+    <t>50000002 - Ingenieur</t>
+  </si>
+  <si>
+    <t>50000003 - Technicus</t>
+  </si>
+  <si>
+    <t>50000005 - Consultant</t>
+  </si>
+  <si>
+    <t>W1 - Tweewekelijks</t>
+  </si>
+  <si>
+    <t>01 - Standaard</t>
+  </si>
+  <si>
+    <t>B1 - Maandelijks bedienden</t>
+  </si>
+  <si>
+    <t>3000 - Kilometervergoeding</t>
+  </si>
+  <si>
+    <t>1200 - Nachtpremie</t>
+  </si>
+  <si>
+    <t>3100 - Verplaatsingsvergoeding</t>
+  </si>
+  <si>
+    <t>2000 - Eindejaarspremie</t>
+  </si>
+  <si>
+    <t>1400 - Gevarentoelage</t>
+  </si>
+  <si>
+    <t>0002 - Persoonlijke gegevens</t>
+  </si>
+  <si>
+    <t>2006 - Afwezigheidsquota</t>
+  </si>
+  <si>
+    <t>0006 - Adressen</t>
+  </si>
+  <si>
+    <t>0009 - Bankgegevens</t>
+  </si>
+  <si>
+    <t>0008 - Basisbetalingen</t>
+  </si>
+  <si>
+    <t>6056454938</t>
+  </si>
+  <si>
+    <t>6017433034</t>
+  </si>
+  <si>
+    <t>6040928158</t>
+  </si>
+  <si>
+    <t>6070265198</t>
+  </si>
+  <si>
+    <t>6039346039</t>
+  </si>
+  <si>
+    <t>93142057</t>
+  </si>
+  <si>
+    <t>31049270</t>
+  </si>
+  <si>
+    <t>48804894</t>
+  </si>
+  <si>
+    <t>50172916</t>
+  </si>
+  <si>
+    <t>24465164</t>
+  </si>
+  <si>
+    <t>02241416</t>
+  </si>
+  <si>
+    <t>04540890</t>
+  </si>
+  <si>
+    <t>05037435</t>
+  </si>
+  <si>
+    <t>07891517</t>
+  </si>
+  <si>
+    <t>05140668</t>
+  </si>
+  <si>
+    <t>MC-02 - CNC Draaibank 2</t>
+  </si>
+  <si>
+    <t>AS-01 - Assemblagelijn 1</t>
+  </si>
+  <si>
+    <t>PK-01 - Verpakkingslijn 1</t>
+  </si>
+  <si>
+    <t>MT-01 - Onderhoudswerkplaats</t>
+  </si>
+  <si>
+    <t>0022349039</t>
+  </si>
+  <si>
+    <t>0054325062</t>
+  </si>
+  <si>
+    <t>0033261971</t>
+  </si>
+  <si>
+    <t>0051189248</t>
+  </si>
+  <si>
+    <t>0046180522</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>0021612170</t>
+  </si>
+  <si>
+    <t>0036662291</t>
+  </si>
+  <si>
+    <t>0020865790</t>
+  </si>
+  <si>
+    <t>0051129177</t>
+  </si>
+  <si>
+    <t>0073634939</t>
+  </si>
+  <si>
+    <t>ANT-06-01-015</t>
+  </si>
+  <si>
+    <t>GNT-03-02-018</t>
+  </si>
+  <si>
+    <t>LIE-10-04-044</t>
+  </si>
+  <si>
+    <t>LIE-07-04-003</t>
+  </si>
+  <si>
+    <t>ANT-07-02-039</t>
+  </si>
+  <si>
+    <t>4023563592</t>
+  </si>
+  <si>
+    <t>4018091542</t>
+  </si>
+  <si>
+    <t>4054959919</t>
+  </si>
+  <si>
+    <t>4081532388</t>
+  </si>
+  <si>
+    <t>4040627230</t>
+  </si>
+  <si>
+    <t>1060645619</t>
+  </si>
+  <si>
+    <t>1082631078</t>
+  </si>
+  <si>
+    <t>1051756596</t>
+  </si>
+  <si>
+    <t>1039940526</t>
+  </si>
+  <si>
+    <t>1024217801</t>
+  </si>
+  <si>
+    <t>MP924550</t>
+  </si>
+  <si>
+    <t>MP840535</t>
+  </si>
+  <si>
+    <t>MP809307</t>
+  </si>
+  <si>
+    <t>MP500322</t>
+  </si>
+  <si>
+    <t>MP339019</t>
+  </si>
+  <si>
+    <t>IFLOT - Technische plaats</t>
+  </si>
+  <si>
+    <t>IFLO - Functionele locatie</t>
+  </si>
+  <si>
+    <t>EQKT - Equipment</t>
+  </si>
+  <si>
+    <t>000268750254</t>
+  </si>
+  <si>
+    <t>000948750053</t>
+  </si>
+  <si>
+    <t>000775992567</t>
+  </si>
+  <si>
+    <t>000596165385</t>
+  </si>
+  <si>
+    <t>000426949987</t>
+  </si>
+  <si>
+    <t>IP-46517</t>
+  </si>
+  <si>
+    <t>IP-47455</t>
+  </si>
+  <si>
+    <t>IP-53168</t>
+  </si>
+  <si>
+    <t>IP-53571</t>
+  </si>
+  <si>
+    <t>IP-64869</t>
+  </si>
+  <si>
+    <t>1 - Foutsoorten</t>
+  </si>
+  <si>
+    <t>3 - Maatregelen</t>
+  </si>
+  <si>
+    <t>2 - Foutoorzaken</t>
+  </si>
+  <si>
+    <t>A2 - Aanvaard na herbewerking</t>
+  </si>
+  <si>
+    <t>A1 - Aanvaard met beperkingen</t>
+  </si>
+  <si>
+    <t>R - Afgekeurd</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>1300</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>0647689605</t>
-  </si>
-  <si>
-    <t>0896583550</t>
-  </si>
-  <si>
-    <t>0629536596</t>
-  </si>
-  <si>
-    <t>0361905644</t>
-  </si>
-  <si>
-    <t>0757096815</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>08.07.2023</t>
-  </si>
-  <si>
-    <t>09.09.2023</t>
-  </si>
-  <si>
-    <t>24.02.2026</t>
-  </si>
-  <si>
-    <t>31.01.2023</t>
-  </si>
-  <si>
-    <t>14.07.2023</t>
-  </si>
-  <si>
-    <t>CHF</t>
-  </si>
-  <si>
-    <t>SEK</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>FR</t>
-  </si>
-  <si>
-    <t>FRT-388911</t>
-  </si>
-  <si>
-    <t>MAT-695675</t>
-  </si>
-  <si>
-    <t>HLB-792328</t>
-  </si>
-  <si>
-    <t>HLB-475239</t>
-  </si>
-  <si>
-    <t>HLB-191307</t>
-  </si>
-  <si>
-    <t>Premium Klep DN50</t>
-  </si>
-  <si>
-    <t>Industrieel Plaat 2mm staal</t>
-  </si>
-  <si>
-    <t>Speciaal Bout M8x40</t>
-  </si>
-  <si>
-    <t>Technisch Buis 100mm</t>
-  </si>
-  <si>
-    <t>Industrieel Reinigingsmiddel</t>
-  </si>
-  <si>
-    <t>002 - Hulpstoffen</t>
-  </si>
-  <si>
-    <t>003 - Verpakkingsmateriaal</t>
-  </si>
-  <si>
-    <t>008 - Reserveonderdelen</t>
-  </si>
-  <si>
-    <t>012 - Chemicaliën</t>
-  </si>
-  <si>
-    <t>ERSA - Reserveonderdeel</t>
-  </si>
-  <si>
-    <t>ROH - Grondstof</t>
-  </si>
-  <si>
-    <t>DIEN - Dienst</t>
-  </si>
-  <si>
-    <t>FERT - Eindproduct</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>0000456370</t>
-  </si>
-  <si>
-    <t>0000114491</t>
-  </si>
-  <si>
-    <t>0000793262</t>
-  </si>
-  <si>
-    <t>0000804348</t>
-  </si>
-  <si>
-    <t>0000349889</t>
-  </si>
-  <si>
-    <t>Troch, Beernaert en Blondeel CommV</t>
-  </si>
-  <si>
-    <t>Rombouts-Borremans CV</t>
-  </si>
-  <si>
-    <t>Bogaert-Dewaele CV</t>
-  </si>
-  <si>
-    <t>Van Dyck BV</t>
-  </si>
-  <si>
-    <t>De Jonghe VOF</t>
-  </si>
-  <si>
-    <t>4585503332</t>
-  </si>
-  <si>
-    <t>4571632517</t>
-  </si>
-  <si>
-    <t>4543894700</t>
-  </si>
-  <si>
-    <t>4537373418</t>
-  </si>
-  <si>
-    <t>4599437834</t>
-  </si>
-  <si>
-    <t>00090</t>
-  </si>
-  <si>
-    <t>00130</t>
-  </si>
-  <si>
-    <t>00040</t>
-  </si>
-  <si>
-    <t>00030</t>
-  </si>
-  <si>
-    <t>00010</t>
-  </si>
-  <si>
-    <t>005 - Inkoop Logistiek</t>
-  </si>
-  <si>
-    <t>003 - Inkoop IT</t>
-  </si>
-  <si>
-    <t>002 - Inkoop Technisch</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2133.10</t>
-  </si>
-  <si>
-    <t>3280.98</t>
-  </si>
-  <si>
-    <t>1606.20</t>
-  </si>
-  <si>
-    <t>2457.16</t>
-  </si>
-  <si>
-    <t>488.77</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>PAL</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>16905.32</t>
-  </si>
-  <si>
-    <t>38336.00</t>
-  </si>
-  <si>
-    <t>2494.12</t>
-  </si>
-  <si>
-    <t>41768.71</t>
-  </si>
-  <si>
-    <t>9727.09</t>
-  </si>
-  <si>
-    <t>5099420758</t>
-  </si>
-  <si>
-    <t>5088688213</t>
-  </si>
-  <si>
-    <t>5047935871</t>
-  </si>
-  <si>
-    <t>5048508373</t>
-  </si>
-  <si>
-    <t>5080951734</t>
-  </si>
-  <si>
-    <t>5121405842</t>
-  </si>
-  <si>
-    <t>5135741672</t>
-  </si>
-  <si>
-    <t>5131912357</t>
-  </si>
-  <si>
-    <t>5131376387</t>
-  </si>
-  <si>
-    <t>5163298053</t>
-  </si>
-  <si>
-    <t>102 - Retour GR PO</t>
-  </si>
-  <si>
-    <t>501 - Goederenontvangst zonder PO</t>
-  </si>
-  <si>
-    <t>651 - Afschrijving</t>
-  </si>
-  <si>
-    <t>301 - Overplaatsing werk-werk</t>
-  </si>
-  <si>
-    <t>B20260023</t>
-  </si>
-  <si>
-    <t>B20252652</t>
-  </si>
-  <si>
-    <t>B20236472</t>
-  </si>
-  <si>
-    <t>B20231452</t>
-  </si>
-  <si>
-    <t>B20243278</t>
-  </si>
-  <si>
-    <t>7920</t>
-  </si>
-  <si>
-    <t>3020</t>
-  </si>
-  <si>
-    <t>7900</t>
-  </si>
-  <si>
-    <t>PD - MRP</t>
-  </si>
-  <si>
-    <t>ND - Geen planning</t>
-  </si>
-  <si>
-    <t>V1 - Automatisch herbestelpunt</t>
-  </si>
-  <si>
-    <t>0000344487</t>
-  </si>
-  <si>
-    <t>0000119744</t>
-  </si>
-  <si>
-    <t>0000336336</t>
-  </si>
-  <si>
-    <t>0000465682</t>
-  </si>
-  <si>
-    <t>0000256339</t>
-  </si>
-  <si>
-    <t>Wouters-Van Gorp CV</t>
-  </si>
-  <si>
-    <t>De Bruyne, De Block en Desmet CV</t>
-  </si>
-  <si>
-    <t>Van Loo, Van den Bergh en Janssens CommV</t>
-  </si>
-  <si>
-    <t>Callebaut, Merckx en Heymans CV</t>
-  </si>
-  <si>
-    <t>Daniels, De Smedt en Geuens VOF</t>
-  </si>
-  <si>
-    <t>0577961108</t>
-  </si>
-  <si>
-    <t>0475338875</t>
-  </si>
-  <si>
-    <t>0526174222</t>
-  </si>
-  <si>
-    <t>0703556658</t>
-  </si>
-  <si>
-    <t>0665428351</t>
-  </si>
-  <si>
-    <t>000300</t>
-  </si>
-  <si>
-    <t>000100</t>
-  </si>
-  <si>
-    <t>000170</t>
-  </si>
-  <si>
-    <t>000290</t>
-  </si>
-  <si>
-    <t>000270</t>
-  </si>
-  <si>
-    <t>50 - Overheid</t>
-  </si>
-  <si>
-    <t>30 - Detailhandel</t>
-  </si>
-  <si>
-    <t>20 - Groothandel</t>
-  </si>
-  <si>
-    <t>03 - Reserveonderdelen</t>
-  </si>
-  <si>
-    <t>02 - Diensten</t>
-  </si>
-  <si>
-    <t>01 - Producten</t>
-  </si>
-  <si>
-    <t>10 - Militair materieel</t>
-  </si>
-  <si>
-    <t>04 - Consulting</t>
-  </si>
-  <si>
-    <t>0004 - Verzendpunt Gent</t>
-  </si>
-  <si>
-    <t>0001 - Verzendpunt Antwerpen</t>
-  </si>
-  <si>
-    <t>8025172501</t>
-  </si>
-  <si>
-    <t>8043903344</t>
-  </si>
-  <si>
-    <t>8017861268</t>
-  </si>
-  <si>
-    <t>8031508085</t>
-  </si>
-  <si>
-    <t>8023986969</t>
-  </si>
-  <si>
-    <t>9053794750</t>
-  </si>
-  <si>
-    <t>9095228447</t>
-  </si>
-  <si>
-    <t>9064263757</t>
-  </si>
-  <si>
-    <t>9017334949</t>
-  </si>
-  <si>
-    <t>9045216053</t>
-  </si>
-  <si>
-    <t>PR00</t>
-  </si>
-  <si>
-    <t>K004</t>
-  </si>
-  <si>
-    <t>K007</t>
-  </si>
-  <si>
-    <t>K005</t>
-  </si>
-  <si>
-    <t>MWST</t>
-  </si>
-  <si>
-    <t>CIF</t>
-  </si>
-  <si>
-    <t>CIP</t>
-  </si>
-  <si>
-    <t>DDP</t>
-  </si>
-  <si>
-    <t>FAS</t>
-  </si>
-  <si>
-    <t>ZB01 - Netto 14 dagen</t>
-  </si>
-  <si>
-    <t>ZB02 - Netto 30 dagen</t>
-  </si>
-  <si>
-    <t>ZB04 - 2% 10d, netto 30d</t>
-  </si>
-  <si>
-    <t>04 - Particulier</t>
-  </si>
-  <si>
-    <t>03 - Overheid</t>
-  </si>
-  <si>
-    <t>06 - Defensie</t>
-  </si>
-  <si>
-    <t>BE01 - Vlaanderen</t>
-  </si>
-  <si>
-    <t>BE02 - Wallonië</t>
-  </si>
-  <si>
-    <t>NL01 - Randstad</t>
-  </si>
-  <si>
-    <t>140000</t>
-  </si>
-  <si>
-    <t>160000</t>
-  </si>
-  <si>
-    <t>510000</t>
-  </si>
-  <si>
-    <t>400000</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>Uitzonderlijke kosten</t>
-  </si>
-  <si>
-    <t>Opbrengsten verkoop</t>
-  </si>
-  <si>
-    <t>Overige kosten</t>
-  </si>
-  <si>
-    <t>Vorderingen op klanten</t>
-  </si>
-  <si>
-    <t>Kas</t>
-  </si>
-  <si>
-    <t>3100 - Marketing</t>
-  </si>
-  <si>
-    <t>1300 - IT</t>
-  </si>
-  <si>
-    <t>4000 - R&amp;D</t>
-  </si>
-  <si>
-    <t>3000 - Verkoop</t>
-  </si>
-  <si>
-    <t>PC4787</t>
-  </si>
-  <si>
-    <t>PC2618</t>
-  </si>
-  <si>
-    <t>PC3205</t>
-  </si>
-  <si>
-    <t>PC4393</t>
-  </si>
-  <si>
-    <t>PC9014</t>
-  </si>
-  <si>
-    <t>SA - Grootboekdocument</t>
-  </si>
-  <si>
-    <t>KG - Leverancierscreditnota</t>
-  </si>
-  <si>
-    <t>DG - Klantcreditnota</t>
-  </si>
-  <si>
-    <t>S - Debet</t>
-  </si>
-  <si>
-    <t>H - Credit</t>
-  </si>
-  <si>
-    <t>143442.46</t>
-  </si>
-  <si>
-    <t>26462.19</t>
-  </si>
-  <si>
-    <t>17736.90</t>
-  </si>
-  <si>
-    <t>90242.10</t>
-  </si>
-  <si>
-    <t>282104.89</t>
-  </si>
-  <si>
-    <t>V5 - 21% BTW verlegging</t>
-  </si>
-  <si>
-    <t>V3 - 21% BTW</t>
-  </si>
-  <si>
-    <t>VX - BTW intracommunautair</t>
-  </si>
-  <si>
-    <t>0804648420</t>
-  </si>
-  <si>
-    <t>0904976700</t>
-  </si>
-  <si>
-    <t>0539354509</t>
-  </si>
-  <si>
-    <t>1000 - Operations</t>
-  </si>
-  <si>
-    <t>3000 - Defensie</t>
-  </si>
-  <si>
-    <t>2000 - Support</t>
-  </si>
-  <si>
-    <t>849648</t>
-  </si>
-  <si>
-    <t>887529</t>
-  </si>
-  <si>
-    <t>801793</t>
-  </si>
-  <si>
-    <t>864780</t>
-  </si>
-  <si>
-    <t>839440</t>
-  </si>
-  <si>
-    <t>420000 - Loonkosten</t>
-  </si>
-  <si>
-    <t>440000 - Overige kosten</t>
-  </si>
-  <si>
-    <t>410000 - Externe diensten</t>
-  </si>
-  <si>
-    <t>1420 - Manuren</t>
-  </si>
-  <si>
-    <t>1440 - Setup-uren</t>
-  </si>
-  <si>
-    <t>1430 - Reparatie-uren</t>
-  </si>
-  <si>
-    <t>1410 - Machineuren</t>
-  </si>
-  <si>
-    <t>P-9637.4.09</t>
-  </si>
-  <si>
-    <t>P-8862.1.05</t>
-  </si>
-  <si>
-    <t>P-1983.4.04</t>
-  </si>
-  <si>
-    <t>P-3329.3.08</t>
-  </si>
-  <si>
-    <t>P-4804.4.09</t>
-  </si>
-  <si>
-    <t>00082005</t>
-  </si>
-  <si>
-    <t>00081261</t>
-  </si>
-  <si>
-    <t>00032047</t>
-  </si>
-  <si>
-    <t>00041845</t>
-  </si>
-  <si>
-    <t>00010604</t>
-  </si>
-  <si>
-    <t>BE10 - België Brussel</t>
-  </si>
-  <si>
-    <t>NL10 - Nederland</t>
-  </si>
-  <si>
-    <t>BE30 - België Luik</t>
-  </si>
-  <si>
-    <t>0003 - Magazijn</t>
-  </si>
-  <si>
-    <t>0004 - Productie</t>
-  </si>
-  <si>
-    <t>0001 - Hoofdkantoor</t>
-  </si>
-  <si>
-    <t>4 - Extern</t>
-  </si>
-  <si>
-    <t>1 - Actief</t>
-  </si>
-  <si>
-    <t>2 - Gepensioneerd</t>
-  </si>
-  <si>
-    <t>5 - Stagiair</t>
-  </si>
-  <si>
-    <t>02 - Deeltijds onbepaalde duur</t>
-  </si>
-  <si>
-    <t>05 - Interimkracht</t>
-  </si>
-  <si>
-    <t>01 - Voltijds onbepaalde duur</t>
-  </si>
-  <si>
-    <t>03 - Voltijds bepaalde duur</t>
-  </si>
-  <si>
-    <t>58180089</t>
-  </si>
-  <si>
-    <t>50891639</t>
-  </si>
-  <si>
-    <t>58159674</t>
-  </si>
-  <si>
-    <t>58313102</t>
-  </si>
-  <si>
-    <t>54047783</t>
-  </si>
-  <si>
-    <t>50000008 - Analist</t>
-  </si>
-  <si>
-    <t>50000003 - Senior Specialist</t>
-  </si>
-  <si>
-    <t>50000002 - Teamleider</t>
-  </si>
-  <si>
-    <t>50000005 - Junior Medewerker</t>
-  </si>
-  <si>
-    <t>50000002 - Ingenieur</t>
-  </si>
-  <si>
-    <t>50000004 - Administratief</t>
-  </si>
-  <si>
-    <t>50000007 - Operator</t>
-  </si>
-  <si>
-    <t>50000006 - Analist</t>
-  </si>
-  <si>
-    <t>B1 - Maandelijks bedienden</t>
-  </si>
-  <si>
-    <t>W1 - Tweewekelijks</t>
-  </si>
-  <si>
-    <t>01 - Standaard</t>
-  </si>
-  <si>
-    <t>B2 - Maandelijks arbeiders</t>
-  </si>
-  <si>
-    <t>3100 - Verplaatsingsvergoeding</t>
-  </si>
-  <si>
-    <t>2000 - Eindejaarspremie</t>
-  </si>
-  <si>
-    <t>1300 - Weekendpremie</t>
-  </si>
-  <si>
-    <t>1400 - Gevarentoelage</t>
-  </si>
-  <si>
-    <t>0007 - Geplande werktijd</t>
-  </si>
-  <si>
-    <t>2001 - Afwezigheden</t>
-  </si>
-  <si>
-    <t>0015 - Aanvullende betalingen</t>
-  </si>
-  <si>
-    <t>0014 - Periodieke betalingen/inhoudingen</t>
-  </si>
-  <si>
-    <t>0009 - Bankgegevens</t>
-  </si>
-  <si>
-    <t>6054538280</t>
-  </si>
-  <si>
-    <t>6048910321</t>
-  </si>
-  <si>
-    <t>6016189595</t>
-  </si>
-  <si>
-    <t>6089495570</t>
-  </si>
-  <si>
-    <t>6068879739</t>
-  </si>
-  <si>
-    <t>31938879</t>
-  </si>
-  <si>
-    <t>57448551</t>
-  </si>
-  <si>
-    <t>27271838</t>
-  </si>
-  <si>
-    <t>42178609</t>
-  </si>
-  <si>
-    <t>27048757</t>
-  </si>
-  <si>
-    <t>02734365</t>
-  </si>
-  <si>
-    <t>06619798</t>
-  </si>
-  <si>
-    <t>03469962</t>
-  </si>
-  <si>
-    <t>01282378</t>
-  </si>
-  <si>
-    <t>05250120</t>
-  </si>
-  <si>
-    <t>QC-01 - Kwaliteitscontrole 1</t>
-  </si>
-  <si>
-    <t>MC-01 - CNC Freesmachine 1</t>
-  </si>
-  <si>
-    <t>AS-01 - Assemblagelijn 1</t>
-  </si>
-  <si>
-    <t>PK-01 - Verpakkingslijn 1</t>
-  </si>
-  <si>
-    <t>MC-02 - CNC Draaibank 2</t>
-  </si>
-  <si>
-    <t>0065091067</t>
-  </si>
-  <si>
-    <t>0062956010</t>
-  </si>
-  <si>
-    <t>0044837444</t>
-  </si>
-  <si>
-    <t>0050608758</t>
-  </si>
-  <si>
-    <t>0035897872</t>
-  </si>
-  <si>
-    <t>0002</t>
-  </si>
-  <si>
-    <t>0003</t>
-  </si>
-  <si>
-    <t>0005</t>
-  </si>
-  <si>
-    <t>0001</t>
-  </si>
-  <si>
-    <t>0052054376</t>
-  </si>
-  <si>
-    <t>0042654991</t>
-  </si>
-  <si>
-    <t>0034065742</t>
-  </si>
-  <si>
-    <t>0083924734</t>
-  </si>
-  <si>
-    <t>0080172445</t>
-  </si>
-  <si>
-    <t>ANT-05-04-024</t>
-  </si>
-  <si>
-    <t>BRU-02-04-049</t>
-  </si>
-  <si>
-    <t>LIE-06-00-049</t>
-  </si>
-  <si>
-    <t>LIE-09-04-007</t>
-  </si>
-  <si>
-    <t>GNT-04-04-007</t>
-  </si>
-  <si>
-    <t>4097919143</t>
-  </si>
-  <si>
-    <t>4057756913</t>
-  </si>
-  <si>
-    <t>4065875852</t>
-  </si>
-  <si>
-    <t>4018563774</t>
-  </si>
-  <si>
-    <t>4024627010</t>
-  </si>
-  <si>
-    <t>1094797191</t>
-  </si>
-  <si>
-    <t>1032081886</t>
-  </si>
-  <si>
-    <t>1024553854</t>
-  </si>
-  <si>
-    <t>1057938679</t>
-  </si>
-  <si>
-    <t>1084734742</t>
-  </si>
-  <si>
-    <t>MP330774</t>
-  </si>
-  <si>
-    <t>MP522716</t>
-  </si>
-  <si>
-    <t>MP186809</t>
-  </si>
-  <si>
-    <t>MP158174</t>
-  </si>
-  <si>
-    <t>MP388735</t>
-  </si>
-  <si>
-    <t>IFLO - Functionele locatie</t>
-  </si>
-  <si>
-    <t>IFLOT - Technische plaats</t>
-  </si>
-  <si>
-    <t>EQUI - Equipment technisch</t>
-  </si>
-  <si>
-    <t>000892851689</t>
-  </si>
-  <si>
-    <t>000298550942</t>
-  </si>
-  <si>
-    <t>000189082374</t>
-  </si>
-  <si>
-    <t>000773484716</t>
-  </si>
-  <si>
-    <t>000552770892</t>
-  </si>
-  <si>
-    <t>IP-94413</t>
-  </si>
-  <si>
-    <t>IP-48201</t>
-  </si>
-  <si>
-    <t>IP-84858</t>
-  </si>
-  <si>
-    <t>IP-67187</t>
-  </si>
-  <si>
-    <t>IP-81316</t>
-  </si>
-  <si>
-    <t>9 - Kenmerken</t>
-  </si>
-  <si>
-    <t>5 - Activiteiten</t>
-  </si>
-  <si>
-    <t>3 - Maatregelen</t>
-  </si>
-  <si>
-    <t>R - Afgekeurd</t>
-  </si>
-  <si>
-    <t>A2 - Aanvaard na herbewerking</t>
-  </si>
-  <si>
-    <t>A - Aanvaard</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>002 - Vloeropslagplaats</t>
   </si>
   <si>
+    <t>005 - Buitenopslag</t>
+  </si>
+  <si>
     <t>001 - Hoogbouwmagazijn</t>
   </si>
   <si>
-    <t>003 - Stellingopslag</t>
-  </si>
-  <si>
-    <t>010 - Goederenontvangst</t>
-  </si>
-  <si>
-    <t>F-42-06</t>
-  </si>
-  <si>
-    <t>C-14-05</t>
-  </si>
-  <si>
-    <t>H-24-02</t>
-  </si>
-  <si>
-    <t>B-14-01</t>
-  </si>
-  <si>
-    <t>A-32-02</t>
-  </si>
-  <si>
-    <t>0000721034</t>
-  </si>
-  <si>
-    <t>0000840798</t>
-  </si>
-  <si>
-    <t>0000464181</t>
-  </si>
-  <si>
-    <t>0000681635</t>
-  </si>
-  <si>
-    <t>0000627319</t>
-  </si>
-  <si>
-    <t>HU97348974</t>
-  </si>
-  <si>
-    <t>HU77389251</t>
-  </si>
-  <si>
-    <t>HU91602429</t>
-  </si>
-  <si>
-    <t>HU60237979</t>
-  </si>
-  <si>
-    <t>HU18109580</t>
+    <t>D-18-04</t>
+  </si>
+  <si>
+    <t>H-11-06</t>
+  </si>
+  <si>
+    <t>A-49-06</t>
+  </si>
+  <si>
+    <t>A-25-04</t>
+  </si>
+  <si>
+    <t>H-35-04</t>
+  </si>
+  <si>
+    <t>0000885959</t>
+  </si>
+  <si>
+    <t>0000723759</t>
+  </si>
+  <si>
+    <t>0000909597</t>
+  </si>
+  <si>
+    <t>0000991139</t>
+  </si>
+  <si>
+    <t>0000611577</t>
+  </si>
+  <si>
+    <t>HU36851835</t>
+  </si>
+  <si>
+    <t>HU90925341</t>
+  </si>
+  <si>
+    <t>HU44061679</t>
+  </si>
+  <si>
+    <t>HU63408724</t>
+  </si>
+  <si>
+    <t>HU28124774</t>
+  </si>
+  <si>
+    <t>LOC_AMS_01</t>
+  </si>
+  <si>
+    <t>LOC_LIE_01</t>
   </si>
   <si>
     <t>DC_ANT_01</t>
   </si>
   <si>
-    <t>DC_BRU_01</t>
-  </si>
-  <si>
-    <t>LOC_GNT_01</t>
-  </si>
-  <si>
-    <t>LOC_ANT_01</t>
-  </si>
-  <si>
-    <t>SCM-906071</t>
-  </si>
-  <si>
-    <t>SCM-577824</t>
-  </si>
-  <si>
-    <t>SCM-596711</t>
-  </si>
-  <si>
-    <t>SCM-479296</t>
-  </si>
-  <si>
-    <t>SCM-884536</t>
-  </si>
-  <si>
-    <t>DP-2025-11</t>
-  </si>
-  <si>
-    <t>DP-2026-11</t>
-  </si>
-  <si>
-    <t>DP-2024-01</t>
-  </si>
-  <si>
-    <t>DP-2026-01</t>
-  </si>
-  <si>
-    <t>DP-2025-03</t>
+    <t>SCM-776961</t>
+  </si>
+  <si>
+    <t>SCM-583317</t>
+  </si>
+  <si>
+    <t>SCM-300372</t>
+  </si>
+  <si>
+    <t>SCM-825494</t>
+  </si>
+  <si>
+    <t>SCM-944719</t>
+  </si>
+  <si>
+    <t>DP-2026-09</t>
+  </si>
+  <si>
+    <t>DP-2024-04</t>
+  </si>
+  <si>
+    <t>DP-2026-03</t>
+  </si>
+  <si>
+    <t>DP-2026-02</t>
+  </si>
+  <si>
+    <t>ANT -&gt; LON</t>
+  </si>
+  <si>
+    <t>BRU -&gt; ROT</t>
+  </si>
+  <si>
+    <t>AMS -&gt; BRU</t>
+  </si>
+  <si>
+    <t>FRA -&gt; BRU</t>
   </si>
   <si>
     <t>FRA -&gt; ANT</t>
   </si>
   <si>
-    <t>LIE -&gt; ROT</t>
-  </si>
-  <si>
-    <t>ROT -&gt; AMS</t>
-  </si>
-  <si>
-    <t>ROT -&gt; FRA</t>
-  </si>
-  <si>
-    <t>PAR -&gt; LON</t>
-  </si>
-  <si>
-    <t>Vendor 0000651823</t>
-  </si>
-  <si>
-    <t>Vendor 0000962905</t>
-  </si>
-  <si>
-    <t>Vendor 0000822839</t>
-  </si>
-  <si>
-    <t>Vendor 0000398565</t>
-  </si>
-  <si>
-    <t>Vendor 0000918878</t>
-  </si>
-  <si>
-    <t>QA-6347</t>
-  </si>
-  <si>
-    <t>QA-7484</t>
-  </si>
-  <si>
-    <t>QA-8327</t>
-  </si>
-  <si>
-    <t>QA-5271</t>
-  </si>
-  <si>
-    <t>QA-2508</t>
-  </si>
-  <si>
-    <t>5557183868</t>
-  </si>
-  <si>
-    <t>5547821556</t>
-  </si>
-  <si>
-    <t>5540901445</t>
-  </si>
-  <si>
-    <t>5577194912</t>
-  </si>
-  <si>
-    <t>5556052107</t>
+    <t>Vendor 0000170849</t>
+  </si>
+  <si>
+    <t>Vendor 0000191030</t>
+  </si>
+  <si>
+    <t>Vendor 0000259924</t>
+  </si>
+  <si>
+    <t>Vendor 0000290648</t>
+  </si>
+  <si>
+    <t>Vendor 0000730954</t>
+  </si>
+  <si>
+    <t>QA-2722</t>
+  </si>
+  <si>
+    <t>QA-8935</t>
+  </si>
+  <si>
+    <t>QA-2301</t>
+  </si>
+  <si>
+    <t>QA-6503</t>
+  </si>
+  <si>
+    <t>QA-3259</t>
+  </si>
+  <si>
+    <t>5547172717</t>
+  </si>
+  <si>
+    <t>5521906271</t>
+  </si>
+  <si>
+    <t>5550619504</t>
+  </si>
+  <si>
+    <t>5542554282</t>
+  </si>
+  <si>
+    <t>5559185343</t>
+  </si>
+  <si>
+    <t>FSTD</t>
+  </si>
+  <si>
+    <t>FAUTO</t>
+  </si>
+  <si>
+    <t>FMAN</t>
   </si>
   <si>
     <t>FP02</t>
   </si>
   <si>
-    <t>FP01</t>
-  </si>
-  <si>
-    <t>FP03</t>
-  </si>
-  <si>
-    <t>FSTD</t>
-  </si>
-  <si>
-    <t>575211033547</t>
-  </si>
-  <si>
-    <t>957241656463</t>
-  </si>
-  <si>
-    <t>596739460941</t>
-  </si>
-  <si>
-    <t>284271096863</t>
-  </si>
-  <si>
-    <t>896187544052</t>
-  </si>
-  <si>
-    <t>5281311463</t>
-  </si>
-  <si>
-    <t>5968997420</t>
-  </si>
-  <si>
-    <t>9004983913</t>
-  </si>
-  <si>
-    <t>4839584397</t>
-  </si>
-  <si>
-    <t>9297892742</t>
-  </si>
-  <si>
-    <t>CO-572995</t>
-  </si>
-  <si>
-    <t>CO-169478</t>
-  </si>
-  <si>
-    <t>CO-438271</t>
-  </si>
-  <si>
-    <t>CO-174561</t>
-  </si>
-  <si>
-    <t>CO-373092</t>
-  </si>
-  <si>
-    <t>PR-153800</t>
-  </si>
-  <si>
-    <t>PR-417890</t>
-  </si>
-  <si>
-    <t>PR-968164</t>
-  </si>
-  <si>
-    <t>PR-109233</t>
-  </si>
-  <si>
-    <t>PR-608030</t>
-  </si>
-  <si>
-    <t>IN-5725234</t>
-  </si>
-  <si>
-    <t>IN-2184962</t>
-  </si>
-  <si>
-    <t>IN-5499988</t>
-  </si>
-  <si>
-    <t>IN-3269793</t>
-  </si>
-  <si>
-    <t>IN-4118587</t>
-  </si>
-  <si>
-    <t>ITR-91495707</t>
-  </si>
-  <si>
-    <t>SAG-42799018</t>
-  </si>
-  <si>
-    <t>SAG-75743473</t>
-  </si>
-  <si>
-    <t>SAG-32902729</t>
-  </si>
-  <si>
-    <t>ITR-20712049</t>
-  </si>
-  <si>
-    <t>REG-001</t>
+    <t>825789188668</t>
+  </si>
+  <si>
+    <t>342622384808</t>
+  </si>
+  <si>
+    <t>569173150068</t>
+  </si>
+  <si>
+    <t>574795293269</t>
+  </si>
+  <si>
+    <t>229651663077</t>
+  </si>
+  <si>
+    <t>3601426743</t>
+  </si>
+  <si>
+    <t>4181138191</t>
+  </si>
+  <si>
+    <t>3919223650</t>
+  </si>
+  <si>
+    <t>9926626988</t>
+  </si>
+  <si>
+    <t>4044732544</t>
+  </si>
+  <si>
+    <t>CO-512109</t>
+  </si>
+  <si>
+    <t>CO-596537</t>
+  </si>
+  <si>
+    <t>CO-248027</t>
+  </si>
+  <si>
+    <t>CO-802961</t>
+  </si>
+  <si>
+    <t>CO-895202</t>
+  </si>
+  <si>
+    <t>PR-847304</t>
+  </si>
+  <si>
+    <t>PR-459701</t>
+  </si>
+  <si>
+    <t>PR-236745</t>
+  </si>
+  <si>
+    <t>PR-754152</t>
+  </si>
+  <si>
+    <t>PR-265411</t>
+  </si>
+  <si>
+    <t>IN-1379801</t>
+  </si>
+  <si>
+    <t>IN-6096190</t>
+  </si>
+  <si>
+    <t>IN-5797634</t>
+  </si>
+  <si>
+    <t>IN-5914554</t>
+  </si>
+  <si>
+    <t>IN-7259217</t>
+  </si>
+  <si>
+    <t>SAG-42174851</t>
+  </si>
+  <si>
+    <t>LAN-76059567</t>
+  </si>
+  <si>
+    <t>LAN-68730890</t>
+  </si>
+  <si>
+    <t>LAN-67527192</t>
+  </si>
+  <si>
+    <t>ISK-57665984</t>
+  </si>
+  <si>
+    <t>REG-004</t>
+  </si>
+  <si>
+    <t>REG-003</t>
   </si>
   <si>
     <t>REG-002</t>
   </si>
   <si>
-    <t>REG-004</t>
-  </si>
-  <si>
-    <t>93881.0</t>
-  </si>
-  <si>
-    <t>80713.0</t>
-  </si>
-  <si>
-    <t>95934.0</t>
-  </si>
-  <si>
-    <t>41170.0</t>
-  </si>
-  <si>
-    <t>85132.0</t>
+    <t>63338.0</t>
+  </si>
+  <si>
+    <t>64666.0</t>
+  </si>
+  <si>
+    <t>42816.0</t>
+  </si>
+  <si>
+    <t>54879.0</t>
+  </si>
+  <si>
+    <t>18722.0</t>
+  </si>
+  <si>
+    <t>E1 - Elektriciteit dag</t>
+  </si>
+  <si>
+    <t>W1 - Water huishoudelijk</t>
   </si>
   <si>
     <t>G2 - Aardgas sociaal</t>
   </si>
   <si>
-    <t>E2 - Elektriciteit nacht</t>
-  </si>
-  <si>
-    <t>G1 - Aardgas normaal</t>
-  </si>
-  <si>
-    <t>E1 - Elektriciteit dag</t>
+    <t>04 - Warmte</t>
+  </si>
+  <si>
+    <t>02 - Aardgas</t>
+  </si>
+  <si>
+    <t>01 - Elektriciteit</t>
   </si>
   <si>
     <t>03 - Water</t>
   </si>
   <si>
-    <t>04 - Warmte</t>
-  </si>
-  <si>
-    <t>05 - Telecommunicatie</t>
-  </si>
-  <si>
-    <t>05.01.2019</t>
-  </si>
-  <si>
-    <t>16.04.2017</t>
-  </si>
-  <si>
-    <t>26.07.2024</t>
-  </si>
-  <si>
-    <t>19.12.2020</t>
-  </si>
-  <si>
-    <t>07.11.2021</t>
-  </si>
-  <si>
-    <t>27.09.2024</t>
-  </si>
-  <si>
-    <t>05.09.2022</t>
-  </si>
-  <si>
-    <t>549587151894192901</t>
-  </si>
-  <si>
-    <t>542390666605856738</t>
-  </si>
-  <si>
-    <t>545200324403471002</t>
-  </si>
-  <si>
-    <t>547078702367283268</t>
-  </si>
-  <si>
-    <t>546809303858179621</t>
-  </si>
-  <si>
-    <t>9783 kWh</t>
-  </si>
-  <si>
-    <t>40949 kWh</t>
-  </si>
-  <si>
-    <t>30235 kWh</t>
-  </si>
-  <si>
-    <t>31453 kWh</t>
-  </si>
-  <si>
-    <t>20292 kWh</t>
-  </si>
-  <si>
-    <t>DEF-3736</t>
-  </si>
-  <si>
-    <t>PRJ-2558</t>
-  </si>
-  <si>
-    <t>IT-7287</t>
-  </si>
-  <si>
-    <t>DEF-8179</t>
-  </si>
-  <si>
-    <t>PRJ-9806</t>
-  </si>
-  <si>
-    <t>NW-594554</t>
-  </si>
-  <si>
-    <t>NW-809644</t>
-  </si>
-  <si>
-    <t>NW-531749</t>
-  </si>
-  <si>
-    <t>NW-606365</t>
-  </si>
-  <si>
-    <t>NW-781730</t>
-  </si>
-  <si>
-    <t>0460</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>0330</t>
-  </si>
-  <si>
-    <t>Fase 2 compleet</t>
-  </si>
-  <si>
-    <t>Prototype gereed</t>
-  </si>
-  <si>
-    <t>Fase 1 compleet</t>
+    <t>08.01.2020</t>
+  </si>
+  <si>
+    <t>19.03.2015</t>
+  </si>
+  <si>
+    <t>21.03.2021</t>
+  </si>
+  <si>
+    <t>02.11.2018</t>
+  </si>
+  <si>
+    <t>10.05.2020</t>
+  </si>
+  <si>
+    <t>10.11.2025</t>
+  </si>
+  <si>
+    <t>20.08.2018</t>
+  </si>
+  <si>
+    <t>544629302034207210</t>
+  </si>
+  <si>
+    <t>547747498235173332</t>
+  </si>
+  <si>
+    <t>547398753901678103</t>
+  </si>
+  <si>
+    <t>541500378336495876</t>
+  </si>
+  <si>
+    <t>541656198490770939</t>
+  </si>
+  <si>
+    <t>27701 kWh</t>
+  </si>
+  <si>
+    <t>45648 kWh</t>
+  </si>
+  <si>
+    <t>36664 kWh</t>
+  </si>
+  <si>
+    <t>10760 kWh</t>
+  </si>
+  <si>
+    <t>38139 kWh</t>
+  </si>
+  <si>
+    <t>PRJ-2007</t>
+  </si>
+  <si>
+    <t>INF-7682</t>
+  </si>
+  <si>
+    <t>IT-8209</t>
+  </si>
+  <si>
+    <t>IT-7063</t>
+  </si>
+  <si>
+    <t>DEF-1870</t>
+  </si>
+  <si>
+    <t>NW-629661</t>
+  </si>
+  <si>
+    <t>NW-931010</t>
+  </si>
+  <si>
+    <t>NW-592878</t>
+  </si>
+  <si>
+    <t>NW-318571</t>
+  </si>
+  <si>
+    <t>NW-457250</t>
+  </si>
+  <si>
+    <t>0130</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>Overdracht</t>
+  </si>
+  <si>
+    <t>Go-live</t>
+  </si>
+  <si>
+    <t>Projectstart</t>
   </si>
   <si>
     <t>Ontwerp goedgekeurd</t>
-  </si>
-  <si>
-    <t>Testfase compleet</t>
   </si>
   <si>
     <t>Kolomnaam</t>
@@ -3507,7 +3513,7 @@
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="15.7109375" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" customWidth="1"/>
@@ -3515,37 +3521,36 @@
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="24.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="31.7109375" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" customWidth="1"/>
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="24.7109375" customWidth="1"/>
     <col min="20" max="20" width="34.7109375" customWidth="1"/>
-    <col min="21" max="21" width="21.7109375" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" customWidth="1"/>
     <col min="22" max="22" width="22.7109375" customWidth="1"/>
     <col min="23" max="23" width="21.7109375" customWidth="1"/>
-    <col min="24" max="24" width="18.7109375" customWidth="1"/>
+    <col min="24" max="24" width="24.7109375" customWidth="1"/>
     <col min="25" max="25" width="12.7109375" customWidth="1"/>
     <col min="26" max="26" width="14.7109375" customWidth="1"/>
-    <col min="27" max="27" width="29.7109375" customWidth="1"/>
-    <col min="28" max="28" width="20.7109375" customWidth="1"/>
-    <col min="29" max="29" width="40.7109375" customWidth="1"/>
+    <col min="27" max="27" width="28.7109375" customWidth="1"/>
+    <col min="28" max="28" width="21.7109375" customWidth="1"/>
+    <col min="29" max="29" width="29.7109375" customWidth="1"/>
     <col min="30" max="30" width="28.7109375" customWidth="1"/>
     <col min="31" max="31" width="23.7109375" customWidth="1"/>
     <col min="32" max="32" width="24.7109375" customWidth="1"/>
     <col min="33" max="33" width="13.7109375" customWidth="1"/>
-    <col min="34" max="34" width="23.7109375" customWidth="1"/>
-    <col min="35" max="35" width="26.7109375" customWidth="1"/>
+    <col min="34" max="34" width="22.7109375" customWidth="1"/>
+    <col min="35" max="35" width="23.7109375" customWidth="1"/>
     <col min="36" max="36" width="12.7109375" customWidth="1"/>
-    <col min="37" max="37" width="27.7109375" customWidth="1"/>
-    <col min="38" max="38" width="21.7109375" customWidth="1"/>
-    <col min="39" max="39" width="30.7109375" customWidth="1"/>
-    <col min="40" max="40" width="39.7109375" customWidth="1"/>
-    <col min="41" max="41" width="40.7109375" customWidth="1"/>
-    <col min="42" max="42" width="38.7109375" customWidth="1"/>
+    <col min="37" max="37" width="26.7109375" customWidth="1"/>
+    <col min="38" max="38" width="22.7109375" customWidth="1"/>
+    <col min="39" max="39" width="27.7109375" customWidth="1"/>
+    <col min="40" max="41" width="40.7109375" customWidth="1"/>
+    <col min="42" max="42" width="37.7109375" customWidth="1"/>
     <col min="43" max="43" width="18.7109375" customWidth="1"/>
-    <col min="44" max="44" width="28.7109375" customWidth="1"/>
+    <col min="44" max="44" width="36.7109375" customWidth="1"/>
     <col min="45" max="45" width="14.7109375" customWidth="1"/>
     <col min="46" max="46" width="15.7109375" customWidth="1"/>
     <col min="47" max="47" width="21.7109375" customWidth="1"/>
@@ -3571,7 +3576,7 @@
     <col min="68" max="68" width="24.7109375" customWidth="1"/>
     <col min="69" max="69" width="31.7109375" customWidth="1"/>
     <col min="70" max="70" width="19.7109375" customWidth="1"/>
-    <col min="71" max="71" width="35.7109375" customWidth="1"/>
+    <col min="71" max="71" width="33.7109375" customWidth="1"/>
     <col min="72" max="72" width="25.7109375" customWidth="1"/>
     <col min="73" max="73" width="31.7109375" customWidth="1"/>
     <col min="74" max="74" width="32.7109375" customWidth="1"/>
@@ -3581,8 +3586,7 @@
     <col min="78" max="78" width="34.7109375" customWidth="1"/>
     <col min="79" max="79" width="32.7109375" customWidth="1"/>
     <col min="80" max="80" width="31.7109375" customWidth="1"/>
-    <col min="81" max="81" width="28.7109375" customWidth="1"/>
-    <col min="82" max="82" width="30.7109375" customWidth="1"/>
+    <col min="81" max="82" width="28.7109375" customWidth="1"/>
     <col min="83" max="84" width="21.7109375" customWidth="1"/>
     <col min="85" max="85" width="27.7109375" customWidth="1"/>
     <col min="86" max="86" width="15.7109375" customWidth="1"/>
@@ -3603,15 +3607,15 @@
     <col min="103" max="103" width="25.7109375" customWidth="1"/>
     <col min="104" max="104" width="34.7109375" customWidth="1"/>
     <col min="105" max="105" width="30.7109375" customWidth="1"/>
-    <col min="106" max="106" width="23.7109375" customWidth="1"/>
+    <col min="106" max="106" width="25.7109375" customWidth="1"/>
     <col min="107" max="107" width="34.7109375" customWidth="1"/>
     <col min="108" max="108" width="29.7109375" customWidth="1"/>
     <col min="109" max="110" width="33.7109375" customWidth="1"/>
     <col min="111" max="111" width="30.7109375" customWidth="1"/>
-    <col min="112" max="112" width="27.7109375" customWidth="1"/>
+    <col min="112" max="112" width="23.7109375" customWidth="1"/>
     <col min="113" max="113" width="28.7109375" customWidth="1"/>
     <col min="114" max="114" width="32.7109375" customWidth="1"/>
-    <col min="115" max="115" width="40.7109375" customWidth="1"/>
+    <col min="115" max="115" width="30.7109375" customWidth="1"/>
     <col min="116" max="116" width="20.7109375" customWidth="1"/>
     <col min="117" max="117" width="23.7109375" customWidth="1"/>
     <col min="118" max="118" width="28.7109375" customWidth="1"/>
@@ -3644,7 +3648,7 @@
     <col min="151" max="151" width="26.7109375" customWidth="1"/>
     <col min="152" max="152" width="21.7109375" customWidth="1"/>
     <col min="153" max="153" width="26.7109375" customWidth="1"/>
-    <col min="154" max="154" width="23.7109375" customWidth="1"/>
+    <col min="154" max="154" width="20.7109375" customWidth="1"/>
     <col min="155" max="155" width="22.7109375" customWidth="1"/>
     <col min="156" max="156" width="23.7109375" customWidth="1"/>
     <col min="157" max="157" width="37.7109375" customWidth="1"/>
@@ -4166,22 +4170,22 @@
         <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N2" t="s">
         <v>220</v>
@@ -4214,412 +4218,418 @@
         <v>265</v>
       </c>
       <c r="X2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AB2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AD2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AE2" t="s">
-        <v>301</v>
+        <v>304</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>309</v>
       </c>
       <c r="AG2" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="AH2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AI2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AJ2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AK2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AM2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AO2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AP2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AQ2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AR2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AS2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AT2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AU2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AV2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AW2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AX2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AY2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AZ2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="BA2" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="BB2" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="BC2" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="BD2" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="BE2" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="BF2" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="BG2" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="BH2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="BI2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="BJ2" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="BK2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="BL2" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="BM2" t="s">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="BN2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="BO2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="BP2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="BQ2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="BR2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="BS2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="BT2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="BU2" t="s">
-        <v>479</v>
+        <v>377</v>
       </c>
       <c r="BV2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="BW2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="BX2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="BY2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="BZ2" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="CA2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="CB2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="CC2" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="CD2" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="CE2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="CF2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="CG2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="CH2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="CI2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="CJ2" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="CK2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="CL2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="CM2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="CN2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="CO2" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="CP2" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="CQ2" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="CR2" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="CS2" t="s">
-        <v>572</v>
+        <v>580</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>584</v>
       </c>
       <c r="CU2" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="CV2" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="CW2" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="CX2" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="CY2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="CZ2" t="s">
-        <v>444</v>
+        <v>381</v>
       </c>
       <c r="DA2" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="DB2" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="DC2" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="DD2" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="DE2" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="DF2" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="DG2" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="DH2" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="DI2" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="DJ2" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="DK2" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="DL2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="DM2" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="DN2" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="DO2" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="DP2" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="DQ2" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="DR2" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="DS2" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="DT2" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="DU2" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="DV2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="DW2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="DX2" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="DY2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="DZ2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="EA2" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="EB2" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="EC2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="ED2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="EE2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="EF2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="EG2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="EH2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="EI2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="EJ2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="EK2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="EL2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="EM2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="EN2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="EO2" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="EP2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="EQ2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="ER2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="ES2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="ET2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="EU2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="EV2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="EW2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="EX2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="EY2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="FA2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="FB2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="FC2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="FD2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="FE2" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="FF2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:162">
@@ -4645,22 +4655,22 @@
         <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N3" t="s">
         <v>221</v>
@@ -4690,418 +4700,421 @@
         <v>261</v>
       </c>
       <c r="W3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="X3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AC3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AD3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AE3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AF3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG3" t="s">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="AH3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AI3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AJ3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AK3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AL3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AM3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AO3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AP3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AQ3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AR3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AS3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AT3" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AU3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AV3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AW3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AX3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AY3" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AZ3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="BA3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="BB3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="BC3" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="BD3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="BE3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="BF3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="BG3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="BH3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="BI3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="BJ3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="BK3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="BL3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="BM3" t="s">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="BN3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="BO3" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="BP3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="BQ3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="BR3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="BS3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="BT3" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="BU3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="BV3" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="BW3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="BX3" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="BY3" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="BZ3" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="CA3" t="s">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="CB3" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="CC3" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="CD3" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="CE3" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="CF3" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="CG3" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="CH3" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="CI3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="CJ3" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="CK3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="CL3" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="CM3" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="CN3" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="CO3" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="CP3" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="CQ3" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="CR3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="CS3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="CU3" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="CV3" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="CW3" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="CX3" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="CY3" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="CZ3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="DA3" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="DB3" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="DC3" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="DD3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="DE3" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="DF3" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="DG3" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="DH3" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="DI3" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="DJ3" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="DK3" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="DL3" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="DM3" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="DN3" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="DO3" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="DP3" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="DQ3" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="DR3" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="DS3" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="DT3" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="DU3" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="DV3" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="DW3" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="DX3" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="DY3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="DZ3" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="EA3" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="EB3" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="EC3" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="ED3" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="EE3" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="EF3" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="EG3" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="EH3" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="EI3" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="EJ3" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="EK3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="EL3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="EM3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="EN3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="EO3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="EP3" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="EQ3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="ER3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="ES3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="ET3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="EU3" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="EV3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="EW3" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="EX3" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="EY3" t="s">
-        <v>823</v>
+        <v>827</v>
+      </c>
+      <c r="EZ3" t="s">
+        <v>831</v>
       </c>
       <c r="FA3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="FB3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="FC3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="FD3" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="FE3" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="FF3" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4" spans="1:162">
@@ -5127,22 +5140,22 @@
         <v>191</v>
       </c>
       <c r="H4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N4" t="s">
         <v>222</v>
@@ -5175,421 +5188,418 @@
         <v>266</v>
       </c>
       <c r="X4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AB4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AC4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AD4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AE4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AF4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AG4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AH4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AI4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AJ4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AK4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AM4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AN4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AO4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AP4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AQ4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AR4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AS4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AT4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AU4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AV4" t="s">
+        <v>378</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>378</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>387</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>391</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>396</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>401</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>406</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>416</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>421</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>425</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>381</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>431</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>436</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>441</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>444</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>450</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>381</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>453</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>458</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>462</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>467</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>472</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>477</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>482</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>486</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>490</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>494</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>499</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>504</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>509</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>381</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>514</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>517</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>519</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>523</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>528</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>533</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>537</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>539</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>544</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>548</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>552</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>557</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>562</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>567</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>571</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>573</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>577</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>581</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>585</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>589</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>592</v>
+      </c>
+      <c r="CW4" t="s">
+        <v>597</v>
+      </c>
+      <c r="CX4" t="s">
+        <v>599</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>604</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>381</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>609</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>614</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>616</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>621</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>625</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>628</v>
+      </c>
+      <c r="DG4" t="s">
+        <v>633</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>637</v>
+      </c>
+      <c r="DI4" t="s">
+        <v>641</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>644</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>649</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>654</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>659</v>
+      </c>
+      <c r="DN4" t="s">
+        <v>664</v>
+      </c>
+      <c r="DO4" t="s">
+        <v>669</v>
+      </c>
+      <c r="DP4" t="s">
+        <v>673</v>
+      </c>
+      <c r="DQ4" t="s">
+        <v>678</v>
+      </c>
+      <c r="DR4" t="s">
+        <v>682</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>687</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>692</v>
+      </c>
+      <c r="DU4" t="s">
+        <v>697</v>
+      </c>
+      <c r="DV4" t="s">
+        <v>702</v>
+      </c>
+      <c r="DW4" t="s">
+        <v>706</v>
+      </c>
+      <c r="DX4" t="s">
+        <v>710</v>
+      </c>
+      <c r="DY4" t="s">
+        <v>715</v>
+      </c>
+      <c r="DZ4" t="s">
+        <v>718</v>
+      </c>
+      <c r="EA4" t="s">
+        <v>723</v>
+      </c>
+      <c r="EB4" t="s">
         <v>374</v>
       </c>
-      <c r="AW4" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>380</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>384</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>388</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>393</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>395</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>400</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>405</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>409</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>414</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>418</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>423</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>428</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>433</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>438</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>442</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>444</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>447</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>452</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>457</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>462</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>467</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>472</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>476</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>480</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>483</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>487</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>492</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>497</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>502</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>375</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>505</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>510</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>514</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>517</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>522</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>527</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>530</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>534</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>539</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>540</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>545</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>550</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>553</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>559</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>562</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>565</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>569</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>574</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>575</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>579</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>583</v>
-      </c>
-      <c r="CW4" t="s">
-        <v>587</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>591</v>
-      </c>
-      <c r="CY4" t="s">
-        <v>595</v>
-      </c>
-      <c r="CZ4" t="s">
-        <v>375</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>600</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>605</v>
-      </c>
-      <c r="DC4" t="s">
-        <v>606</v>
-      </c>
-      <c r="DD4" t="s">
-        <v>611</v>
-      </c>
-      <c r="DE4" t="s">
-        <v>615</v>
-      </c>
-      <c r="DF4" t="s">
-        <v>619</v>
-      </c>
-      <c r="DG4" t="s">
-        <v>622</v>
-      </c>
-      <c r="DH4" t="s">
-        <v>626</v>
-      </c>
-      <c r="DI4" t="s">
-        <v>630</v>
-      </c>
-      <c r="DJ4" t="s">
-        <v>636</v>
-      </c>
-      <c r="DK4" t="s">
-        <v>640</v>
-      </c>
-      <c r="DL4" t="s">
-        <v>645</v>
-      </c>
-      <c r="DM4" t="s">
-        <v>650</v>
-      </c>
-      <c r="DN4" t="s">
-        <v>655</v>
-      </c>
-      <c r="DO4" t="s">
-        <v>660</v>
-      </c>
-      <c r="DP4" t="s">
-        <v>665</v>
-      </c>
-      <c r="DQ4" t="s">
-        <v>670</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>674</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>679</v>
-      </c>
-      <c r="DT4" t="s">
-        <v>684</v>
-      </c>
-      <c r="DU4" t="s">
-        <v>689</v>
-      </c>
-      <c r="DV4" t="s">
-        <v>694</v>
-      </c>
-      <c r="DW4" t="s">
-        <v>699</v>
-      </c>
-      <c r="DX4" t="s">
-        <v>702</v>
-      </c>
-      <c r="DY4" t="s">
-        <v>707</v>
-      </c>
-      <c r="DZ4" t="s">
-        <v>711</v>
-      </c>
-      <c r="EA4" t="s">
-        <v>715</v>
-      </c>
-      <c r="EB4" t="s">
-        <v>718</v>
-      </c>
       <c r="EC4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="ED4" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="EE4" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="EF4" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="EG4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="EH4" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="EI4" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="EJ4" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="EK4" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="EL4" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="EM4" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="EN4" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="EO4" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="EP4" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="EQ4" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="ER4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="ES4" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="ET4" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="EU4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="EV4" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="EW4" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="EX4" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="EY4" t="s">
-        <v>824</v>
-      </c>
-      <c r="EZ4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="FA4" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="FB4" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="FC4" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="FD4" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="FE4" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="FF4" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:162">
@@ -5603,7 +5613,7 @@
         <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
         <v>182</v>
@@ -5615,22 +5625,22 @@
         <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N5" t="s">
         <v>223</v>
@@ -5663,418 +5673,421 @@
         <v>267</v>
       </c>
       <c r="X5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Y5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AC5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AD5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AE5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AF5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AG5" t="s">
-        <v>165</v>
+        <v>316</v>
       </c>
       <c r="AH5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AI5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AJ5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AK5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AL5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AM5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AN5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AP5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AQ5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AR5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AS5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AT5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AU5" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AV5" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AW5" t="s">
+        <v>383</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>388</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>392</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>397</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>402</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>407</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>412</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>417</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>422</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>425</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>428</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>432</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>437</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>442</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>446</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>448</v>
+      </c>
+      <c r="BM5" t="s">
         <v>377</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="BN5" t="s">
+        <v>454</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>459</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>463</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>468</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>473</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>478</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>483</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>377</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>491</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>495</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>500</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>505</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>510</v>
+      </c>
+      <c r="CA5" t="s">
         <v>381</v>
       </c>
-      <c r="AY5" t="s">
-        <v>384</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>389</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>393</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>396</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>401</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>406</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>410</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>414</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>419</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>424</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>429</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>434</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>439</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>441</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>444</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>448</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>453</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>458</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>463</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>468</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>473</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>477</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>479</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>484</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>488</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>493</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>498</v>
-      </c>
-      <c r="BZ5" t="s">
-        <v>503</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>374</v>
-      </c>
       <c r="CB5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="CC5" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="CD5" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="CE5" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="CF5" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="CG5" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="CH5" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="CI5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="CJ5" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="CK5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="CL5" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="CM5" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="CN5" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="CO5" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="CP5" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="CQ5" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="CR5" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="CS5" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="CT5" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="CU5" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="CV5" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="CW5" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="CX5" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="CY5" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="CZ5" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="DA5" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="DB5" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="DC5" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="DD5" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="DE5" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="DF5" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="DG5" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="DH5" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="DI5" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="DJ5" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="DK5" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="DL5" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="DM5" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="DN5" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="DO5" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="DP5" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="DQ5" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="DR5" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="DS5" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="DT5" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="DU5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="DV5" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="DW5" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="DX5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="DY5" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="DZ5" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="EA5" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="EB5" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="EC5" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="ED5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="EE5" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="EF5" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="EG5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="EH5" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="EI5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="EJ5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="EK5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="EL5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="EM5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="EN5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="EO5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="EP5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="EQ5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="ER5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="ES5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="ET5" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="EU5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="EV5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="EW5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="EX5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="EY5" t="s">
-        <v>825</v>
+        <v>829</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>832</v>
       </c>
       <c r="FA5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="FB5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="FC5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="FD5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="FE5" t="s">
-        <v>852</v>
+        <v>426</v>
       </c>
       <c r="FF5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="6" spans="1:162">
@@ -6088,7 +6101,7 @@
         <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
         <v>183</v>
@@ -6097,22 +6110,22 @@
         <v>188</v>
       </c>
       <c r="G6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M6" t="s">
         <v>219</v>
@@ -6145,424 +6158,418 @@
         <v>264</v>
       </c>
       <c r="W6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Y6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AB6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AC6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AD6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AE6" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG6" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="AH6" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AI6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AJ6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AK6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AL6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AM6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AP6" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AQ6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AR6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AS6" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AT6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AU6" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AV6" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="AW6" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="AX6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="AY6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AZ6" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="BA6" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="BB6" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="BC6" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="BD6" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="BE6" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="BF6" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="BG6" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="BH6" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="BI6" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="BJ6" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="BK6" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="BL6" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="BM6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="BN6" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="BO6" t="s">
-        <v>454</v>
+        <v>177</v>
       </c>
       <c r="BP6" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="BQ6" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="BR6" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="BS6" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="BT6" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="BU6" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="BV6" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="BW6" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="BX6" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="BY6" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="BZ6" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="CA6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="CB6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="CC6" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="CD6" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="CE6" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="CF6" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="CG6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="CH6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="CI6" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="CJ6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="CK6" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="CL6" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="CM6" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="CN6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="CO6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="CP6" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="CQ6" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="CR6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="CS6" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="CT6" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="CU6" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="CV6" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="CW6" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="CX6" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="CY6" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="CZ6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="DA6" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="DB6" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="DC6" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="DD6" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="DE6" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="DF6" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="DG6" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="DH6" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="DI6" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="DJ6" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="DK6" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="DL6" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="DM6" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="DN6" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="DO6" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="DP6" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="DQ6" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="DR6" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="DS6" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="DT6" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="DU6" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="DV6" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="DW6" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="DX6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="DY6" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="DZ6" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="EA6" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="EB6" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="EC6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="ED6" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="EE6" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="EF6" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="EG6" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="EH6" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="EI6" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="EJ6" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="EK6" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="EL6" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="EM6" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="EN6" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="EO6" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="EP6" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="EQ6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="ER6" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="ES6" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="ET6" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="EU6" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="EV6" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="EW6" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="EX6" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="EY6" t="s">
-        <v>826</v>
-      </c>
-      <c r="EZ6" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="FA6" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="FB6" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="FC6" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="FD6" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="FE6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="FF6" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
   </sheetData>
@@ -6581,13 +6588,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6595,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6609,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6620,7 +6627,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6631,7 +6638,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6642,7 +6649,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6653,7 +6660,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6664,7 +6671,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6675,7 +6682,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6686,7 +6693,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6694,10 +6701,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C11" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6708,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6719,7 +6726,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6730,7 +6737,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6738,10 +6745,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C15" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6749,10 +6756,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C16" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6760,10 +6767,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C17" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6774,7 +6781,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6785,7 +6792,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6793,10 +6800,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C20" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6807,7 +6814,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6818,7 +6825,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6829,7 +6836,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6840,7 +6847,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6851,7 +6858,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6859,10 +6866,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C26" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6873,7 +6880,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6884,7 +6891,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6892,10 +6899,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C29" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6903,10 +6910,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C30" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6917,7 +6924,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6928,7 +6935,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6939,7 +6946,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6950,7 +6957,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6961,7 +6968,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6972,7 +6979,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6983,7 +6990,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6994,7 +7001,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7005,7 +7012,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7016,7 +7023,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7027,7 +7034,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7035,10 +7042,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C42" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7046,10 +7053,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C43" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7057,10 +7064,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C44" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7068,10 +7075,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C45" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7082,7 +7089,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7090,10 +7097,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C47" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7104,7 +7111,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7115,7 +7122,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7126,7 +7133,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7137,7 +7144,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7148,7 +7155,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7159,7 +7166,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7170,7 +7177,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7181,7 +7188,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7192,7 +7199,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7203,7 +7210,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7214,7 +7221,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7225,7 +7232,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7236,7 +7243,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7247,7 +7254,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7258,7 +7265,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7269,7 +7276,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7280,7 +7287,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7291,7 +7298,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7302,7 +7309,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7313,7 +7320,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7324,7 +7331,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7335,7 +7342,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7346,7 +7353,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7357,7 +7364,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7368,7 +7375,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7379,7 +7386,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7390,7 +7397,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7401,7 +7408,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7412,7 +7419,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7423,7 +7430,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7434,7 +7441,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7445,7 +7452,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7456,7 +7463,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7467,7 +7474,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7478,7 +7485,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7489,7 +7496,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7500,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7511,7 +7518,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7522,7 +7529,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7533,7 +7540,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7544,7 +7551,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7555,7 +7562,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7566,7 +7573,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7577,7 +7584,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7588,7 +7595,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7599,7 +7606,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7610,7 +7617,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7621,7 +7628,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7632,7 +7639,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7643,7 +7650,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7654,7 +7661,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7665,7 +7672,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7676,7 +7683,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7687,7 +7694,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7698,7 +7705,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7709,7 +7716,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7720,7 +7727,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7731,7 +7738,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7742,7 +7749,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7753,7 +7760,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7764,7 +7771,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7775,7 +7782,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7786,7 +7793,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7797,7 +7804,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7808,7 +7815,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7819,7 +7826,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7830,7 +7837,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7841,7 +7848,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7852,7 +7859,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7863,7 +7870,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7874,7 +7881,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7885,7 +7892,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7896,7 +7903,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7907,7 +7914,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7918,7 +7925,7 @@
         <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7929,7 +7936,7 @@
         <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7940,7 +7947,7 @@
         <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7951,7 +7958,7 @@
         <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7962,7 +7969,7 @@
         <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7973,7 +7980,7 @@
         <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7984,7 +7991,7 @@
         <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7995,7 +8002,7 @@
         <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8006,7 +8013,7 @@
         <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8017,7 +8024,7 @@
         <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8028,7 +8035,7 @@
         <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8039,7 +8046,7 @@
         <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8050,7 +8057,7 @@
         <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8061,7 +8068,7 @@
         <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8072,7 +8079,7 @@
         <v>134</v>
       </c>
       <c r="C136" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8083,7 +8090,7 @@
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8094,7 +8101,7 @@
         <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8105,7 +8112,7 @@
         <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8116,7 +8123,7 @@
         <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8127,7 +8134,7 @@
         <v>139</v>
       </c>
       <c r="C141" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8138,7 +8145,7 @@
         <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8149,7 +8156,7 @@
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8160,7 +8167,7 @@
         <v>142</v>
       </c>
       <c r="C144" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8171,7 +8178,7 @@
         <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8182,7 +8189,7 @@
         <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8193,7 +8200,7 @@
         <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8204,7 +8211,7 @@
         <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8215,7 +8222,7 @@
         <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8226,7 +8233,7 @@
         <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8237,7 +8244,7 @@
         <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8248,7 +8255,7 @@
         <v>150</v>
       </c>
       <c r="C152" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8259,7 +8266,7 @@
         <v>151</v>
       </c>
       <c r="C153" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8270,7 +8277,7 @@
         <v>152</v>
       </c>
       <c r="C154" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8281,7 +8288,7 @@
         <v>153</v>
       </c>
       <c r="C155" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8292,7 +8299,7 @@
         <v>154</v>
       </c>
       <c r="C156" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8303,7 +8310,7 @@
         <v>155</v>
       </c>
       <c r="C157" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8314,7 +8321,7 @@
         <v>156</v>
       </c>
       <c r="C158" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8325,7 +8332,7 @@
         <v>157</v>
       </c>
       <c r="C159" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8336,7 +8343,7 @@
         <v>158</v>
       </c>
       <c r="C160" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8347,7 +8354,7 @@
         <v>159</v>
       </c>
       <c r="C161" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8358,7 +8365,7 @@
         <v>160</v>
       </c>
       <c r="C162" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8369,7 +8376,7 @@
         <v>161</v>
       </c>
       <c r="C163" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
